--- a/V9_W8_B32/data_instructions/VLIW_Excel/Unit2_to_4_ShuffleUnit.xlsx
+++ b/V9_W8_B32/data_instructions/VLIW_Excel/Unit2_to_4_ShuffleUnit.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\legoa\NCU\專題\專題內容\組譯器\WeightBiasRearranger\V7\data_instructions\VLIW_Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\legoa\NCU\專題\專題內容\組譯器\WeightBiasRearranger\V9_W8_B32\data_instructions\VLIW_Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5644E8C8-6879-430D-BB7B-C978CDBB88CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DE230FA-F5BF-4470-8E30-5A4CD35FC68A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{78D60548-BA91-4173-9352-325C39DD31E5}"/>
+    <workbookView xWindow="10718" yWindow="0" windowWidth="10965" windowHeight="12863" xr2:uid="{78D60548-BA91-4173-9352-325C39DD31E5}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1699" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1700" uniqueCount="98">
   <si>
     <t>OP_Code</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -428,6 +428,10 @@
     <t>002016_2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>Requant_Sel[3]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -667,16 +671,37 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -688,18 +713,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -707,15 +720,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1181,23 +1185,26 @@
       <c r="M5" s="8" t="s">
         <v>71</v>
       </c>
+      <c r="N5" s="7" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.45">
       <c r="B7" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="20" t="s">
+      <c r="C7" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="E7" s="20"/>
-      <c r="F7" s="32"/>
-      <c r="G7" s="20"/>
-      <c r="H7" s="20"/>
-      <c r="I7" s="20"/>
-      <c r="J7" s="20"/>
+      <c r="D7" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" s="18"/>
+      <c r="F7" s="20"/>
+      <c r="G7" s="18"/>
+      <c r="H7" s="18"/>
+      <c r="I7" s="18"/>
+      <c r="J7" s="18"/>
       <c r="L7" s="9" t="s">
         <v>0</v>
       </c>
@@ -1223,14 +1230,14 @@
       <c r="B8">
         <v>0</v>
       </c>
-      <c r="C8" s="20"/>
-      <c r="D8" s="33"/>
-      <c r="E8" s="20"/>
-      <c r="F8" s="33"/>
-      <c r="G8" s="20"/>
-      <c r="H8" s="20"/>
-      <c r="I8" s="20"/>
-      <c r="J8" s="20"/>
+      <c r="C8" s="18"/>
+      <c r="D8" s="21"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="21"/>
+      <c r="G8" s="18"/>
+      <c r="H8" s="18"/>
+      <c r="I8" s="18"/>
+      <c r="J8" s="18"/>
       <c r="L8" s="11" t="s">
         <v>5</v>
       </c>
@@ -1269,14 +1276,14 @@
       <c r="A9">
         <v>0</v>
       </c>
-      <c r="C9" s="20"/>
-      <c r="D9" s="33"/>
-      <c r="E9" s="20"/>
-      <c r="F9" s="33"/>
-      <c r="G9" s="20"/>
-      <c r="H9" s="20"/>
-      <c r="I9" s="20"/>
-      <c r="J9" s="20"/>
+      <c r="C9" s="18"/>
+      <c r="D9" s="21"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="21"/>
+      <c r="G9" s="18"/>
+      <c r="H9" s="18"/>
+      <c r="I9" s="18"/>
+      <c r="J9" s="18"/>
       <c r="L9" s="12" t="s">
         <v>15</v>
       </c>
@@ -1293,14 +1300,14 @@
       <c r="U9" s="10"/>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C10" s="20"/>
-      <c r="D10" s="33"/>
-      <c r="E10" s="20"/>
-      <c r="F10" s="33"/>
-      <c r="G10" s="20"/>
-      <c r="H10" s="20"/>
-      <c r="I10" s="20"/>
-      <c r="J10" s="20"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="21"/>
+      <c r="G10" s="18"/>
+      <c r="H10" s="18"/>
+      <c r="I10" s="18"/>
+      <c r="J10" s="18"/>
       <c r="L10" s="14" t="s">
         <v>17</v>
       </c>
@@ -1324,14 +1331,14 @@
       <c r="U10" s="10"/>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C11" s="20"/>
-      <c r="D11" s="34"/>
-      <c r="E11" s="20"/>
-      <c r="F11" s="34"/>
-      <c r="G11" s="20"/>
-      <c r="H11" s="20"/>
-      <c r="I11" s="20"/>
-      <c r="J11" s="20"/>
+      <c r="C11" s="18"/>
+      <c r="D11" s="22"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="22"/>
+      <c r="G11" s="18"/>
+      <c r="H11" s="18"/>
+      <c r="I11" s="18"/>
+      <c r="J11" s="18"/>
       <c r="L11" s="15" t="s">
         <v>23</v>
       </c>
@@ -1353,22 +1360,22 @@
       <c r="B12" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C12" s="20" t="s">
+      <c r="C12" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="D12" s="18" t="s">
+      <c r="D12" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E12" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="F12" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="G12" s="20"/>
-      <c r="H12" s="20"/>
-      <c r="I12" s="20"/>
-      <c r="J12" s="20"/>
+      <c r="E12" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="F12" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="G12" s="18"/>
+      <c r="H12" s="18"/>
+      <c r="I12" s="18"/>
+      <c r="J12" s="18"/>
       <c r="L12" s="9" t="s">
         <v>0</v>
       </c>
@@ -1394,14 +1401,14 @@
       <c r="B13">
         <v>1</v>
       </c>
-      <c r="C13" s="20"/>
-      <c r="D13" s="18"/>
-      <c r="E13" s="33"/>
-      <c r="F13" s="19"/>
-      <c r="G13" s="20"/>
-      <c r="H13" s="20"/>
-      <c r="I13" s="20"/>
-      <c r="J13" s="20"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="21"/>
+      <c r="F13" s="23"/>
+      <c r="G13" s="18"/>
+      <c r="H13" s="18"/>
+      <c r="I13" s="18"/>
+      <c r="J13" s="18"/>
       <c r="L13" s="11" t="s">
         <v>5</v>
       </c>
@@ -1437,14 +1444,14 @@
       </c>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C14" s="20"/>
-      <c r="D14" s="18"/>
-      <c r="E14" s="33"/>
-      <c r="F14" s="19"/>
-      <c r="G14" s="20"/>
-      <c r="H14" s="20"/>
-      <c r="I14" s="20"/>
-      <c r="J14" s="20"/>
+      <c r="C14" s="18"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="21"/>
+      <c r="F14" s="23"/>
+      <c r="G14" s="18"/>
+      <c r="H14" s="18"/>
+      <c r="I14" s="18"/>
+      <c r="J14" s="18"/>
       <c r="L14" s="12" t="s">
         <v>15</v>
       </c>
@@ -1470,14 +1477,14 @@
       </c>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C15" s="20"/>
-      <c r="D15" s="18"/>
-      <c r="E15" s="33"/>
-      <c r="F15" s="19"/>
-      <c r="G15" s="20"/>
-      <c r="H15" s="20"/>
-      <c r="I15" s="20"/>
-      <c r="J15" s="20"/>
+      <c r="C15" s="18"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="21"/>
+      <c r="F15" s="23"/>
+      <c r="G15" s="18"/>
+      <c r="H15" s="18"/>
+      <c r="I15" s="18"/>
+      <c r="J15" s="18"/>
       <c r="L15" s="14" t="s">
         <v>17</v>
       </c>
@@ -1501,14 +1508,14 @@
       <c r="U15" s="10"/>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C16" s="20"/>
-      <c r="D16" s="18"/>
-      <c r="E16" s="34"/>
-      <c r="F16" s="19"/>
-      <c r="G16" s="20"/>
-      <c r="H16" s="20"/>
-      <c r="I16" s="20"/>
-      <c r="J16" s="20"/>
+      <c r="C16" s="18"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="22"/>
+      <c r="F16" s="23"/>
+      <c r="G16" s="18"/>
+      <c r="H16" s="18"/>
+      <c r="I16" s="18"/>
+      <c r="J16" s="18"/>
       <c r="L16" s="15" t="s">
         <v>23</v>
       </c>
@@ -1527,22 +1534,22 @@
       <c r="U16" s="10"/>
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C17" s="20" t="s">
+      <c r="C17" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="D17" s="32"/>
-      <c r="E17" s="18" t="s">
+      <c r="D17" s="20"/>
+      <c r="E17" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="F17" s="28" t="s">
-        <v>26</v>
-      </c>
-      <c r="G17" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="H17" s="20"/>
-      <c r="I17" s="20"/>
-      <c r="J17" s="20"/>
+      <c r="F17" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="G17" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="H17" s="18"/>
+      <c r="I17" s="18"/>
+      <c r="J17" s="18"/>
       <c r="L17" s="9" t="s">
         <v>0</v>
       </c>
@@ -1565,14 +1572,14 @@
       <c r="U17" s="10"/>
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C18" s="20"/>
-      <c r="D18" s="33"/>
-      <c r="E18" s="18"/>
-      <c r="F18" s="21"/>
-      <c r="G18" s="19"/>
-      <c r="H18" s="20"/>
-      <c r="I18" s="20"/>
-      <c r="J18" s="20"/>
+      <c r="C18" s="18"/>
+      <c r="D18" s="21"/>
+      <c r="E18" s="19"/>
+      <c r="F18" s="24"/>
+      <c r="G18" s="23"/>
+      <c r="H18" s="18"/>
+      <c r="I18" s="18"/>
+      <c r="J18" s="18"/>
       <c r="L18" s="11" t="s">
         <v>5</v>
       </c>
@@ -1608,14 +1615,14 @@
       </c>
     </row>
     <row r="19" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C19" s="20"/>
-      <c r="D19" s="33"/>
-      <c r="E19" s="18"/>
-      <c r="F19" s="21"/>
-      <c r="G19" s="19"/>
-      <c r="H19" s="20"/>
-      <c r="I19" s="20"/>
-      <c r="J19" s="20"/>
+      <c r="C19" s="18"/>
+      <c r="D19" s="21"/>
+      <c r="E19" s="19"/>
+      <c r="F19" s="24"/>
+      <c r="G19" s="23"/>
+      <c r="H19" s="18"/>
+      <c r="I19" s="18"/>
+      <c r="J19" s="18"/>
       <c r="L19" s="12" t="s">
         <v>15</v>
       </c>
@@ -1641,14 +1648,14 @@
       </c>
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C20" s="20"/>
-      <c r="D20" s="33"/>
-      <c r="E20" s="18"/>
-      <c r="F20" s="21"/>
-      <c r="G20" s="19"/>
-      <c r="H20" s="20"/>
-      <c r="I20" s="20"/>
-      <c r="J20" s="20"/>
+      <c r="C20" s="18"/>
+      <c r="D20" s="21"/>
+      <c r="E20" s="19"/>
+      <c r="F20" s="24"/>
+      <c r="G20" s="23"/>
+      <c r="H20" s="18"/>
+      <c r="I20" s="18"/>
+      <c r="J20" s="18"/>
       <c r="L20" s="14" t="s">
         <v>17</v>
       </c>
@@ -1671,14 +1678,14 @@
       <c r="U20" s="10"/>
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C21" s="20"/>
-      <c r="D21" s="34"/>
-      <c r="E21" s="18"/>
-      <c r="F21" s="21"/>
-      <c r="G21" s="19"/>
-      <c r="H21" s="20"/>
-      <c r="I21" s="20"/>
-      <c r="J21" s="20"/>
+      <c r="C21" s="18"/>
+      <c r="D21" s="22"/>
+      <c r="E21" s="19"/>
+      <c r="F21" s="24"/>
+      <c r="G21" s="23"/>
+      <c r="H21" s="18"/>
+      <c r="I21" s="18"/>
+      <c r="J21" s="18"/>
       <c r="L21" s="15" t="s">
         <v>23</v>
       </c>
@@ -1698,24 +1705,24 @@
       <c r="B22" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C22" s="20" t="s">
+      <c r="C22" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="D22" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="E22" s="21"/>
-      <c r="F22" s="18" t="s">
+      <c r="D22" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="E22" s="24"/>
+      <c r="F22" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="G22" s="18" t="s">
+      <c r="G22" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="H22" s="20"/>
-      <c r="I22" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="J22" s="20"/>
+      <c r="H22" s="18"/>
+      <c r="I22" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="J22" s="18"/>
       <c r="L22" s="9" t="s">
         <v>0</v>
       </c>
@@ -1741,14 +1748,14 @@
       <c r="B23">
         <v>2</v>
       </c>
-      <c r="C23" s="20"/>
-      <c r="D23" s="33"/>
-      <c r="E23" s="21"/>
-      <c r="F23" s="18"/>
-      <c r="G23" s="18"/>
-      <c r="H23" s="20"/>
-      <c r="I23" s="19"/>
-      <c r="J23" s="20"/>
+      <c r="C23" s="18"/>
+      <c r="D23" s="21"/>
+      <c r="E23" s="24"/>
+      <c r="F23" s="19"/>
+      <c r="G23" s="19"/>
+      <c r="H23" s="18"/>
+      <c r="I23" s="23"/>
+      <c r="J23" s="18"/>
       <c r="L23" s="11" t="s">
         <v>5</v>
       </c>
@@ -1784,14 +1791,14 @@
       </c>
     </row>
     <row r="24" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C24" s="20"/>
-      <c r="D24" s="33"/>
-      <c r="E24" s="21"/>
-      <c r="F24" s="18"/>
-      <c r="G24" s="18"/>
-      <c r="H24" s="20"/>
-      <c r="I24" s="19"/>
-      <c r="J24" s="20"/>
+      <c r="C24" s="18"/>
+      <c r="D24" s="21"/>
+      <c r="E24" s="24"/>
+      <c r="F24" s="19"/>
+      <c r="G24" s="19"/>
+      <c r="H24" s="18"/>
+      <c r="I24" s="23"/>
+      <c r="J24" s="18"/>
       <c r="L24" s="12" t="s">
         <v>15</v>
       </c>
@@ -1817,14 +1824,14 @@
       </c>
     </row>
     <row r="25" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C25" s="20"/>
-      <c r="D25" s="33"/>
-      <c r="E25" s="21"/>
-      <c r="F25" s="18"/>
-      <c r="G25" s="18"/>
-      <c r="H25" s="20"/>
-      <c r="I25" s="19"/>
-      <c r="J25" s="20"/>
+      <c r="C25" s="18"/>
+      <c r="D25" s="21"/>
+      <c r="E25" s="24"/>
+      <c r="F25" s="19"/>
+      <c r="G25" s="19"/>
+      <c r="H25" s="18"/>
+      <c r="I25" s="23"/>
+      <c r="J25" s="18"/>
       <c r="L25" s="14" t="s">
         <v>17</v>
       </c>
@@ -1848,14 +1855,14 @@
       <c r="U25" s="10"/>
     </row>
     <row r="26" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C26" s="20"/>
-      <c r="D26" s="34"/>
-      <c r="E26" s="21"/>
-      <c r="F26" s="18"/>
-      <c r="G26" s="18"/>
-      <c r="H26" s="20"/>
-      <c r="I26" s="19"/>
-      <c r="J26" s="20"/>
+      <c r="C26" s="18"/>
+      <c r="D26" s="22"/>
+      <c r="E26" s="24"/>
+      <c r="F26" s="19"/>
+      <c r="G26" s="19"/>
+      <c r="H26" s="18"/>
+      <c r="I26" s="23"/>
+      <c r="J26" s="18"/>
       <c r="L26" s="15" t="s">
         <v>23</v>
       </c>
@@ -1883,26 +1890,26 @@
       <c r="A29" t="s">
         <v>48</v>
       </c>
-      <c r="C29" s="20" t="s">
+      <c r="C29" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="D29" s="18" t="s">
+      <c r="D29" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E29" s="21"/>
-      <c r="F29" s="28" t="s">
-        <v>26</v>
-      </c>
-      <c r="G29" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="H29" s="19" t="s">
+      <c r="E29" s="24"/>
+      <c r="F29" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="G29" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="H29" s="23" t="s">
         <v>26</v>
       </c>
       <c r="I29" s="26" t="s">
         <v>49</v>
       </c>
-      <c r="J29" s="20"/>
+      <c r="J29" s="18"/>
       <c r="L29" s="9" t="s">
         <v>0</v>
       </c>
@@ -1925,14 +1932,14 @@
       <c r="U29" s="10"/>
     </row>
     <row r="30" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C30" s="20"/>
-      <c r="D30" s="18"/>
-      <c r="E30" s="21"/>
-      <c r="F30" s="21"/>
-      <c r="G30" s="20"/>
-      <c r="H30" s="19"/>
+      <c r="C30" s="18"/>
+      <c r="D30" s="19"/>
+      <c r="E30" s="24"/>
+      <c r="F30" s="24"/>
+      <c r="G30" s="18"/>
+      <c r="H30" s="23"/>
       <c r="I30" s="27"/>
-      <c r="J30" s="20"/>
+      <c r="J30" s="18"/>
       <c r="L30" s="11" t="s">
         <v>5</v>
       </c>
@@ -1968,14 +1975,14 @@
       </c>
     </row>
     <row r="31" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C31" s="20"/>
-      <c r="D31" s="18"/>
-      <c r="E31" s="21"/>
-      <c r="F31" s="21"/>
-      <c r="G31" s="20"/>
-      <c r="H31" s="19"/>
+      <c r="C31" s="18"/>
+      <c r="D31" s="19"/>
+      <c r="E31" s="24"/>
+      <c r="F31" s="24"/>
+      <c r="G31" s="18"/>
+      <c r="H31" s="23"/>
       <c r="I31" s="27"/>
-      <c r="J31" s="20"/>
+      <c r="J31" s="18"/>
       <c r="L31" s="12" t="s">
         <v>15</v>
       </c>
@@ -2001,14 +2008,14 @@
       </c>
     </row>
     <row r="32" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C32" s="20"/>
-      <c r="D32" s="18"/>
-      <c r="E32" s="21"/>
-      <c r="F32" s="21"/>
-      <c r="G32" s="20"/>
-      <c r="H32" s="19"/>
+      <c r="C32" s="18"/>
+      <c r="D32" s="19"/>
+      <c r="E32" s="24"/>
+      <c r="F32" s="24"/>
+      <c r="G32" s="18"/>
+      <c r="H32" s="23"/>
       <c r="I32" s="27"/>
-      <c r="J32" s="20"/>
+      <c r="J32" s="18"/>
       <c r="L32" s="14" t="s">
         <v>17</v>
       </c>
@@ -2031,14 +2038,14 @@
       <c r="U32" s="10"/>
     </row>
     <row r="33" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C33" s="20"/>
-      <c r="D33" s="18"/>
-      <c r="E33" s="21"/>
-      <c r="F33" s="21"/>
-      <c r="G33" s="20"/>
-      <c r="H33" s="19"/>
+      <c r="C33" s="18"/>
+      <c r="D33" s="19"/>
+      <c r="E33" s="24"/>
+      <c r="F33" s="24"/>
+      <c r="G33" s="18"/>
+      <c r="H33" s="23"/>
       <c r="I33" s="27"/>
-      <c r="J33" s="20"/>
+      <c r="J33" s="18"/>
       <c r="L33" s="15" t="s">
         <v>23</v>
       </c>
@@ -2055,24 +2062,24 @@
       <c r="U33" s="10"/>
     </row>
     <row r="34" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C34" s="20" t="s">
+      <c r="C34" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="D34" s="20"/>
-      <c r="E34" s="20"/>
-      <c r="F34" s="28" t="s">
-        <v>26</v>
-      </c>
-      <c r="G34" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="H34" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="I34" s="18" t="s">
+      <c r="D34" s="18"/>
+      <c r="E34" s="18"/>
+      <c r="F34" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="G34" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="H34" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="I34" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="J34" s="19" t="s">
+      <c r="J34" s="23" t="s">
         <v>26</v>
       </c>
       <c r="L34" s="9" t="s">
@@ -2097,14 +2104,14 @@
       <c r="U34" s="10"/>
     </row>
     <row r="35" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C35" s="20"/>
-      <c r="D35" s="20"/>
-      <c r="E35" s="20"/>
-      <c r="F35" s="21"/>
-      <c r="G35" s="20"/>
-      <c r="H35" s="20"/>
-      <c r="I35" s="18"/>
-      <c r="J35" s="19"/>
+      <c r="C35" s="18"/>
+      <c r="D35" s="18"/>
+      <c r="E35" s="18"/>
+      <c r="F35" s="24"/>
+      <c r="G35" s="18"/>
+      <c r="H35" s="18"/>
+      <c r="I35" s="19"/>
+      <c r="J35" s="23"/>
       <c r="L35" s="11" t="s">
         <v>5</v>
       </c>
@@ -2143,14 +2150,14 @@
       <c r="A36">
         <v>5</v>
       </c>
-      <c r="C36" s="20"/>
-      <c r="D36" s="20"/>
-      <c r="E36" s="20"/>
-      <c r="F36" s="21"/>
-      <c r="G36" s="20"/>
-      <c r="H36" s="20"/>
-      <c r="I36" s="18"/>
-      <c r="J36" s="19"/>
+      <c r="C36" s="18"/>
+      <c r="D36" s="18"/>
+      <c r="E36" s="18"/>
+      <c r="F36" s="24"/>
+      <c r="G36" s="18"/>
+      <c r="H36" s="18"/>
+      <c r="I36" s="19"/>
+      <c r="J36" s="23"/>
       <c r="L36" s="12" t="s">
         <v>15</v>
       </c>
@@ -2176,14 +2183,14 @@
       </c>
     </row>
     <row r="37" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C37" s="20"/>
-      <c r="D37" s="20"/>
-      <c r="E37" s="20"/>
-      <c r="F37" s="21"/>
-      <c r="G37" s="20"/>
-      <c r="H37" s="20"/>
-      <c r="I37" s="18"/>
-      <c r="J37" s="19"/>
+      <c r="C37" s="18"/>
+      <c r="D37" s="18"/>
+      <c r="E37" s="18"/>
+      <c r="F37" s="24"/>
+      <c r="G37" s="18"/>
+      <c r="H37" s="18"/>
+      <c r="I37" s="19"/>
+      <c r="J37" s="23"/>
       <c r="L37" s="14" t="s">
         <v>17</v>
       </c>
@@ -2206,14 +2213,14 @@
       <c r="U37" s="10"/>
     </row>
     <row r="38" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C38" s="20"/>
-      <c r="D38" s="20"/>
-      <c r="E38" s="20"/>
-      <c r="F38" s="21"/>
-      <c r="G38" s="20"/>
-      <c r="H38" s="20"/>
-      <c r="I38" s="18"/>
-      <c r="J38" s="19"/>
+      <c r="C38" s="18"/>
+      <c r="D38" s="18"/>
+      <c r="E38" s="18"/>
+      <c r="F38" s="24"/>
+      <c r="G38" s="18"/>
+      <c r="H38" s="18"/>
+      <c r="I38" s="19"/>
+      <c r="J38" s="23"/>
       <c r="L38" s="15" t="s">
         <v>23</v>
       </c>
@@ -2233,26 +2240,26 @@
       <c r="B39" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C39" s="20" t="s">
+      <c r="C39" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="D39" s="20"/>
-      <c r="E39" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="F39" s="18" t="s">
+      <c r="D39" s="18"/>
+      <c r="E39" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="F39" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="G39" s="18" t="s">
+      <c r="G39" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="H39" s="18" t="s">
+      <c r="H39" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="I39" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="J39" s="25" t="s">
+      <c r="I39" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="J39" s="28" t="s">
         <v>32</v>
       </c>
       <c r="L39" s="9" t="s">
@@ -2280,14 +2287,14 @@
       <c r="B40">
         <v>3</v>
       </c>
-      <c r="C40" s="20"/>
-      <c r="D40" s="20"/>
-      <c r="E40" s="21"/>
-      <c r="F40" s="18"/>
-      <c r="G40" s="18"/>
-      <c r="H40" s="18"/>
-      <c r="I40" s="19"/>
-      <c r="J40" s="25"/>
+      <c r="C40" s="18"/>
+      <c r="D40" s="18"/>
+      <c r="E40" s="24"/>
+      <c r="F40" s="19"/>
+      <c r="G40" s="19"/>
+      <c r="H40" s="19"/>
+      <c r="I40" s="23"/>
+      <c r="J40" s="28"/>
       <c r="L40" s="11" t="s">
         <v>5</v>
       </c>
@@ -2326,14 +2333,14 @@
       <c r="B41" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="C41" s="20"/>
-      <c r="D41" s="20"/>
-      <c r="E41" s="21"/>
-      <c r="F41" s="18"/>
-      <c r="G41" s="18"/>
-      <c r="H41" s="18"/>
-      <c r="I41" s="19"/>
-      <c r="J41" s="25"/>
+      <c r="C41" s="18"/>
+      <c r="D41" s="18"/>
+      <c r="E41" s="24"/>
+      <c r="F41" s="19"/>
+      <c r="G41" s="19"/>
+      <c r="H41" s="19"/>
+      <c r="I41" s="23"/>
+      <c r="J41" s="28"/>
       <c r="L41" s="12" t="s">
         <v>15</v>
       </c>
@@ -2362,14 +2369,14 @@
       <c r="B42">
         <v>0</v>
       </c>
-      <c r="C42" s="20"/>
-      <c r="D42" s="20"/>
-      <c r="E42" s="21"/>
-      <c r="F42" s="18"/>
-      <c r="G42" s="18"/>
-      <c r="H42" s="18"/>
-      <c r="I42" s="19"/>
-      <c r="J42" s="25"/>
+      <c r="C42" s="18"/>
+      <c r="D42" s="18"/>
+      <c r="E42" s="24"/>
+      <c r="F42" s="19"/>
+      <c r="G42" s="19"/>
+      <c r="H42" s="19"/>
+      <c r="I42" s="23"/>
+      <c r="J42" s="28"/>
       <c r="L42" s="14" t="s">
         <v>17</v>
       </c>
@@ -2394,14 +2401,14 @@
       <c r="U42" s="10"/>
     </row>
     <row r="43" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C43" s="20"/>
-      <c r="D43" s="20"/>
-      <c r="E43" s="21"/>
-      <c r="F43" s="18"/>
-      <c r="G43" s="18"/>
-      <c r="H43" s="18"/>
-      <c r="I43" s="19"/>
-      <c r="J43" s="25"/>
+      <c r="C43" s="18"/>
+      <c r="D43" s="18"/>
+      <c r="E43" s="24"/>
+      <c r="F43" s="19"/>
+      <c r="G43" s="19"/>
+      <c r="H43" s="19"/>
+      <c r="I43" s="23"/>
+      <c r="J43" s="28"/>
       <c r="L43" s="15" t="s">
         <v>23</v>
       </c>
@@ -2425,26 +2432,26 @@
       <c r="P44" s="10"/>
     </row>
     <row r="45" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C45" s="20" t="s">
+      <c r="C45" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="D45" s="18"/>
-      <c r="E45" s="18" t="s">
+      <c r="D45" s="19"/>
+      <c r="E45" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="F45" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="G45" s="28" t="s">
-        <v>26</v>
-      </c>
-      <c r="H45" s="28" t="s">
+      <c r="F45" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="G45" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="H45" s="25" t="s">
         <v>26</v>
       </c>
       <c r="I45" s="26" t="s">
         <v>49</v>
       </c>
-      <c r="J45" s="20"/>
+      <c r="J45" s="18"/>
       <c r="L45" s="9" t="s">
         <v>0</v>
       </c>
@@ -2467,14 +2474,14 @@
       <c r="U45" s="10"/>
     </row>
     <row r="46" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C46" s="20"/>
-      <c r="D46" s="18"/>
-      <c r="E46" s="18"/>
-      <c r="F46" s="19"/>
-      <c r="G46" s="21"/>
-      <c r="H46" s="21"/>
+      <c r="C46" s="18"/>
+      <c r="D46" s="19"/>
+      <c r="E46" s="19"/>
+      <c r="F46" s="23"/>
+      <c r="G46" s="24"/>
+      <c r="H46" s="24"/>
       <c r="I46" s="27"/>
-      <c r="J46" s="20"/>
+      <c r="J46" s="18"/>
       <c r="L46" s="11" t="s">
         <v>5</v>
       </c>
@@ -2510,14 +2517,14 @@
       </c>
     </row>
     <row r="47" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C47" s="20"/>
-      <c r="D47" s="18"/>
-      <c r="E47" s="18"/>
-      <c r="F47" s="19"/>
-      <c r="G47" s="21"/>
-      <c r="H47" s="21"/>
+      <c r="C47" s="18"/>
+      <c r="D47" s="19"/>
+      <c r="E47" s="19"/>
+      <c r="F47" s="23"/>
+      <c r="G47" s="24"/>
+      <c r="H47" s="24"/>
       <c r="I47" s="27"/>
-      <c r="J47" s="20"/>
+      <c r="J47" s="18"/>
       <c r="L47" s="12" t="s">
         <v>15</v>
       </c>
@@ -2543,14 +2550,14 @@
       </c>
     </row>
     <row r="48" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C48" s="20"/>
-      <c r="D48" s="18"/>
-      <c r="E48" s="18"/>
-      <c r="F48" s="19"/>
-      <c r="G48" s="21"/>
-      <c r="H48" s="21"/>
+      <c r="C48" s="18"/>
+      <c r="D48" s="19"/>
+      <c r="E48" s="19"/>
+      <c r="F48" s="23"/>
+      <c r="G48" s="24"/>
+      <c r="H48" s="24"/>
       <c r="I48" s="27"/>
-      <c r="J48" s="20"/>
+      <c r="J48" s="18"/>
       <c r="L48" s="14" t="s">
         <v>17</v>
       </c>
@@ -2573,14 +2580,14 @@
       <c r="U48" s="10"/>
     </row>
     <row r="49" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C49" s="20"/>
-      <c r="D49" s="18"/>
-      <c r="E49" s="18"/>
-      <c r="F49" s="19"/>
-      <c r="G49" s="21"/>
-      <c r="H49" s="21"/>
+      <c r="C49" s="18"/>
+      <c r="D49" s="19"/>
+      <c r="E49" s="19"/>
+      <c r="F49" s="23"/>
+      <c r="G49" s="24"/>
+      <c r="H49" s="24"/>
       <c r="I49" s="27"/>
-      <c r="J49" s="20"/>
+      <c r="J49" s="18"/>
       <c r="L49" s="15" t="s">
         <v>23</v>
       </c>
@@ -2597,24 +2604,24 @@
       <c r="U49" s="10"/>
     </row>
     <row r="50" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C50" s="20" t="s">
+      <c r="C50" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="D50" s="20"/>
-      <c r="E50" s="20"/>
-      <c r="F50" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="G50" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="H50" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="I50" s="18" t="s">
+      <c r="D50" s="18"/>
+      <c r="E50" s="18"/>
+      <c r="F50" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="G50" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="H50" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="I50" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="J50" s="19" t="s">
+      <c r="J50" s="23" t="s">
         <v>26</v>
       </c>
       <c r="L50" s="9" t="s">
@@ -2639,14 +2646,14 @@
       <c r="U50" s="10"/>
     </row>
     <row r="51" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C51" s="20"/>
-      <c r="D51" s="20"/>
-      <c r="E51" s="20"/>
-      <c r="F51" s="23"/>
-      <c r="G51" s="23"/>
-      <c r="H51" s="23"/>
-      <c r="I51" s="18"/>
-      <c r="J51" s="19"/>
+      <c r="C51" s="18"/>
+      <c r="D51" s="18"/>
+      <c r="E51" s="18"/>
+      <c r="F51" s="30"/>
+      <c r="G51" s="30"/>
+      <c r="H51" s="30"/>
+      <c r="I51" s="19"/>
+      <c r="J51" s="23"/>
       <c r="L51" s="11" t="s">
         <v>5</v>
       </c>
@@ -2682,14 +2689,14 @@
       </c>
     </row>
     <row r="52" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C52" s="20"/>
-      <c r="D52" s="20"/>
-      <c r="E52" s="20"/>
-      <c r="F52" s="23"/>
-      <c r="G52" s="23"/>
-      <c r="H52" s="23"/>
-      <c r="I52" s="18"/>
-      <c r="J52" s="19"/>
+      <c r="C52" s="18"/>
+      <c r="D52" s="18"/>
+      <c r="E52" s="18"/>
+      <c r="F52" s="30"/>
+      <c r="G52" s="30"/>
+      <c r="H52" s="30"/>
+      <c r="I52" s="19"/>
+      <c r="J52" s="23"/>
       <c r="L52" s="12" t="s">
         <v>15</v>
       </c>
@@ -2715,14 +2722,14 @@
       </c>
     </row>
     <row r="53" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C53" s="20"/>
-      <c r="D53" s="20"/>
-      <c r="E53" s="20"/>
-      <c r="F53" s="23"/>
-      <c r="G53" s="23"/>
-      <c r="H53" s="23"/>
-      <c r="I53" s="18"/>
-      <c r="J53" s="19"/>
+      <c r="C53" s="18"/>
+      <c r="D53" s="18"/>
+      <c r="E53" s="18"/>
+      <c r="F53" s="30"/>
+      <c r="G53" s="30"/>
+      <c r="H53" s="30"/>
+      <c r="I53" s="19"/>
+      <c r="J53" s="23"/>
       <c r="L53" s="14" t="s">
         <v>17</v>
       </c>
@@ -2745,14 +2752,14 @@
       <c r="U53" s="10"/>
     </row>
     <row r="54" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C54" s="20"/>
-      <c r="D54" s="20"/>
-      <c r="E54" s="20"/>
-      <c r="F54" s="24"/>
-      <c r="G54" s="24"/>
-      <c r="H54" s="24"/>
-      <c r="I54" s="18"/>
-      <c r="J54" s="19"/>
+      <c r="C54" s="18"/>
+      <c r="D54" s="18"/>
+      <c r="E54" s="18"/>
+      <c r="F54" s="31"/>
+      <c r="G54" s="31"/>
+      <c r="H54" s="31"/>
+      <c r="I54" s="19"/>
+      <c r="J54" s="23"/>
       <c r="L54" s="15" t="s">
         <v>23</v>
       </c>
@@ -2772,26 +2779,26 @@
       <c r="B55" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C55" s="20" t="s">
+      <c r="C55" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="D55" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="E55" s="21"/>
-      <c r="F55" s="18" t="s">
+      <c r="D55" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="E55" s="24"/>
+      <c r="F55" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="G55" s="18" t="s">
+      <c r="G55" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="H55" s="18" t="s">
+      <c r="H55" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="I55" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="J55" s="25" t="s">
+      <c r="I55" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="J55" s="28" t="s">
         <v>32</v>
       </c>
       <c r="L55" s="9" t="s">
@@ -2819,14 +2826,14 @@
       <c r="B56">
         <v>4</v>
       </c>
-      <c r="C56" s="20"/>
-      <c r="D56" s="21"/>
-      <c r="E56" s="21"/>
-      <c r="F56" s="18"/>
-      <c r="G56" s="18"/>
-      <c r="H56" s="18"/>
-      <c r="I56" s="19"/>
-      <c r="J56" s="25"/>
+      <c r="C56" s="18"/>
+      <c r="D56" s="24"/>
+      <c r="E56" s="24"/>
+      <c r="F56" s="19"/>
+      <c r="G56" s="19"/>
+      <c r="H56" s="19"/>
+      <c r="I56" s="23"/>
+      <c r="J56" s="28"/>
       <c r="L56" s="11" t="s">
         <v>5</v>
       </c>
@@ -2865,14 +2872,14 @@
       <c r="B57" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="C57" s="20"/>
-      <c r="D57" s="21"/>
-      <c r="E57" s="21"/>
-      <c r="F57" s="18"/>
-      <c r="G57" s="18"/>
-      <c r="H57" s="18"/>
-      <c r="I57" s="19"/>
-      <c r="J57" s="25"/>
+      <c r="C57" s="18"/>
+      <c r="D57" s="24"/>
+      <c r="E57" s="24"/>
+      <c r="F57" s="19"/>
+      <c r="G57" s="19"/>
+      <c r="H57" s="19"/>
+      <c r="I57" s="23"/>
+      <c r="J57" s="28"/>
       <c r="L57" s="12" t="s">
         <v>15</v>
       </c>
@@ -2901,14 +2908,14 @@
       <c r="B58">
         <v>1</v>
       </c>
-      <c r="C58" s="20"/>
-      <c r="D58" s="21"/>
-      <c r="E58" s="21"/>
-      <c r="F58" s="18"/>
-      <c r="G58" s="18"/>
-      <c r="H58" s="18"/>
-      <c r="I58" s="19"/>
-      <c r="J58" s="25"/>
+      <c r="C58" s="18"/>
+      <c r="D58" s="24"/>
+      <c r="E58" s="24"/>
+      <c r="F58" s="19"/>
+      <c r="G58" s="19"/>
+      <c r="H58" s="19"/>
+      <c r="I58" s="23"/>
+      <c r="J58" s="28"/>
       <c r="L58" s="14" t="s">
         <v>17</v>
       </c>
@@ -2933,14 +2940,14 @@
       <c r="U58" s="10"/>
     </row>
     <row r="59" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C59" s="20"/>
-      <c r="D59" s="21"/>
-      <c r="E59" s="21"/>
-      <c r="F59" s="18"/>
-      <c r="G59" s="18"/>
-      <c r="H59" s="18"/>
-      <c r="I59" s="19"/>
-      <c r="J59" s="25"/>
+      <c r="C59" s="18"/>
+      <c r="D59" s="24"/>
+      <c r="E59" s="24"/>
+      <c r="F59" s="19"/>
+      <c r="G59" s="19"/>
+      <c r="H59" s="19"/>
+      <c r="I59" s="23"/>
+      <c r="J59" s="28"/>
       <c r="L59" s="15" t="s">
         <v>23</v>
       </c>
@@ -2964,26 +2971,26 @@
       <c r="P60" s="10"/>
     </row>
     <row r="61" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C61" s="20" t="s">
+      <c r="C61" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="D61" s="18" t="s">
+      <c r="D61" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E61" s="21"/>
-      <c r="F61" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="G61" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="H61" s="20" t="s">
+      <c r="E61" s="24"/>
+      <c r="F61" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="G61" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="H61" s="18" t="s">
         <v>26</v>
       </c>
       <c r="I61" s="26" t="s">
         <v>49</v>
       </c>
-      <c r="J61" s="20"/>
+      <c r="J61" s="18"/>
       <c r="L61" s="9" t="s">
         <v>0</v>
       </c>
@@ -3006,14 +3013,14 @@
       <c r="U61" s="10"/>
     </row>
     <row r="62" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C62" s="20"/>
-      <c r="D62" s="18"/>
-      <c r="E62" s="21"/>
-      <c r="F62" s="20"/>
-      <c r="G62" s="19"/>
-      <c r="H62" s="20"/>
+      <c r="C62" s="18"/>
+      <c r="D62" s="19"/>
+      <c r="E62" s="24"/>
+      <c r="F62" s="18"/>
+      <c r="G62" s="23"/>
+      <c r="H62" s="18"/>
       <c r="I62" s="27"/>
-      <c r="J62" s="20"/>
+      <c r="J62" s="18"/>
       <c r="L62" s="11" t="s">
         <v>5</v>
       </c>
@@ -3052,14 +3059,14 @@
       <c r="A63">
         <v>10</v>
       </c>
-      <c r="C63" s="20"/>
-      <c r="D63" s="18"/>
-      <c r="E63" s="21"/>
-      <c r="F63" s="20"/>
-      <c r="G63" s="19"/>
-      <c r="H63" s="20"/>
+      <c r="C63" s="18"/>
+      <c r="D63" s="19"/>
+      <c r="E63" s="24"/>
+      <c r="F63" s="18"/>
+      <c r="G63" s="23"/>
+      <c r="H63" s="18"/>
       <c r="I63" s="27"/>
-      <c r="J63" s="20"/>
+      <c r="J63" s="18"/>
       <c r="L63" s="12" t="s">
         <v>15</v>
       </c>
@@ -3085,14 +3092,14 @@
       </c>
     </row>
     <row r="64" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C64" s="20"/>
-      <c r="D64" s="18"/>
-      <c r="E64" s="21"/>
-      <c r="F64" s="20"/>
-      <c r="G64" s="19"/>
-      <c r="H64" s="20"/>
+      <c r="C64" s="18"/>
+      <c r="D64" s="19"/>
+      <c r="E64" s="24"/>
+      <c r="F64" s="18"/>
+      <c r="G64" s="23"/>
+      <c r="H64" s="18"/>
       <c r="I64" s="27"/>
-      <c r="J64" s="20"/>
+      <c r="J64" s="18"/>
       <c r="L64" s="14" t="s">
         <v>17</v>
       </c>
@@ -3115,14 +3122,14 @@
       <c r="U64" s="10"/>
     </row>
     <row r="65" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C65" s="20"/>
-      <c r="D65" s="18"/>
-      <c r="E65" s="21"/>
-      <c r="F65" s="20"/>
-      <c r="G65" s="19"/>
-      <c r="H65" s="20"/>
+      <c r="C65" s="18"/>
+      <c r="D65" s="19"/>
+      <c r="E65" s="24"/>
+      <c r="F65" s="18"/>
+      <c r="G65" s="23"/>
+      <c r="H65" s="18"/>
       <c r="I65" s="27"/>
-      <c r="J65" s="20"/>
+      <c r="J65" s="18"/>
       <c r="L65" s="15" t="s">
         <v>23</v>
       </c>
@@ -3139,24 +3146,24 @@
       <c r="U65" s="10"/>
     </row>
     <row r="66" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C66" s="20" t="s">
+      <c r="C66" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="D66" s="20"/>
-      <c r="E66" s="20"/>
-      <c r="F66" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="G66" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="H66" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="I66" s="18" t="s">
+      <c r="D66" s="18"/>
+      <c r="E66" s="18"/>
+      <c r="F66" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="G66" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="H66" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="I66" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="J66" s="19" t="s">
+      <c r="J66" s="23" t="s">
         <v>26</v>
       </c>
       <c r="L66" s="9" t="s">
@@ -3181,14 +3188,14 @@
       <c r="U66" s="10"/>
     </row>
     <row r="67" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C67" s="20"/>
-      <c r="D67" s="20"/>
-      <c r="E67" s="20"/>
-      <c r="F67" s="20"/>
-      <c r="G67" s="20"/>
-      <c r="H67" s="20"/>
-      <c r="I67" s="18"/>
-      <c r="J67" s="19"/>
+      <c r="C67" s="18"/>
+      <c r="D67" s="18"/>
+      <c r="E67" s="18"/>
+      <c r="F67" s="18"/>
+      <c r="G67" s="18"/>
+      <c r="H67" s="18"/>
+      <c r="I67" s="19"/>
+      <c r="J67" s="23"/>
       <c r="L67" s="11" t="s">
         <v>5</v>
       </c>
@@ -3224,14 +3231,14 @@
       </c>
     </row>
     <row r="68" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C68" s="20"/>
-      <c r="D68" s="20"/>
-      <c r="E68" s="20"/>
-      <c r="F68" s="20"/>
-      <c r="G68" s="20"/>
-      <c r="H68" s="20"/>
-      <c r="I68" s="18"/>
-      <c r="J68" s="19"/>
+      <c r="C68" s="18"/>
+      <c r="D68" s="18"/>
+      <c r="E68" s="18"/>
+      <c r="F68" s="18"/>
+      <c r="G68" s="18"/>
+      <c r="H68" s="18"/>
+      <c r="I68" s="19"/>
+      <c r="J68" s="23"/>
       <c r="L68" s="12" t="s">
         <v>15</v>
       </c>
@@ -3257,14 +3264,14 @@
       </c>
     </row>
     <row r="69" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C69" s="20"/>
-      <c r="D69" s="20"/>
-      <c r="E69" s="20"/>
-      <c r="F69" s="20"/>
-      <c r="G69" s="20"/>
-      <c r="H69" s="20"/>
-      <c r="I69" s="18"/>
-      <c r="J69" s="19"/>
+      <c r="C69" s="18"/>
+      <c r="D69" s="18"/>
+      <c r="E69" s="18"/>
+      <c r="F69" s="18"/>
+      <c r="G69" s="18"/>
+      <c r="H69" s="18"/>
+      <c r="I69" s="19"/>
+      <c r="J69" s="23"/>
       <c r="L69" s="14" t="s">
         <v>17</v>
       </c>
@@ -3287,14 +3294,14 @@
       <c r="U69" s="10"/>
     </row>
     <row r="70" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C70" s="20"/>
-      <c r="D70" s="20"/>
-      <c r="E70" s="20"/>
-      <c r="F70" s="20"/>
-      <c r="G70" s="20"/>
-      <c r="H70" s="20"/>
-      <c r="I70" s="18"/>
-      <c r="J70" s="19"/>
+      <c r="C70" s="18"/>
+      <c r="D70" s="18"/>
+      <c r="E70" s="18"/>
+      <c r="F70" s="18"/>
+      <c r="G70" s="18"/>
+      <c r="H70" s="18"/>
+      <c r="I70" s="19"/>
+      <c r="J70" s="23"/>
       <c r="L70" s="15" t="s">
         <v>23</v>
       </c>
@@ -3314,26 +3321,26 @@
       <c r="B71" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C71" s="20" t="s">
+      <c r="C71" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="D71" s="20"/>
-      <c r="E71" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="F71" s="18" t="s">
+      <c r="D71" s="18"/>
+      <c r="E71" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="F71" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="G71" s="18" t="s">
+      <c r="G71" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="H71" s="18" t="s">
+      <c r="H71" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="I71" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="J71" s="25" t="s">
+      <c r="I71" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="J71" s="28" t="s">
         <v>32</v>
       </c>
       <c r="L71" s="9" t="s">
@@ -3361,14 +3368,14 @@
       <c r="B72">
         <v>5</v>
       </c>
-      <c r="C72" s="20"/>
-      <c r="D72" s="20"/>
-      <c r="E72" s="21"/>
-      <c r="F72" s="18"/>
-      <c r="G72" s="18"/>
-      <c r="H72" s="18"/>
-      <c r="I72" s="19"/>
-      <c r="J72" s="25"/>
+      <c r="C72" s="18"/>
+      <c r="D72" s="18"/>
+      <c r="E72" s="24"/>
+      <c r="F72" s="19"/>
+      <c r="G72" s="19"/>
+      <c r="H72" s="19"/>
+      <c r="I72" s="23"/>
+      <c r="J72" s="28"/>
       <c r="L72" s="11" t="s">
         <v>5</v>
       </c>
@@ -3407,14 +3414,14 @@
       <c r="B73" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="C73" s="20"/>
-      <c r="D73" s="20"/>
-      <c r="E73" s="21"/>
-      <c r="F73" s="18"/>
-      <c r="G73" s="18"/>
-      <c r="H73" s="18"/>
-      <c r="I73" s="19"/>
-      <c r="J73" s="25"/>
+      <c r="C73" s="18"/>
+      <c r="D73" s="18"/>
+      <c r="E73" s="24"/>
+      <c r="F73" s="19"/>
+      <c r="G73" s="19"/>
+      <c r="H73" s="19"/>
+      <c r="I73" s="23"/>
+      <c r="J73" s="28"/>
       <c r="L73" s="12" t="s">
         <v>15</v>
       </c>
@@ -3443,14 +3450,14 @@
       <c r="B74">
         <v>2</v>
       </c>
-      <c r="C74" s="20"/>
-      <c r="D74" s="20"/>
-      <c r="E74" s="21"/>
-      <c r="F74" s="18"/>
-      <c r="G74" s="18"/>
-      <c r="H74" s="18"/>
-      <c r="I74" s="19"/>
-      <c r="J74" s="25"/>
+      <c r="C74" s="18"/>
+      <c r="D74" s="18"/>
+      <c r="E74" s="24"/>
+      <c r="F74" s="19"/>
+      <c r="G74" s="19"/>
+      <c r="H74" s="19"/>
+      <c r="I74" s="23"/>
+      <c r="J74" s="28"/>
       <c r="L74" s="14" t="s">
         <v>17</v>
       </c>
@@ -3475,14 +3482,14 @@
       <c r="U74" s="10"/>
     </row>
     <row r="75" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C75" s="20"/>
-      <c r="D75" s="20"/>
-      <c r="E75" s="21"/>
-      <c r="F75" s="18"/>
-      <c r="G75" s="18"/>
-      <c r="H75" s="18"/>
-      <c r="I75" s="19"/>
-      <c r="J75" s="25"/>
+      <c r="C75" s="18"/>
+      <c r="D75" s="18"/>
+      <c r="E75" s="24"/>
+      <c r="F75" s="19"/>
+      <c r="G75" s="19"/>
+      <c r="H75" s="19"/>
+      <c r="I75" s="23"/>
+      <c r="J75" s="28"/>
       <c r="L75" s="15" t="s">
         <v>23</v>
       </c>
@@ -3506,26 +3513,26 @@
       <c r="P76" s="10"/>
     </row>
     <row r="77" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C77" s="20" t="s">
+      <c r="C77" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="D77" s="18"/>
-      <c r="E77" s="18" t="s">
+      <c r="D77" s="19"/>
+      <c r="E77" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="F77" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="G77" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="H77" s="19" t="s">
+      <c r="F77" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="G77" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="H77" s="23" t="s">
         <v>26</v>
       </c>
       <c r="I77" s="26" t="s">
         <v>49</v>
       </c>
-      <c r="J77" s="20"/>
+      <c r="J77" s="18"/>
       <c r="L77" s="9" t="s">
         <v>0</v>
       </c>
@@ -3548,14 +3555,14 @@
       <c r="U77" s="10"/>
     </row>
     <row r="78" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C78" s="20"/>
-      <c r="D78" s="18"/>
-      <c r="E78" s="18"/>
-      <c r="F78" s="20"/>
-      <c r="G78" s="20"/>
-      <c r="H78" s="19"/>
+      <c r="C78" s="18"/>
+      <c r="D78" s="19"/>
+      <c r="E78" s="19"/>
+      <c r="F78" s="18"/>
+      <c r="G78" s="18"/>
+      <c r="H78" s="23"/>
       <c r="I78" s="27"/>
-      <c r="J78" s="20"/>
+      <c r="J78" s="18"/>
       <c r="L78" s="11" t="s">
         <v>5</v>
       </c>
@@ -3591,14 +3598,14 @@
       </c>
     </row>
     <row r="79" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C79" s="20"/>
-      <c r="D79" s="18"/>
-      <c r="E79" s="18"/>
-      <c r="F79" s="20"/>
-      <c r="G79" s="20"/>
-      <c r="H79" s="19"/>
+      <c r="C79" s="18"/>
+      <c r="D79" s="19"/>
+      <c r="E79" s="19"/>
+      <c r="F79" s="18"/>
+      <c r="G79" s="18"/>
+      <c r="H79" s="23"/>
       <c r="I79" s="27"/>
-      <c r="J79" s="20"/>
+      <c r="J79" s="18"/>
       <c r="L79" s="12" t="s">
         <v>15</v>
       </c>
@@ -3624,14 +3631,14 @@
       </c>
     </row>
     <row r="80" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C80" s="20"/>
-      <c r="D80" s="18"/>
-      <c r="E80" s="18"/>
-      <c r="F80" s="20"/>
-      <c r="G80" s="20"/>
-      <c r="H80" s="19"/>
+      <c r="C80" s="18"/>
+      <c r="D80" s="19"/>
+      <c r="E80" s="19"/>
+      <c r="F80" s="18"/>
+      <c r="G80" s="18"/>
+      <c r="H80" s="23"/>
       <c r="I80" s="27"/>
-      <c r="J80" s="20"/>
+      <c r="J80" s="18"/>
       <c r="L80" s="14" t="s">
         <v>17</v>
       </c>
@@ -3654,14 +3661,14 @@
       <c r="U80" s="10"/>
     </row>
     <row r="81" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C81" s="20"/>
-      <c r="D81" s="18"/>
-      <c r="E81" s="18"/>
-      <c r="F81" s="20"/>
-      <c r="G81" s="20"/>
-      <c r="H81" s="19"/>
+      <c r="C81" s="18"/>
+      <c r="D81" s="19"/>
+      <c r="E81" s="19"/>
+      <c r="F81" s="18"/>
+      <c r="G81" s="18"/>
+      <c r="H81" s="23"/>
       <c r="I81" s="27"/>
-      <c r="J81" s="20"/>
+      <c r="J81" s="18"/>
       <c r="L81" s="15" t="s">
         <v>23</v>
       </c>
@@ -3678,24 +3685,24 @@
       <c r="U81" s="10"/>
     </row>
     <row r="82" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C82" s="20" t="s">
+      <c r="C82" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="D82" s="20"/>
-      <c r="E82" s="20"/>
-      <c r="F82" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="G82" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="H82" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="I82" s="18" t="s">
+      <c r="D82" s="18"/>
+      <c r="E82" s="18"/>
+      <c r="F82" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="G82" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="H82" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="I82" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="J82" s="19" t="s">
+      <c r="J82" s="23" t="s">
         <v>26</v>
       </c>
       <c r="L82" s="9" t="s">
@@ -3720,14 +3727,14 @@
       <c r="U82" s="10"/>
     </row>
     <row r="83" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C83" s="20"/>
-      <c r="D83" s="20"/>
-      <c r="E83" s="20"/>
-      <c r="F83" s="20"/>
-      <c r="G83" s="20"/>
-      <c r="H83" s="20"/>
-      <c r="I83" s="18"/>
-      <c r="J83" s="19"/>
+      <c r="C83" s="18"/>
+      <c r="D83" s="18"/>
+      <c r="E83" s="18"/>
+      <c r="F83" s="18"/>
+      <c r="G83" s="18"/>
+      <c r="H83" s="18"/>
+      <c r="I83" s="19"/>
+      <c r="J83" s="23"/>
       <c r="L83" s="11" t="s">
         <v>5</v>
       </c>
@@ -3763,14 +3770,14 @@
       </c>
     </row>
     <row r="84" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C84" s="20"/>
-      <c r="D84" s="20"/>
-      <c r="E84" s="20"/>
-      <c r="F84" s="20"/>
-      <c r="G84" s="20"/>
-      <c r="H84" s="20"/>
-      <c r="I84" s="18"/>
-      <c r="J84" s="19"/>
+      <c r="C84" s="18"/>
+      <c r="D84" s="18"/>
+      <c r="E84" s="18"/>
+      <c r="F84" s="18"/>
+      <c r="G84" s="18"/>
+      <c r="H84" s="18"/>
+      <c r="I84" s="19"/>
+      <c r="J84" s="23"/>
       <c r="L84" s="12" t="s">
         <v>15</v>
       </c>
@@ -3796,14 +3803,14 @@
       </c>
     </row>
     <row r="85" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C85" s="20"/>
-      <c r="D85" s="20"/>
-      <c r="E85" s="20"/>
-      <c r="F85" s="20"/>
-      <c r="G85" s="20"/>
-      <c r="H85" s="20"/>
-      <c r="I85" s="18"/>
-      <c r="J85" s="19"/>
+      <c r="C85" s="18"/>
+      <c r="D85" s="18"/>
+      <c r="E85" s="18"/>
+      <c r="F85" s="18"/>
+      <c r="G85" s="18"/>
+      <c r="H85" s="18"/>
+      <c r="I85" s="19"/>
+      <c r="J85" s="23"/>
       <c r="L85" s="14" t="s">
         <v>17</v>
       </c>
@@ -3826,14 +3833,14 @@
       <c r="U85" s="10"/>
     </row>
     <row r="86" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C86" s="20"/>
-      <c r="D86" s="20"/>
-      <c r="E86" s="20"/>
-      <c r="F86" s="20"/>
-      <c r="G86" s="20"/>
-      <c r="H86" s="20"/>
-      <c r="I86" s="18"/>
-      <c r="J86" s="19"/>
+      <c r="C86" s="18"/>
+      <c r="D86" s="18"/>
+      <c r="E86" s="18"/>
+      <c r="F86" s="18"/>
+      <c r="G86" s="18"/>
+      <c r="H86" s="18"/>
+      <c r="I86" s="19"/>
+      <c r="J86" s="23"/>
       <c r="L86" s="15" t="s">
         <v>23</v>
       </c>
@@ -3853,26 +3860,26 @@
       <c r="B87" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C87" s="20" t="s">
+      <c r="C87" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="D87" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="E87" s="21"/>
-      <c r="F87" s="18" t="s">
+      <c r="D87" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="E87" s="24"/>
+      <c r="F87" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="G87" s="18" t="s">
+      <c r="G87" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="H87" s="18" t="s">
+      <c r="H87" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="I87" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="J87" s="25" t="s">
+      <c r="I87" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="J87" s="28" t="s">
         <v>32</v>
       </c>
       <c r="L87" s="9" t="s">
@@ -3900,14 +3907,14 @@
       <c r="B88">
         <v>6</v>
       </c>
-      <c r="C88" s="20"/>
-      <c r="D88" s="21"/>
-      <c r="E88" s="21"/>
-      <c r="F88" s="18"/>
-      <c r="G88" s="18"/>
-      <c r="H88" s="18"/>
-      <c r="I88" s="19"/>
-      <c r="J88" s="25"/>
+      <c r="C88" s="18"/>
+      <c r="D88" s="24"/>
+      <c r="E88" s="24"/>
+      <c r="F88" s="19"/>
+      <c r="G88" s="19"/>
+      <c r="H88" s="19"/>
+      <c r="I88" s="23"/>
+      <c r="J88" s="28"/>
       <c r="L88" s="11" t="s">
         <v>5</v>
       </c>
@@ -3949,14 +3956,14 @@
       <c r="B89" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="C89" s="20"/>
-      <c r="D89" s="21"/>
-      <c r="E89" s="21"/>
-      <c r="F89" s="18"/>
-      <c r="G89" s="18"/>
-      <c r="H89" s="18"/>
-      <c r="I89" s="19"/>
-      <c r="J89" s="25"/>
+      <c r="C89" s="18"/>
+      <c r="D89" s="24"/>
+      <c r="E89" s="24"/>
+      <c r="F89" s="19"/>
+      <c r="G89" s="19"/>
+      <c r="H89" s="19"/>
+      <c r="I89" s="23"/>
+      <c r="J89" s="28"/>
       <c r="L89" s="12" t="s">
         <v>15</v>
       </c>
@@ -3985,14 +3992,14 @@
       <c r="B90">
         <v>3</v>
       </c>
-      <c r="C90" s="20"/>
-      <c r="D90" s="21"/>
-      <c r="E90" s="21"/>
-      <c r="F90" s="18"/>
-      <c r="G90" s="18"/>
-      <c r="H90" s="18"/>
-      <c r="I90" s="19"/>
-      <c r="J90" s="25"/>
+      <c r="C90" s="18"/>
+      <c r="D90" s="24"/>
+      <c r="E90" s="24"/>
+      <c r="F90" s="19"/>
+      <c r="G90" s="19"/>
+      <c r="H90" s="19"/>
+      <c r="I90" s="23"/>
+      <c r="J90" s="28"/>
       <c r="L90" s="14" t="s">
         <v>17</v>
       </c>
@@ -4017,14 +4024,14 @@
       <c r="U90" s="10"/>
     </row>
     <row r="91" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C91" s="20"/>
-      <c r="D91" s="21"/>
-      <c r="E91" s="21"/>
-      <c r="F91" s="18"/>
-      <c r="G91" s="18"/>
-      <c r="H91" s="18"/>
-      <c r="I91" s="19"/>
-      <c r="J91" s="25"/>
+      <c r="C91" s="18"/>
+      <c r="D91" s="24"/>
+      <c r="E91" s="24"/>
+      <c r="F91" s="19"/>
+      <c r="G91" s="19"/>
+      <c r="H91" s="19"/>
+      <c r="I91" s="23"/>
+      <c r="J91" s="28"/>
       <c r="L91" s="15" t="s">
         <v>23</v>
       </c>
@@ -4054,26 +4061,26 @@
       <c r="A94" t="s">
         <v>64</v>
       </c>
-      <c r="C94" s="20" t="s">
+      <c r="C94" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="D94" s="18" t="s">
+      <c r="D94" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E94" s="21"/>
-      <c r="F94" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="G94" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="H94" s="20" t="s">
+      <c r="E94" s="24"/>
+      <c r="F94" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="G94" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="H94" s="18" t="s">
         <v>26</v>
       </c>
       <c r="I94" s="26" t="s">
         <v>49</v>
       </c>
-      <c r="J94" s="20"/>
+      <c r="J94" s="18"/>
       <c r="L94" s="9" t="s">
         <v>0</v>
       </c>
@@ -4096,14 +4103,14 @@
       <c r="U94" s="10"/>
     </row>
     <row r="95" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C95" s="20"/>
-      <c r="D95" s="18"/>
-      <c r="E95" s="21"/>
-      <c r="F95" s="19"/>
-      <c r="G95" s="20"/>
-      <c r="H95" s="20"/>
+      <c r="C95" s="18"/>
+      <c r="D95" s="19"/>
+      <c r="E95" s="24"/>
+      <c r="F95" s="23"/>
+      <c r="G95" s="18"/>
+      <c r="H95" s="18"/>
       <c r="I95" s="27"/>
-      <c r="J95" s="20"/>
+      <c r="J95" s="18"/>
       <c r="L95" s="11" t="s">
         <v>5</v>
       </c>
@@ -4139,14 +4146,14 @@
       </c>
     </row>
     <row r="96" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C96" s="20"/>
-      <c r="D96" s="18"/>
-      <c r="E96" s="21"/>
-      <c r="F96" s="19"/>
-      <c r="G96" s="20"/>
-      <c r="H96" s="20"/>
+      <c r="C96" s="18"/>
+      <c r="D96" s="19"/>
+      <c r="E96" s="24"/>
+      <c r="F96" s="23"/>
+      <c r="G96" s="18"/>
+      <c r="H96" s="18"/>
       <c r="I96" s="27"/>
-      <c r="J96" s="20"/>
+      <c r="J96" s="18"/>
       <c r="L96" s="12" t="s">
         <v>15</v>
       </c>
@@ -4172,14 +4179,14 @@
       </c>
     </row>
     <row r="97" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C97" s="20"/>
-      <c r="D97" s="18"/>
-      <c r="E97" s="21"/>
-      <c r="F97" s="19"/>
-      <c r="G97" s="20"/>
-      <c r="H97" s="20"/>
+      <c r="C97" s="18"/>
+      <c r="D97" s="19"/>
+      <c r="E97" s="24"/>
+      <c r="F97" s="23"/>
+      <c r="G97" s="18"/>
+      <c r="H97" s="18"/>
       <c r="I97" s="27"/>
-      <c r="J97" s="20"/>
+      <c r="J97" s="18"/>
       <c r="L97" s="14" t="s">
         <v>17</v>
       </c>
@@ -4202,14 +4209,14 @@
       <c r="U97" s="10"/>
     </row>
     <row r="98" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C98" s="20"/>
-      <c r="D98" s="18"/>
-      <c r="E98" s="21"/>
-      <c r="F98" s="19"/>
-      <c r="G98" s="20"/>
-      <c r="H98" s="20"/>
+      <c r="C98" s="18"/>
+      <c r="D98" s="19"/>
+      <c r="E98" s="24"/>
+      <c r="F98" s="23"/>
+      <c r="G98" s="18"/>
+      <c r="H98" s="18"/>
       <c r="I98" s="27"/>
-      <c r="J98" s="20"/>
+      <c r="J98" s="18"/>
       <c r="L98" s="15" t="s">
         <v>23</v>
       </c>
@@ -4226,24 +4233,24 @@
       <c r="U98" s="10"/>
     </row>
     <row r="99" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C99" s="20" t="s">
+      <c r="C99" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="D99" s="20"/>
-      <c r="E99" s="20"/>
-      <c r="F99" s="28" t="s">
-        <v>26</v>
-      </c>
-      <c r="G99" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="H99" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="I99" s="18" t="s">
+      <c r="D99" s="18"/>
+      <c r="E99" s="18"/>
+      <c r="F99" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="G99" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="H99" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="I99" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="J99" s="19" t="s">
+      <c r="J99" s="23" t="s">
         <v>26</v>
       </c>
       <c r="L99" s="9" t="s">
@@ -4268,14 +4275,14 @@
       <c r="U99" s="10"/>
     </row>
     <row r="100" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C100" s="20"/>
-      <c r="D100" s="20"/>
-      <c r="E100" s="20"/>
-      <c r="F100" s="21"/>
-      <c r="G100" s="20"/>
-      <c r="H100" s="20"/>
-      <c r="I100" s="18"/>
-      <c r="J100" s="19"/>
+      <c r="C100" s="18"/>
+      <c r="D100" s="18"/>
+      <c r="E100" s="18"/>
+      <c r="F100" s="24"/>
+      <c r="G100" s="18"/>
+      <c r="H100" s="18"/>
+      <c r="I100" s="19"/>
+      <c r="J100" s="23"/>
       <c r="L100" s="11" t="s">
         <v>5</v>
       </c>
@@ -4311,14 +4318,14 @@
       </c>
     </row>
     <row r="101" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C101" s="20"/>
-      <c r="D101" s="20"/>
-      <c r="E101" s="20"/>
-      <c r="F101" s="21"/>
-      <c r="G101" s="20"/>
-      <c r="H101" s="20"/>
-      <c r="I101" s="18"/>
-      <c r="J101" s="19"/>
+      <c r="C101" s="18"/>
+      <c r="D101" s="18"/>
+      <c r="E101" s="18"/>
+      <c r="F101" s="24"/>
+      <c r="G101" s="18"/>
+      <c r="H101" s="18"/>
+      <c r="I101" s="19"/>
+      <c r="J101" s="23"/>
       <c r="L101" s="12" t="s">
         <v>15</v>
       </c>
@@ -4344,14 +4351,14 @@
       </c>
     </row>
     <row r="102" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C102" s="20"/>
-      <c r="D102" s="20"/>
-      <c r="E102" s="20"/>
-      <c r="F102" s="21"/>
-      <c r="G102" s="20"/>
-      <c r="H102" s="20"/>
-      <c r="I102" s="18"/>
-      <c r="J102" s="19"/>
+      <c r="C102" s="18"/>
+      <c r="D102" s="18"/>
+      <c r="E102" s="18"/>
+      <c r="F102" s="24"/>
+      <c r="G102" s="18"/>
+      <c r="H102" s="18"/>
+      <c r="I102" s="19"/>
+      <c r="J102" s="23"/>
       <c r="L102" s="14" t="s">
         <v>17</v>
       </c>
@@ -4374,14 +4381,14 @@
       <c r="U102" s="10"/>
     </row>
     <row r="103" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C103" s="20"/>
-      <c r="D103" s="20"/>
-      <c r="E103" s="20"/>
-      <c r="F103" s="21"/>
-      <c r="G103" s="20"/>
-      <c r="H103" s="20"/>
-      <c r="I103" s="18"/>
-      <c r="J103" s="19"/>
+      <c r="C103" s="18"/>
+      <c r="D103" s="18"/>
+      <c r="E103" s="18"/>
+      <c r="F103" s="24"/>
+      <c r="G103" s="18"/>
+      <c r="H103" s="18"/>
+      <c r="I103" s="19"/>
+      <c r="J103" s="23"/>
       <c r="L103" s="15" t="s">
         <v>23</v>
       </c>
@@ -4401,26 +4408,26 @@
       <c r="B104" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C104" s="20" t="s">
+      <c r="C104" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="D104" s="20"/>
-      <c r="E104" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="F104" s="18" t="s">
+      <c r="D104" s="18"/>
+      <c r="E104" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="F104" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="G104" s="18" t="s">
+      <c r="G104" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="H104" s="18" t="s">
+      <c r="H104" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="I104" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="J104" s="25" t="s">
+      <c r="I104" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="J104" s="28" t="s">
         <v>32</v>
       </c>
       <c r="L104" s="9" t="s">
@@ -4448,14 +4455,14 @@
       <c r="B105">
         <v>7</v>
       </c>
-      <c r="C105" s="20"/>
-      <c r="D105" s="20"/>
-      <c r="E105" s="21"/>
-      <c r="F105" s="18"/>
-      <c r="G105" s="18"/>
-      <c r="H105" s="18"/>
-      <c r="I105" s="19"/>
-      <c r="J105" s="25"/>
+      <c r="C105" s="18"/>
+      <c r="D105" s="18"/>
+      <c r="E105" s="24"/>
+      <c r="F105" s="19"/>
+      <c r="G105" s="19"/>
+      <c r="H105" s="19"/>
+      <c r="I105" s="23"/>
+      <c r="J105" s="28"/>
       <c r="L105" s="11" t="s">
         <v>5</v>
       </c>
@@ -4494,14 +4501,14 @@
       <c r="B106" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="C106" s="20"/>
-      <c r="D106" s="20"/>
-      <c r="E106" s="21"/>
-      <c r="F106" s="18"/>
-      <c r="G106" s="18"/>
-      <c r="H106" s="18"/>
-      <c r="I106" s="19"/>
-      <c r="J106" s="25"/>
+      <c r="C106" s="18"/>
+      <c r="D106" s="18"/>
+      <c r="E106" s="24"/>
+      <c r="F106" s="19"/>
+      <c r="G106" s="19"/>
+      <c r="H106" s="19"/>
+      <c r="I106" s="23"/>
+      <c r="J106" s="28"/>
       <c r="L106" s="12" t="s">
         <v>15</v>
       </c>
@@ -4530,14 +4537,14 @@
       <c r="B107">
         <v>4</v>
       </c>
-      <c r="C107" s="20"/>
-      <c r="D107" s="20"/>
-      <c r="E107" s="21"/>
-      <c r="F107" s="18"/>
-      <c r="G107" s="18"/>
-      <c r="H107" s="18"/>
-      <c r="I107" s="19"/>
-      <c r="J107" s="25"/>
+      <c r="C107" s="18"/>
+      <c r="D107" s="18"/>
+      <c r="E107" s="24"/>
+      <c r="F107" s="19"/>
+      <c r="G107" s="19"/>
+      <c r="H107" s="19"/>
+      <c r="I107" s="23"/>
+      <c r="J107" s="28"/>
       <c r="L107" s="14" t="s">
         <v>17</v>
       </c>
@@ -4562,14 +4569,14 @@
       <c r="U107" s="10"/>
     </row>
     <row r="108" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C108" s="20"/>
-      <c r="D108" s="20"/>
-      <c r="E108" s="21"/>
-      <c r="F108" s="18"/>
-      <c r="G108" s="18"/>
-      <c r="H108" s="18"/>
-      <c r="I108" s="19"/>
-      <c r="J108" s="25"/>
+      <c r="C108" s="18"/>
+      <c r="D108" s="18"/>
+      <c r="E108" s="24"/>
+      <c r="F108" s="19"/>
+      <c r="G108" s="19"/>
+      <c r="H108" s="19"/>
+      <c r="I108" s="23"/>
+      <c r="J108" s="28"/>
       <c r="L108" s="15" t="s">
         <v>23</v>
       </c>
@@ -4593,26 +4600,26 @@
       <c r="P109" s="10"/>
     </row>
     <row r="110" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C110" s="20" t="s">
+      <c r="C110" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="D110" s="18"/>
-      <c r="E110" s="18" t="s">
+      <c r="D110" s="19"/>
+      <c r="E110" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="F110" s="28" t="s">
-        <v>26</v>
-      </c>
-      <c r="G110" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="H110" s="28" t="s">
+      <c r="F110" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="G110" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="H110" s="25" t="s">
         <v>26</v>
       </c>
       <c r="I110" s="26" t="s">
         <v>49</v>
       </c>
-      <c r="J110" s="20"/>
+      <c r="J110" s="18"/>
       <c r="L110" s="9" t="s">
         <v>0</v>
       </c>
@@ -4635,14 +4642,14 @@
       <c r="U110" s="10"/>
     </row>
     <row r="111" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C111" s="20"/>
-      <c r="D111" s="18"/>
-      <c r="E111" s="18"/>
-      <c r="F111" s="21"/>
-      <c r="G111" s="19"/>
-      <c r="H111" s="21"/>
+      <c r="C111" s="18"/>
+      <c r="D111" s="19"/>
+      <c r="E111" s="19"/>
+      <c r="F111" s="24"/>
+      <c r="G111" s="23"/>
+      <c r="H111" s="24"/>
       <c r="I111" s="27"/>
-      <c r="J111" s="20"/>
+      <c r="J111" s="18"/>
       <c r="L111" s="11" t="s">
         <v>5</v>
       </c>
@@ -4678,14 +4685,14 @@
       </c>
     </row>
     <row r="112" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C112" s="20"/>
-      <c r="D112" s="18"/>
-      <c r="E112" s="18"/>
-      <c r="F112" s="21"/>
-      <c r="G112" s="19"/>
-      <c r="H112" s="21"/>
+      <c r="C112" s="18"/>
+      <c r="D112" s="19"/>
+      <c r="E112" s="19"/>
+      <c r="F112" s="24"/>
+      <c r="G112" s="23"/>
+      <c r="H112" s="24"/>
       <c r="I112" s="27"/>
-      <c r="J112" s="20"/>
+      <c r="J112" s="18"/>
       <c r="L112" s="12" t="s">
         <v>15</v>
       </c>
@@ -4711,14 +4718,14 @@
       </c>
     </row>
     <row r="113" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C113" s="20"/>
-      <c r="D113" s="18"/>
-      <c r="E113" s="18"/>
-      <c r="F113" s="21"/>
-      <c r="G113" s="19"/>
-      <c r="H113" s="21"/>
+      <c r="C113" s="18"/>
+      <c r="D113" s="19"/>
+      <c r="E113" s="19"/>
+      <c r="F113" s="24"/>
+      <c r="G113" s="23"/>
+      <c r="H113" s="24"/>
       <c r="I113" s="27"/>
-      <c r="J113" s="20"/>
+      <c r="J113" s="18"/>
       <c r="L113" s="14" t="s">
         <v>17</v>
       </c>
@@ -4741,14 +4748,14 @@
       <c r="U113" s="10"/>
     </row>
     <row r="114" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C114" s="20"/>
-      <c r="D114" s="18"/>
-      <c r="E114" s="18"/>
-      <c r="F114" s="21"/>
-      <c r="G114" s="19"/>
-      <c r="H114" s="21"/>
+      <c r="C114" s="18"/>
+      <c r="D114" s="19"/>
+      <c r="E114" s="19"/>
+      <c r="F114" s="24"/>
+      <c r="G114" s="23"/>
+      <c r="H114" s="24"/>
       <c r="I114" s="27"/>
-      <c r="J114" s="20"/>
+      <c r="J114" s="18"/>
       <c r="L114" s="15" t="s">
         <v>23</v>
       </c>
@@ -4765,24 +4772,24 @@
       <c r="U114" s="10"/>
     </row>
     <row r="115" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C115" s="20" t="s">
+      <c r="C115" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="D115" s="20"/>
-      <c r="E115" s="20"/>
-      <c r="F115" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="G115" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="H115" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="I115" s="18" t="s">
+      <c r="D115" s="18"/>
+      <c r="E115" s="18"/>
+      <c r="F115" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="G115" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="H115" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="I115" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="J115" s="19" t="s">
+      <c r="J115" s="23" t="s">
         <v>26</v>
       </c>
       <c r="L115" s="9" t="s">
@@ -4807,14 +4814,14 @@
       <c r="U115" s="10"/>
     </row>
     <row r="116" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C116" s="20"/>
-      <c r="D116" s="20"/>
-      <c r="E116" s="20"/>
-      <c r="F116" s="23"/>
-      <c r="G116" s="23"/>
-      <c r="H116" s="23"/>
-      <c r="I116" s="18"/>
-      <c r="J116" s="19"/>
+      <c r="C116" s="18"/>
+      <c r="D116" s="18"/>
+      <c r="E116" s="18"/>
+      <c r="F116" s="30"/>
+      <c r="G116" s="30"/>
+      <c r="H116" s="30"/>
+      <c r="I116" s="19"/>
+      <c r="J116" s="23"/>
       <c r="L116" s="11" t="s">
         <v>5</v>
       </c>
@@ -4853,14 +4860,14 @@
       <c r="A117">
         <v>20</v>
       </c>
-      <c r="C117" s="20"/>
-      <c r="D117" s="20"/>
-      <c r="E117" s="20"/>
-      <c r="F117" s="23"/>
-      <c r="G117" s="23"/>
-      <c r="H117" s="23"/>
-      <c r="I117" s="18"/>
-      <c r="J117" s="19"/>
+      <c r="C117" s="18"/>
+      <c r="D117" s="18"/>
+      <c r="E117" s="18"/>
+      <c r="F117" s="30"/>
+      <c r="G117" s="30"/>
+      <c r="H117" s="30"/>
+      <c r="I117" s="19"/>
+      <c r="J117" s="23"/>
       <c r="L117" s="12" t="s">
         <v>15</v>
       </c>
@@ -4886,14 +4893,14 @@
       </c>
     </row>
     <row r="118" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C118" s="20"/>
-      <c r="D118" s="20"/>
-      <c r="E118" s="20"/>
-      <c r="F118" s="23"/>
-      <c r="G118" s="23"/>
-      <c r="H118" s="23"/>
-      <c r="I118" s="18"/>
-      <c r="J118" s="19"/>
+      <c r="C118" s="18"/>
+      <c r="D118" s="18"/>
+      <c r="E118" s="18"/>
+      <c r="F118" s="30"/>
+      <c r="G118" s="30"/>
+      <c r="H118" s="30"/>
+      <c r="I118" s="19"/>
+      <c r="J118" s="23"/>
       <c r="L118" s="14" t="s">
         <v>17</v>
       </c>
@@ -4916,14 +4923,14 @@
       <c r="U118" s="10"/>
     </row>
     <row r="119" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C119" s="20"/>
-      <c r="D119" s="20"/>
-      <c r="E119" s="20"/>
-      <c r="F119" s="24"/>
-      <c r="G119" s="24"/>
-      <c r="H119" s="24"/>
-      <c r="I119" s="18"/>
-      <c r="J119" s="19"/>
+      <c r="C119" s="18"/>
+      <c r="D119" s="18"/>
+      <c r="E119" s="18"/>
+      <c r="F119" s="31"/>
+      <c r="G119" s="31"/>
+      <c r="H119" s="31"/>
+      <c r="I119" s="19"/>
+      <c r="J119" s="23"/>
       <c r="L119" s="15" t="s">
         <v>23</v>
       </c>
@@ -4943,26 +4950,26 @@
       <c r="B120" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C120" s="20" t="s">
+      <c r="C120" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="D120" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="E120" s="21"/>
-      <c r="F120" s="18" t="s">
+      <c r="D120" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="E120" s="24"/>
+      <c r="F120" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="G120" s="18" t="s">
+      <c r="G120" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="H120" s="18" t="s">
+      <c r="H120" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="I120" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="J120" s="25" t="s">
+      <c r="I120" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="J120" s="28" t="s">
         <v>32</v>
       </c>
       <c r="L120" s="9" t="s">
@@ -4990,14 +4997,14 @@
       <c r="B121">
         <v>8</v>
       </c>
-      <c r="C121" s="20"/>
-      <c r="D121" s="21"/>
-      <c r="E121" s="21"/>
-      <c r="F121" s="18"/>
-      <c r="G121" s="18"/>
-      <c r="H121" s="18"/>
-      <c r="I121" s="19"/>
-      <c r="J121" s="25"/>
+      <c r="C121" s="18"/>
+      <c r="D121" s="24"/>
+      <c r="E121" s="24"/>
+      <c r="F121" s="19"/>
+      <c r="G121" s="19"/>
+      <c r="H121" s="19"/>
+      <c r="I121" s="23"/>
+      <c r="J121" s="28"/>
       <c r="L121" s="11" t="s">
         <v>5</v>
       </c>
@@ -5036,14 +5043,14 @@
       <c r="B122" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="C122" s="20"/>
-      <c r="D122" s="21"/>
-      <c r="E122" s="21"/>
-      <c r="F122" s="18"/>
-      <c r="G122" s="18"/>
-      <c r="H122" s="18"/>
-      <c r="I122" s="19"/>
-      <c r="J122" s="25"/>
+      <c r="C122" s="18"/>
+      <c r="D122" s="24"/>
+      <c r="E122" s="24"/>
+      <c r="F122" s="19"/>
+      <c r="G122" s="19"/>
+      <c r="H122" s="19"/>
+      <c r="I122" s="23"/>
+      <c r="J122" s="28"/>
       <c r="L122" s="12" t="s">
         <v>15</v>
       </c>
@@ -5072,14 +5079,14 @@
       <c r="B123">
         <v>5</v>
       </c>
-      <c r="C123" s="20"/>
-      <c r="D123" s="21"/>
-      <c r="E123" s="21"/>
-      <c r="F123" s="18"/>
-      <c r="G123" s="18"/>
-      <c r="H123" s="18"/>
-      <c r="I123" s="19"/>
-      <c r="J123" s="25"/>
+      <c r="C123" s="18"/>
+      <c r="D123" s="24"/>
+      <c r="E123" s="24"/>
+      <c r="F123" s="19"/>
+      <c r="G123" s="19"/>
+      <c r="H123" s="19"/>
+      <c r="I123" s="23"/>
+      <c r="J123" s="28"/>
       <c r="L123" s="14" t="s">
         <v>17</v>
       </c>
@@ -5104,14 +5111,14 @@
       <c r="U123" s="10"/>
     </row>
     <row r="124" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C124" s="20"/>
-      <c r="D124" s="21"/>
-      <c r="E124" s="21"/>
-      <c r="F124" s="18"/>
-      <c r="G124" s="18"/>
-      <c r="H124" s="18"/>
-      <c r="I124" s="19"/>
-      <c r="J124" s="25"/>
+      <c r="C124" s="18"/>
+      <c r="D124" s="24"/>
+      <c r="E124" s="24"/>
+      <c r="F124" s="19"/>
+      <c r="G124" s="19"/>
+      <c r="H124" s="19"/>
+      <c r="I124" s="23"/>
+      <c r="J124" s="28"/>
       <c r="L124" s="15" t="s">
         <v>23</v>
       </c>
@@ -5135,26 +5142,26 @@
       <c r="P125" s="10"/>
     </row>
     <row r="126" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C126" s="20" t="s">
+      <c r="C126" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="D126" s="18" t="s">
+      <c r="D126" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E126" s="21"/>
-      <c r="F126" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="G126" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="H126" s="29" t="s">
+      <c r="E126" s="24"/>
+      <c r="F126" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="G126" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="H126" s="32" t="s">
         <v>26</v>
       </c>
       <c r="I126" s="26" t="s">
         <v>49</v>
       </c>
-      <c r="J126" s="20"/>
+      <c r="J126" s="18"/>
       <c r="L126" s="9" t="s">
         <v>0</v>
       </c>
@@ -5177,14 +5184,14 @@
       <c r="U126" s="10"/>
     </row>
     <row r="127" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C127" s="20"/>
-      <c r="D127" s="18"/>
-      <c r="E127" s="21"/>
-      <c r="F127" s="20"/>
-      <c r="G127" s="20"/>
-      <c r="H127" s="30"/>
+      <c r="C127" s="18"/>
+      <c r="D127" s="19"/>
+      <c r="E127" s="24"/>
+      <c r="F127" s="18"/>
+      <c r="G127" s="18"/>
+      <c r="H127" s="33"/>
       <c r="I127" s="27"/>
-      <c r="J127" s="20"/>
+      <c r="J127" s="18"/>
       <c r="L127" s="11" t="s">
         <v>5</v>
       </c>
@@ -5220,14 +5227,14 @@
       </c>
     </row>
     <row r="128" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C128" s="20"/>
-      <c r="D128" s="18"/>
-      <c r="E128" s="21"/>
-      <c r="F128" s="20"/>
-      <c r="G128" s="20"/>
-      <c r="H128" s="30"/>
+      <c r="C128" s="18"/>
+      <c r="D128" s="19"/>
+      <c r="E128" s="24"/>
+      <c r="F128" s="18"/>
+      <c r="G128" s="18"/>
+      <c r="H128" s="33"/>
       <c r="I128" s="27"/>
-      <c r="J128" s="20"/>
+      <c r="J128" s="18"/>
       <c r="L128" s="12" t="s">
         <v>15</v>
       </c>
@@ -5253,14 +5260,14 @@
       </c>
     </row>
     <row r="129" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C129" s="20"/>
-      <c r="D129" s="18"/>
-      <c r="E129" s="21"/>
-      <c r="F129" s="20"/>
-      <c r="G129" s="20"/>
-      <c r="H129" s="30"/>
+      <c r="C129" s="18"/>
+      <c r="D129" s="19"/>
+      <c r="E129" s="24"/>
+      <c r="F129" s="18"/>
+      <c r="G129" s="18"/>
+      <c r="H129" s="33"/>
       <c r="I129" s="27"/>
-      <c r="J129" s="20"/>
+      <c r="J129" s="18"/>
       <c r="L129" s="14" t="s">
         <v>17</v>
       </c>
@@ -5283,14 +5290,14 @@
       <c r="U129" s="10"/>
     </row>
     <row r="130" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C130" s="20"/>
-      <c r="D130" s="18"/>
-      <c r="E130" s="21"/>
-      <c r="F130" s="20"/>
-      <c r="G130" s="20"/>
-      <c r="H130" s="31"/>
+      <c r="C130" s="18"/>
+      <c r="D130" s="19"/>
+      <c r="E130" s="24"/>
+      <c r="F130" s="18"/>
+      <c r="G130" s="18"/>
+      <c r="H130" s="34"/>
       <c r="I130" s="27"/>
-      <c r="J130" s="20"/>
+      <c r="J130" s="18"/>
       <c r="L130" s="15" t="s">
         <v>23</v>
       </c>
@@ -5307,24 +5314,24 @@
       <c r="U130" s="10"/>
     </row>
     <row r="131" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C131" s="20" t="s">
+      <c r="C131" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="D131" s="20"/>
-      <c r="E131" s="20"/>
-      <c r="F131" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="G131" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="H131" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="I131" s="18" t="s">
+      <c r="D131" s="18"/>
+      <c r="E131" s="18"/>
+      <c r="F131" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="G131" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="H131" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="I131" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="J131" s="19" t="s">
+      <c r="J131" s="23" t="s">
         <v>26</v>
       </c>
       <c r="L131" s="9" t="s">
@@ -5349,14 +5356,14 @@
       <c r="U131" s="10"/>
     </row>
     <row r="132" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C132" s="20"/>
-      <c r="D132" s="20"/>
-      <c r="E132" s="20"/>
-      <c r="F132" s="20"/>
-      <c r="G132" s="20"/>
-      <c r="H132" s="20"/>
-      <c r="I132" s="18"/>
-      <c r="J132" s="19"/>
+      <c r="C132" s="18"/>
+      <c r="D132" s="18"/>
+      <c r="E132" s="18"/>
+      <c r="F132" s="18"/>
+      <c r="G132" s="18"/>
+      <c r="H132" s="18"/>
+      <c r="I132" s="19"/>
+      <c r="J132" s="23"/>
       <c r="L132" s="11" t="s">
         <v>5</v>
       </c>
@@ -5392,14 +5399,14 @@
       </c>
     </row>
     <row r="133" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C133" s="20"/>
-      <c r="D133" s="20"/>
-      <c r="E133" s="20"/>
-      <c r="F133" s="20"/>
-      <c r="G133" s="20"/>
-      <c r="H133" s="20"/>
-      <c r="I133" s="18"/>
-      <c r="J133" s="19"/>
+      <c r="C133" s="18"/>
+      <c r="D133" s="18"/>
+      <c r="E133" s="18"/>
+      <c r="F133" s="18"/>
+      <c r="G133" s="18"/>
+      <c r="H133" s="18"/>
+      <c r="I133" s="19"/>
+      <c r="J133" s="23"/>
       <c r="L133" s="12" t="s">
         <v>15</v>
       </c>
@@ -5425,14 +5432,14 @@
       </c>
     </row>
     <row r="134" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C134" s="20"/>
-      <c r="D134" s="20"/>
-      <c r="E134" s="20"/>
-      <c r="F134" s="20"/>
-      <c r="G134" s="20"/>
-      <c r="H134" s="20"/>
-      <c r="I134" s="18"/>
-      <c r="J134" s="19"/>
+      <c r="C134" s="18"/>
+      <c r="D134" s="18"/>
+      <c r="E134" s="18"/>
+      <c r="F134" s="18"/>
+      <c r="G134" s="18"/>
+      <c r="H134" s="18"/>
+      <c r="I134" s="19"/>
+      <c r="J134" s="23"/>
       <c r="L134" s="14" t="s">
         <v>17</v>
       </c>
@@ -5455,14 +5462,14 @@
       <c r="U134" s="10"/>
     </row>
     <row r="135" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C135" s="20"/>
-      <c r="D135" s="20"/>
-      <c r="E135" s="20"/>
-      <c r="F135" s="20"/>
-      <c r="G135" s="20"/>
-      <c r="H135" s="20"/>
-      <c r="I135" s="18"/>
-      <c r="J135" s="19"/>
+      <c r="C135" s="18"/>
+      <c r="D135" s="18"/>
+      <c r="E135" s="18"/>
+      <c r="F135" s="18"/>
+      <c r="G135" s="18"/>
+      <c r="H135" s="18"/>
+      <c r="I135" s="19"/>
+      <c r="J135" s="23"/>
       <c r="L135" s="15" t="s">
         <v>23</v>
       </c>
@@ -5482,26 +5489,26 @@
       <c r="B136" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C136" s="20" t="s">
+      <c r="C136" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="D136" s="20"/>
-      <c r="E136" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="F136" s="18" t="s">
+      <c r="D136" s="18"/>
+      <c r="E136" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="F136" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="G136" s="18" t="s">
+      <c r="G136" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="H136" s="18" t="s">
+      <c r="H136" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="I136" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="J136" s="25" t="s">
+      <c r="I136" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="J136" s="28" t="s">
         <v>32</v>
       </c>
       <c r="L136" s="9" t="s">
@@ -5529,14 +5536,14 @@
       <c r="B137">
         <v>9</v>
       </c>
-      <c r="C137" s="20"/>
-      <c r="D137" s="20"/>
-      <c r="E137" s="21"/>
-      <c r="F137" s="18"/>
-      <c r="G137" s="18"/>
-      <c r="H137" s="18"/>
-      <c r="I137" s="19"/>
-      <c r="J137" s="25"/>
+      <c r="C137" s="18"/>
+      <c r="D137" s="18"/>
+      <c r="E137" s="24"/>
+      <c r="F137" s="19"/>
+      <c r="G137" s="19"/>
+      <c r="H137" s="19"/>
+      <c r="I137" s="23"/>
+      <c r="J137" s="28"/>
       <c r="L137" s="11" t="s">
         <v>5</v>
       </c>
@@ -5575,14 +5582,14 @@
       <c r="B138" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="C138" s="20"/>
-      <c r="D138" s="20"/>
-      <c r="E138" s="21"/>
-      <c r="F138" s="18"/>
-      <c r="G138" s="18"/>
-      <c r="H138" s="18"/>
-      <c r="I138" s="19"/>
-      <c r="J138" s="25"/>
+      <c r="C138" s="18"/>
+      <c r="D138" s="18"/>
+      <c r="E138" s="24"/>
+      <c r="F138" s="19"/>
+      <c r="G138" s="19"/>
+      <c r="H138" s="19"/>
+      <c r="I138" s="23"/>
+      <c r="J138" s="28"/>
       <c r="L138" s="12" t="s">
         <v>15</v>
       </c>
@@ -5611,14 +5618,14 @@
       <c r="B139">
         <v>6</v>
       </c>
-      <c r="C139" s="20"/>
-      <c r="D139" s="20"/>
-      <c r="E139" s="21"/>
-      <c r="F139" s="18"/>
-      <c r="G139" s="18"/>
-      <c r="H139" s="18"/>
-      <c r="I139" s="19"/>
-      <c r="J139" s="25"/>
+      <c r="C139" s="18"/>
+      <c r="D139" s="18"/>
+      <c r="E139" s="24"/>
+      <c r="F139" s="19"/>
+      <c r="G139" s="19"/>
+      <c r="H139" s="19"/>
+      <c r="I139" s="23"/>
+      <c r="J139" s="28"/>
       <c r="L139" s="14" t="s">
         <v>17</v>
       </c>
@@ -5643,14 +5650,14 @@
       <c r="U139" s="10"/>
     </row>
     <row r="140" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C140" s="20"/>
-      <c r="D140" s="20"/>
-      <c r="E140" s="21"/>
-      <c r="F140" s="18"/>
-      <c r="G140" s="18"/>
-      <c r="H140" s="18"/>
-      <c r="I140" s="19"/>
-      <c r="J140" s="25"/>
+      <c r="C140" s="18"/>
+      <c r="D140" s="18"/>
+      <c r="E140" s="24"/>
+      <c r="F140" s="19"/>
+      <c r="G140" s="19"/>
+      <c r="H140" s="19"/>
+      <c r="I140" s="23"/>
+      <c r="J140" s="28"/>
       <c r="L140" s="15" t="s">
         <v>23</v>
       </c>
@@ -5674,26 +5681,26 @@
       <c r="P141" s="10"/>
     </row>
     <row r="142" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C142" s="20" t="s">
+      <c r="C142" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="D142" s="18"/>
-      <c r="E142" s="18" t="s">
+      <c r="D142" s="19"/>
+      <c r="E142" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="F142" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="G142" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="H142" s="20" t="s">
+      <c r="F142" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="G142" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="H142" s="18" t="s">
         <v>26</v>
       </c>
       <c r="I142" s="26" t="s">
         <v>49</v>
       </c>
-      <c r="J142" s="20"/>
+      <c r="J142" s="18"/>
       <c r="L142" s="9" t="s">
         <v>0</v>
       </c>
@@ -5716,14 +5723,14 @@
       <c r="U142" s="10"/>
     </row>
     <row r="143" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C143" s="20"/>
-      <c r="D143" s="18"/>
-      <c r="E143" s="18"/>
-      <c r="F143" s="19"/>
-      <c r="G143" s="20"/>
-      <c r="H143" s="20"/>
+      <c r="C143" s="18"/>
+      <c r="D143" s="19"/>
+      <c r="E143" s="19"/>
+      <c r="F143" s="23"/>
+      <c r="G143" s="18"/>
+      <c r="H143" s="18"/>
       <c r="I143" s="27"/>
-      <c r="J143" s="20"/>
+      <c r="J143" s="18"/>
       <c r="L143" s="11" t="s">
         <v>5</v>
       </c>
@@ -5762,14 +5769,14 @@
       <c r="A144">
         <v>25</v>
       </c>
-      <c r="C144" s="20"/>
-      <c r="D144" s="18"/>
-      <c r="E144" s="18"/>
-      <c r="F144" s="19"/>
-      <c r="G144" s="20"/>
-      <c r="H144" s="20"/>
+      <c r="C144" s="18"/>
+      <c r="D144" s="19"/>
+      <c r="E144" s="19"/>
+      <c r="F144" s="23"/>
+      <c r="G144" s="18"/>
+      <c r="H144" s="18"/>
       <c r="I144" s="27"/>
-      <c r="J144" s="20"/>
+      <c r="J144" s="18"/>
       <c r="L144" s="12" t="s">
         <v>15</v>
       </c>
@@ -5795,14 +5802,14 @@
       </c>
     </row>
     <row r="145" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C145" s="20"/>
-      <c r="D145" s="18"/>
-      <c r="E145" s="18"/>
-      <c r="F145" s="19"/>
-      <c r="G145" s="20"/>
-      <c r="H145" s="20"/>
+      <c r="C145" s="18"/>
+      <c r="D145" s="19"/>
+      <c r="E145" s="19"/>
+      <c r="F145" s="23"/>
+      <c r="G145" s="18"/>
+      <c r="H145" s="18"/>
       <c r="I145" s="27"/>
-      <c r="J145" s="20"/>
+      <c r="J145" s="18"/>
       <c r="L145" s="14" t="s">
         <v>17</v>
       </c>
@@ -5825,14 +5832,14 @@
       <c r="U145" s="10"/>
     </row>
     <row r="146" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C146" s="20"/>
-      <c r="D146" s="18"/>
-      <c r="E146" s="18"/>
-      <c r="F146" s="19"/>
-      <c r="G146" s="20"/>
-      <c r="H146" s="20"/>
+      <c r="C146" s="18"/>
+      <c r="D146" s="19"/>
+      <c r="E146" s="19"/>
+      <c r="F146" s="23"/>
+      <c r="G146" s="18"/>
+      <c r="H146" s="18"/>
       <c r="I146" s="27"/>
-      <c r="J146" s="20"/>
+      <c r="J146" s="18"/>
       <c r="L146" s="15" t="s">
         <v>23</v>
       </c>
@@ -5849,24 +5856,24 @@
       <c r="U146" s="10"/>
     </row>
     <row r="147" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C147" s="20" t="s">
+      <c r="C147" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="D147" s="20"/>
-      <c r="E147" s="20"/>
-      <c r="F147" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="G147" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="H147" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="I147" s="18" t="s">
+      <c r="D147" s="18"/>
+      <c r="E147" s="18"/>
+      <c r="F147" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="G147" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="H147" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="I147" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="J147" s="19" t="s">
+      <c r="J147" s="23" t="s">
         <v>26</v>
       </c>
       <c r="L147" s="9" t="s">
@@ -5891,14 +5898,14 @@
       <c r="U147" s="10"/>
     </row>
     <row r="148" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C148" s="20"/>
-      <c r="D148" s="20"/>
-      <c r="E148" s="20"/>
-      <c r="F148" s="20"/>
-      <c r="G148" s="20"/>
-      <c r="H148" s="20"/>
-      <c r="I148" s="18"/>
-      <c r="J148" s="19"/>
+      <c r="C148" s="18"/>
+      <c r="D148" s="18"/>
+      <c r="E148" s="18"/>
+      <c r="F148" s="18"/>
+      <c r="G148" s="18"/>
+      <c r="H148" s="18"/>
+      <c r="I148" s="19"/>
+      <c r="J148" s="23"/>
       <c r="L148" s="11" t="s">
         <v>5</v>
       </c>
@@ -5934,14 +5941,14 @@
       </c>
     </row>
     <row r="149" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C149" s="20"/>
-      <c r="D149" s="20"/>
-      <c r="E149" s="20"/>
-      <c r="F149" s="20"/>
-      <c r="G149" s="20"/>
-      <c r="H149" s="20"/>
-      <c r="I149" s="18"/>
-      <c r="J149" s="19"/>
+      <c r="C149" s="18"/>
+      <c r="D149" s="18"/>
+      <c r="E149" s="18"/>
+      <c r="F149" s="18"/>
+      <c r="G149" s="18"/>
+      <c r="H149" s="18"/>
+      <c r="I149" s="19"/>
+      <c r="J149" s="23"/>
       <c r="L149" s="12" t="s">
         <v>15</v>
       </c>
@@ -5967,14 +5974,14 @@
       </c>
     </row>
     <row r="150" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C150" s="20"/>
-      <c r="D150" s="20"/>
-      <c r="E150" s="20"/>
-      <c r="F150" s="20"/>
-      <c r="G150" s="20"/>
-      <c r="H150" s="20"/>
-      <c r="I150" s="18"/>
-      <c r="J150" s="19"/>
+      <c r="C150" s="18"/>
+      <c r="D150" s="18"/>
+      <c r="E150" s="18"/>
+      <c r="F150" s="18"/>
+      <c r="G150" s="18"/>
+      <c r="H150" s="18"/>
+      <c r="I150" s="19"/>
+      <c r="J150" s="23"/>
       <c r="L150" s="14" t="s">
         <v>17</v>
       </c>
@@ -5997,14 +6004,14 @@
       <c r="U150" s="10"/>
     </row>
     <row r="151" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C151" s="20"/>
-      <c r="D151" s="20"/>
-      <c r="E151" s="20"/>
-      <c r="F151" s="20"/>
-      <c r="G151" s="20"/>
-      <c r="H151" s="20"/>
-      <c r="I151" s="18"/>
-      <c r="J151" s="19"/>
+      <c r="C151" s="18"/>
+      <c r="D151" s="18"/>
+      <c r="E151" s="18"/>
+      <c r="F151" s="18"/>
+      <c r="G151" s="18"/>
+      <c r="H151" s="18"/>
+      <c r="I151" s="19"/>
+      <c r="J151" s="23"/>
       <c r="L151" s="15" t="s">
         <v>23</v>
       </c>
@@ -6024,26 +6031,26 @@
       <c r="B152" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C152" s="20" t="s">
+      <c r="C152" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="D152" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="E152" s="21"/>
-      <c r="F152" s="18" t="s">
+      <c r="D152" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="E152" s="24"/>
+      <c r="F152" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="G152" s="18" t="s">
+      <c r="G152" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="H152" s="18" t="s">
+      <c r="H152" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="I152" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="J152" s="25" t="s">
+      <c r="I152" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="J152" s="28" t="s">
         <v>32</v>
       </c>
       <c r="L152" s="9" t="s">
@@ -6071,14 +6078,14 @@
       <c r="B153">
         <v>10</v>
       </c>
-      <c r="C153" s="20"/>
-      <c r="D153" s="21"/>
-      <c r="E153" s="21"/>
-      <c r="F153" s="18"/>
-      <c r="G153" s="18"/>
-      <c r="H153" s="18"/>
-      <c r="I153" s="19"/>
-      <c r="J153" s="25"/>
+      <c r="C153" s="18"/>
+      <c r="D153" s="24"/>
+      <c r="E153" s="24"/>
+      <c r="F153" s="19"/>
+      <c r="G153" s="19"/>
+      <c r="H153" s="19"/>
+      <c r="I153" s="23"/>
+      <c r="J153" s="28"/>
       <c r="L153" s="11" t="s">
         <v>5</v>
       </c>
@@ -6117,14 +6124,14 @@
       <c r="B154" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="C154" s="20"/>
-      <c r="D154" s="21"/>
-      <c r="E154" s="21"/>
-      <c r="F154" s="18"/>
-      <c r="G154" s="18"/>
-      <c r="H154" s="18"/>
-      <c r="I154" s="19"/>
-      <c r="J154" s="25"/>
+      <c r="C154" s="18"/>
+      <c r="D154" s="24"/>
+      <c r="E154" s="24"/>
+      <c r="F154" s="19"/>
+      <c r="G154" s="19"/>
+      <c r="H154" s="19"/>
+      <c r="I154" s="23"/>
+      <c r="J154" s="28"/>
       <c r="L154" s="12" t="s">
         <v>15</v>
       </c>
@@ -6153,14 +6160,14 @@
       <c r="B155">
         <v>7</v>
       </c>
-      <c r="C155" s="20"/>
-      <c r="D155" s="21"/>
-      <c r="E155" s="21"/>
-      <c r="F155" s="18"/>
-      <c r="G155" s="18"/>
-      <c r="H155" s="18"/>
-      <c r="I155" s="19"/>
-      <c r="J155" s="25"/>
+      <c r="C155" s="18"/>
+      <c r="D155" s="24"/>
+      <c r="E155" s="24"/>
+      <c r="F155" s="19"/>
+      <c r="G155" s="19"/>
+      <c r="H155" s="19"/>
+      <c r="I155" s="23"/>
+      <c r="J155" s="28"/>
       <c r="L155" s="14" t="s">
         <v>17</v>
       </c>
@@ -6185,14 +6192,14 @@
       <c r="U155" s="10"/>
     </row>
     <row r="156" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C156" s="20"/>
-      <c r="D156" s="21"/>
-      <c r="E156" s="21"/>
-      <c r="F156" s="18"/>
-      <c r="G156" s="18"/>
-      <c r="H156" s="18"/>
-      <c r="I156" s="19"/>
-      <c r="J156" s="25"/>
+      <c r="C156" s="18"/>
+      <c r="D156" s="24"/>
+      <c r="E156" s="24"/>
+      <c r="F156" s="19"/>
+      <c r="G156" s="19"/>
+      <c r="H156" s="19"/>
+      <c r="I156" s="23"/>
+      <c r="J156" s="28"/>
       <c r="L156" s="15" t="s">
         <v>23</v>
       </c>
@@ -6222,26 +6229,26 @@
       <c r="A159" t="s">
         <v>65</v>
       </c>
-      <c r="C159" s="20" t="s">
+      <c r="C159" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="D159" s="18" t="s">
+      <c r="D159" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E159" s="21"/>
-      <c r="F159" s="28" t="s">
-        <v>26</v>
-      </c>
-      <c r="G159" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="H159" s="28" t="s">
+      <c r="E159" s="24"/>
+      <c r="F159" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="G159" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="H159" s="25" t="s">
         <v>26</v>
       </c>
       <c r="I159" s="26" t="s">
         <v>49</v>
       </c>
-      <c r="J159" s="20"/>
+      <c r="J159" s="18"/>
       <c r="L159" s="9" t="s">
         <v>0</v>
       </c>
@@ -6264,14 +6271,14 @@
       <c r="U159" s="10"/>
     </row>
     <row r="160" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C160" s="20"/>
-      <c r="D160" s="18"/>
-      <c r="E160" s="21"/>
-      <c r="F160" s="21"/>
-      <c r="G160" s="19"/>
-      <c r="H160" s="21"/>
+      <c r="C160" s="18"/>
+      <c r="D160" s="19"/>
+      <c r="E160" s="24"/>
+      <c r="F160" s="24"/>
+      <c r="G160" s="23"/>
+      <c r="H160" s="24"/>
       <c r="I160" s="27"/>
-      <c r="J160" s="20"/>
+      <c r="J160" s="18"/>
       <c r="L160" s="11" t="s">
         <v>5</v>
       </c>
@@ -6307,14 +6314,14 @@
       </c>
     </row>
     <row r="161" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C161" s="20"/>
-      <c r="D161" s="18"/>
-      <c r="E161" s="21"/>
-      <c r="F161" s="21"/>
-      <c r="G161" s="19"/>
-      <c r="H161" s="21"/>
+      <c r="C161" s="18"/>
+      <c r="D161" s="19"/>
+      <c r="E161" s="24"/>
+      <c r="F161" s="24"/>
+      <c r="G161" s="23"/>
+      <c r="H161" s="24"/>
       <c r="I161" s="27"/>
-      <c r="J161" s="20"/>
+      <c r="J161" s="18"/>
       <c r="L161" s="12" t="s">
         <v>15</v>
       </c>
@@ -6340,14 +6347,14 @@
       </c>
     </row>
     <row r="162" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C162" s="20"/>
-      <c r="D162" s="18"/>
-      <c r="E162" s="21"/>
-      <c r="F162" s="21"/>
-      <c r="G162" s="19"/>
-      <c r="H162" s="21"/>
+      <c r="C162" s="18"/>
+      <c r="D162" s="19"/>
+      <c r="E162" s="24"/>
+      <c r="F162" s="24"/>
+      <c r="G162" s="23"/>
+      <c r="H162" s="24"/>
       <c r="I162" s="27"/>
-      <c r="J162" s="20"/>
+      <c r="J162" s="18"/>
       <c r="L162" s="14" t="s">
         <v>17</v>
       </c>
@@ -6370,14 +6377,14 @@
       <c r="U162" s="10"/>
     </row>
     <row r="163" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C163" s="20"/>
-      <c r="D163" s="18"/>
-      <c r="E163" s="21"/>
-      <c r="F163" s="21"/>
-      <c r="G163" s="19"/>
-      <c r="H163" s="21"/>
+      <c r="C163" s="18"/>
+      <c r="D163" s="19"/>
+      <c r="E163" s="24"/>
+      <c r="F163" s="24"/>
+      <c r="G163" s="23"/>
+      <c r="H163" s="24"/>
       <c r="I163" s="27"/>
-      <c r="J163" s="20"/>
+      <c r="J163" s="18"/>
       <c r="L163" s="15" t="s">
         <v>23</v>
       </c>
@@ -6394,24 +6401,24 @@
       <c r="U163" s="10"/>
     </row>
     <row r="164" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C164" s="20" t="s">
+      <c r="C164" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="D164" s="20"/>
-      <c r="E164" s="20"/>
-      <c r="F164" s="28" t="s">
-        <v>26</v>
-      </c>
-      <c r="G164" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="H164" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="I164" s="18" t="s">
+      <c r="D164" s="18"/>
+      <c r="E164" s="18"/>
+      <c r="F164" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="G164" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="H164" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="I164" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="J164" s="19" t="s">
+      <c r="J164" s="23" t="s">
         <v>26</v>
       </c>
       <c r="L164" s="9" t="s">
@@ -6436,14 +6443,14 @@
       <c r="U164" s="10"/>
     </row>
     <row r="165" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C165" s="20"/>
-      <c r="D165" s="20"/>
-      <c r="E165" s="20"/>
-      <c r="F165" s="21"/>
-      <c r="G165" s="20"/>
-      <c r="H165" s="20"/>
-      <c r="I165" s="18"/>
-      <c r="J165" s="19"/>
+      <c r="C165" s="18"/>
+      <c r="D165" s="18"/>
+      <c r="E165" s="18"/>
+      <c r="F165" s="24"/>
+      <c r="G165" s="18"/>
+      <c r="H165" s="18"/>
+      <c r="I165" s="19"/>
+      <c r="J165" s="23"/>
       <c r="L165" s="11" t="s">
         <v>5</v>
       </c>
@@ -6479,14 +6486,14 @@
       </c>
     </row>
     <row r="166" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C166" s="20"/>
-      <c r="D166" s="20"/>
-      <c r="E166" s="20"/>
-      <c r="F166" s="21"/>
-      <c r="G166" s="20"/>
-      <c r="H166" s="20"/>
-      <c r="I166" s="18"/>
-      <c r="J166" s="19"/>
+      <c r="C166" s="18"/>
+      <c r="D166" s="18"/>
+      <c r="E166" s="18"/>
+      <c r="F166" s="24"/>
+      <c r="G166" s="18"/>
+      <c r="H166" s="18"/>
+      <c r="I166" s="19"/>
+      <c r="J166" s="23"/>
       <c r="L166" s="12" t="s">
         <v>15</v>
       </c>
@@ -6512,14 +6519,14 @@
       </c>
     </row>
     <row r="167" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C167" s="20"/>
-      <c r="D167" s="20"/>
-      <c r="E167" s="20"/>
-      <c r="F167" s="21"/>
-      <c r="G167" s="20"/>
-      <c r="H167" s="20"/>
-      <c r="I167" s="18"/>
-      <c r="J167" s="19"/>
+      <c r="C167" s="18"/>
+      <c r="D167" s="18"/>
+      <c r="E167" s="18"/>
+      <c r="F167" s="24"/>
+      <c r="G167" s="18"/>
+      <c r="H167" s="18"/>
+      <c r="I167" s="19"/>
+      <c r="J167" s="23"/>
       <c r="L167" s="14" t="s">
         <v>17</v>
       </c>
@@ -6542,14 +6549,14 @@
       <c r="U167" s="10"/>
     </row>
     <row r="168" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C168" s="20"/>
-      <c r="D168" s="20"/>
-      <c r="E168" s="20"/>
-      <c r="F168" s="21"/>
-      <c r="G168" s="20"/>
-      <c r="H168" s="20"/>
-      <c r="I168" s="18"/>
-      <c r="J168" s="19"/>
+      <c r="C168" s="18"/>
+      <c r="D168" s="18"/>
+      <c r="E168" s="18"/>
+      <c r="F168" s="24"/>
+      <c r="G168" s="18"/>
+      <c r="H168" s="18"/>
+      <c r="I168" s="19"/>
+      <c r="J168" s="23"/>
       <c r="L168" s="15" t="s">
         <v>23</v>
       </c>
@@ -6569,26 +6576,26 @@
       <c r="B169" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C169" s="20" t="s">
+      <c r="C169" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="D169" s="20"/>
-      <c r="E169" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="F169" s="18" t="s">
+      <c r="D169" s="18"/>
+      <c r="E169" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="F169" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="G169" s="18" t="s">
+      <c r="G169" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="H169" s="18" t="s">
+      <c r="H169" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="I169" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="J169" s="25" t="s">
+      <c r="I169" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="J169" s="28" t="s">
         <v>32</v>
       </c>
       <c r="L169" s="9" t="s">
@@ -6616,14 +6623,14 @@
       <c r="B170">
         <v>11</v>
       </c>
-      <c r="C170" s="20"/>
-      <c r="D170" s="20"/>
-      <c r="E170" s="21"/>
-      <c r="F170" s="18"/>
-      <c r="G170" s="18"/>
-      <c r="H170" s="18"/>
-      <c r="I170" s="19"/>
-      <c r="J170" s="25"/>
+      <c r="C170" s="18"/>
+      <c r="D170" s="18"/>
+      <c r="E170" s="24"/>
+      <c r="F170" s="19"/>
+      <c r="G170" s="19"/>
+      <c r="H170" s="19"/>
+      <c r="I170" s="23"/>
+      <c r="J170" s="28"/>
       <c r="L170" s="11" t="s">
         <v>5</v>
       </c>
@@ -6665,14 +6672,14 @@
       <c r="B171" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="C171" s="20"/>
-      <c r="D171" s="20"/>
-      <c r="E171" s="21"/>
-      <c r="F171" s="18"/>
-      <c r="G171" s="18"/>
-      <c r="H171" s="18"/>
-      <c r="I171" s="19"/>
-      <c r="J171" s="25"/>
+      <c r="C171" s="18"/>
+      <c r="D171" s="18"/>
+      <c r="E171" s="24"/>
+      <c r="F171" s="19"/>
+      <c r="G171" s="19"/>
+      <c r="H171" s="19"/>
+      <c r="I171" s="23"/>
+      <c r="J171" s="28"/>
       <c r="L171" s="12" t="s">
         <v>15</v>
       </c>
@@ -6701,14 +6708,14 @@
       <c r="B172">
         <v>8</v>
       </c>
-      <c r="C172" s="20"/>
-      <c r="D172" s="20"/>
-      <c r="E172" s="21"/>
-      <c r="F172" s="18"/>
-      <c r="G172" s="18"/>
-      <c r="H172" s="18"/>
-      <c r="I172" s="19"/>
-      <c r="J172" s="25"/>
+      <c r="C172" s="18"/>
+      <c r="D172" s="18"/>
+      <c r="E172" s="24"/>
+      <c r="F172" s="19"/>
+      <c r="G172" s="19"/>
+      <c r="H172" s="19"/>
+      <c r="I172" s="23"/>
+      <c r="J172" s="28"/>
       <c r="L172" s="14" t="s">
         <v>17</v>
       </c>
@@ -6733,14 +6740,14 @@
       <c r="U172" s="10"/>
     </row>
     <row r="173" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C173" s="20"/>
-      <c r="D173" s="20"/>
-      <c r="E173" s="21"/>
-      <c r="F173" s="18"/>
-      <c r="G173" s="18"/>
-      <c r="H173" s="18"/>
-      <c r="I173" s="19"/>
-      <c r="J173" s="25"/>
+      <c r="C173" s="18"/>
+      <c r="D173" s="18"/>
+      <c r="E173" s="24"/>
+      <c r="F173" s="19"/>
+      <c r="G173" s="19"/>
+      <c r="H173" s="19"/>
+      <c r="I173" s="23"/>
+      <c r="J173" s="28"/>
       <c r="L173" s="15" t="s">
         <v>23</v>
       </c>
@@ -6764,26 +6771,26 @@
       <c r="P174" s="10"/>
     </row>
     <row r="175" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C175" s="20" t="s">
+      <c r="C175" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="D175" s="18"/>
-      <c r="E175" s="18" t="s">
+      <c r="D175" s="19"/>
+      <c r="E175" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="F175" s="28" t="s">
-        <v>26</v>
-      </c>
-      <c r="G175" s="28" t="s">
-        <v>26</v>
-      </c>
-      <c r="H175" s="19" t="s">
+      <c r="F175" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="G175" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="H175" s="23" t="s">
         <v>26</v>
       </c>
       <c r="I175" s="26" t="s">
         <v>49</v>
       </c>
-      <c r="J175" s="20"/>
+      <c r="J175" s="18"/>
       <c r="L175" s="9" t="s">
         <v>0</v>
       </c>
@@ -6806,14 +6813,14 @@
       <c r="U175" s="10"/>
     </row>
     <row r="176" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C176" s="20"/>
-      <c r="D176" s="18"/>
-      <c r="E176" s="18"/>
-      <c r="F176" s="21"/>
-      <c r="G176" s="21"/>
-      <c r="H176" s="19"/>
+      <c r="C176" s="18"/>
+      <c r="D176" s="19"/>
+      <c r="E176" s="19"/>
+      <c r="F176" s="24"/>
+      <c r="G176" s="24"/>
+      <c r="H176" s="23"/>
       <c r="I176" s="27"/>
-      <c r="J176" s="20"/>
+      <c r="J176" s="18"/>
       <c r="L176" s="11" t="s">
         <v>5</v>
       </c>
@@ -6849,14 +6856,14 @@
       </c>
     </row>
     <row r="177" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C177" s="20"/>
-      <c r="D177" s="18"/>
-      <c r="E177" s="18"/>
-      <c r="F177" s="21"/>
-      <c r="G177" s="21"/>
-      <c r="H177" s="19"/>
+      <c r="C177" s="18"/>
+      <c r="D177" s="19"/>
+      <c r="E177" s="19"/>
+      <c r="F177" s="24"/>
+      <c r="G177" s="24"/>
+      <c r="H177" s="23"/>
       <c r="I177" s="27"/>
-      <c r="J177" s="20"/>
+      <c r="J177" s="18"/>
       <c r="L177" s="12" t="s">
         <v>15</v>
       </c>
@@ -6882,14 +6889,14 @@
       </c>
     </row>
     <row r="178" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C178" s="20"/>
-      <c r="D178" s="18"/>
-      <c r="E178" s="18"/>
-      <c r="F178" s="21"/>
-      <c r="G178" s="21"/>
-      <c r="H178" s="19"/>
+      <c r="C178" s="18"/>
+      <c r="D178" s="19"/>
+      <c r="E178" s="19"/>
+      <c r="F178" s="24"/>
+      <c r="G178" s="24"/>
+      <c r="H178" s="23"/>
       <c r="I178" s="27"/>
-      <c r="J178" s="20"/>
+      <c r="J178" s="18"/>
       <c r="L178" s="14" t="s">
         <v>17</v>
       </c>
@@ -6912,14 +6919,14 @@
       <c r="U178" s="10"/>
     </row>
     <row r="179" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C179" s="20"/>
-      <c r="D179" s="18"/>
-      <c r="E179" s="18"/>
-      <c r="F179" s="21"/>
-      <c r="G179" s="21"/>
-      <c r="H179" s="19"/>
+      <c r="C179" s="18"/>
+      <c r="D179" s="19"/>
+      <c r="E179" s="19"/>
+      <c r="F179" s="24"/>
+      <c r="G179" s="24"/>
+      <c r="H179" s="23"/>
       <c r="I179" s="27"/>
-      <c r="J179" s="20"/>
+      <c r="J179" s="18"/>
       <c r="L179" s="15" t="s">
         <v>23</v>
       </c>
@@ -6936,24 +6943,24 @@
       <c r="U179" s="10"/>
     </row>
     <row r="180" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C180" s="20" t="s">
+      <c r="C180" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="D180" s="20"/>
-      <c r="E180" s="20"/>
-      <c r="F180" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="G180" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="H180" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="I180" s="18" t="s">
+      <c r="D180" s="18"/>
+      <c r="E180" s="18"/>
+      <c r="F180" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="G180" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="H180" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="I180" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="J180" s="19" t="s">
+      <c r="J180" s="23" t="s">
         <v>26</v>
       </c>
       <c r="L180" s="9" t="s">
@@ -6978,14 +6985,14 @@
       <c r="U180" s="10"/>
     </row>
     <row r="181" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C181" s="20"/>
-      <c r="D181" s="20"/>
-      <c r="E181" s="20"/>
-      <c r="F181" s="23"/>
-      <c r="G181" s="23"/>
-      <c r="H181" s="23"/>
-      <c r="I181" s="18"/>
-      <c r="J181" s="19"/>
+      <c r="C181" s="18"/>
+      <c r="D181" s="18"/>
+      <c r="E181" s="18"/>
+      <c r="F181" s="30"/>
+      <c r="G181" s="30"/>
+      <c r="H181" s="30"/>
+      <c r="I181" s="19"/>
+      <c r="J181" s="23"/>
       <c r="L181" s="11" t="s">
         <v>5</v>
       </c>
@@ -7021,14 +7028,14 @@
       </c>
     </row>
     <row r="182" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C182" s="20"/>
-      <c r="D182" s="20"/>
-      <c r="E182" s="20"/>
-      <c r="F182" s="23"/>
-      <c r="G182" s="23"/>
-      <c r="H182" s="23"/>
-      <c r="I182" s="18"/>
-      <c r="J182" s="19"/>
+      <c r="C182" s="18"/>
+      <c r="D182" s="18"/>
+      <c r="E182" s="18"/>
+      <c r="F182" s="30"/>
+      <c r="G182" s="30"/>
+      <c r="H182" s="30"/>
+      <c r="I182" s="19"/>
+      <c r="J182" s="23"/>
       <c r="L182" s="12" t="s">
         <v>15</v>
       </c>
@@ -7054,14 +7061,14 @@
       </c>
     </row>
     <row r="183" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C183" s="20"/>
-      <c r="D183" s="20"/>
-      <c r="E183" s="20"/>
-      <c r="F183" s="23"/>
-      <c r="G183" s="23"/>
-      <c r="H183" s="23"/>
-      <c r="I183" s="18"/>
-      <c r="J183" s="19"/>
+      <c r="C183" s="18"/>
+      <c r="D183" s="18"/>
+      <c r="E183" s="18"/>
+      <c r="F183" s="30"/>
+      <c r="G183" s="30"/>
+      <c r="H183" s="30"/>
+      <c r="I183" s="19"/>
+      <c r="J183" s="23"/>
       <c r="L183" s="14" t="s">
         <v>17</v>
       </c>
@@ -7084,14 +7091,14 @@
       <c r="U183" s="10"/>
     </row>
     <row r="184" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C184" s="20"/>
-      <c r="D184" s="20"/>
-      <c r="E184" s="20"/>
-      <c r="F184" s="24"/>
-      <c r="G184" s="24"/>
-      <c r="H184" s="24"/>
-      <c r="I184" s="18"/>
-      <c r="J184" s="19"/>
+      <c r="C184" s="18"/>
+      <c r="D184" s="18"/>
+      <c r="E184" s="18"/>
+      <c r="F184" s="31"/>
+      <c r="G184" s="31"/>
+      <c r="H184" s="31"/>
+      <c r="I184" s="19"/>
+      <c r="J184" s="23"/>
       <c r="L184" s="15" t="s">
         <v>23</v>
       </c>
@@ -7111,26 +7118,26 @@
       <c r="B185" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C185" s="20" t="s">
+      <c r="C185" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="D185" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="E185" s="21"/>
-      <c r="F185" s="18" t="s">
+      <c r="D185" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="E185" s="24"/>
+      <c r="F185" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="G185" s="18" t="s">
+      <c r="G185" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="H185" s="18" t="s">
+      <c r="H185" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="I185" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="J185" s="25" t="s">
+      <c r="I185" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="J185" s="28" t="s">
         <v>32</v>
       </c>
       <c r="L185" s="9" t="s">
@@ -7158,14 +7165,14 @@
       <c r="B186">
         <v>12</v>
       </c>
-      <c r="C186" s="20"/>
-      <c r="D186" s="21"/>
-      <c r="E186" s="21"/>
-      <c r="F186" s="18"/>
-      <c r="G186" s="18"/>
-      <c r="H186" s="18"/>
-      <c r="I186" s="19"/>
-      <c r="J186" s="25"/>
+      <c r="C186" s="18"/>
+      <c r="D186" s="24"/>
+      <c r="E186" s="24"/>
+      <c r="F186" s="19"/>
+      <c r="G186" s="19"/>
+      <c r="H186" s="19"/>
+      <c r="I186" s="23"/>
+      <c r="J186" s="28"/>
       <c r="L186" s="11" t="s">
         <v>5</v>
       </c>
@@ -7204,14 +7211,14 @@
       <c r="B187" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="C187" s="20"/>
-      <c r="D187" s="21"/>
-      <c r="E187" s="21"/>
-      <c r="F187" s="18"/>
-      <c r="G187" s="18"/>
-      <c r="H187" s="18"/>
-      <c r="I187" s="19"/>
-      <c r="J187" s="25"/>
+      <c r="C187" s="18"/>
+      <c r="D187" s="24"/>
+      <c r="E187" s="24"/>
+      <c r="F187" s="19"/>
+      <c r="G187" s="19"/>
+      <c r="H187" s="19"/>
+      <c r="I187" s="23"/>
+      <c r="J187" s="28"/>
       <c r="L187" s="12" t="s">
         <v>15</v>
       </c>
@@ -7240,14 +7247,14 @@
       <c r="B188">
         <v>9</v>
       </c>
-      <c r="C188" s="20"/>
-      <c r="D188" s="21"/>
-      <c r="E188" s="21"/>
-      <c r="F188" s="18"/>
-      <c r="G188" s="18"/>
-      <c r="H188" s="18"/>
-      <c r="I188" s="19"/>
-      <c r="J188" s="25"/>
+      <c r="C188" s="18"/>
+      <c r="D188" s="24"/>
+      <c r="E188" s="24"/>
+      <c r="F188" s="19"/>
+      <c r="G188" s="19"/>
+      <c r="H188" s="19"/>
+      <c r="I188" s="23"/>
+      <c r="J188" s="28"/>
       <c r="L188" s="14" t="s">
         <v>17</v>
       </c>
@@ -7272,14 +7279,14 @@
       <c r="U188" s="10"/>
     </row>
     <row r="189" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C189" s="20"/>
-      <c r="D189" s="21"/>
-      <c r="E189" s="21"/>
-      <c r="F189" s="18"/>
-      <c r="G189" s="18"/>
-      <c r="H189" s="18"/>
-      <c r="I189" s="19"/>
-      <c r="J189" s="25"/>
+      <c r="C189" s="18"/>
+      <c r="D189" s="24"/>
+      <c r="E189" s="24"/>
+      <c r="F189" s="19"/>
+      <c r="G189" s="19"/>
+      <c r="H189" s="19"/>
+      <c r="I189" s="23"/>
+      <c r="J189" s="28"/>
       <c r="L189" s="15" t="s">
         <v>23</v>
       </c>
@@ -7303,26 +7310,26 @@
       <c r="P190" s="10"/>
     </row>
     <row r="191" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C191" s="20" t="s">
+      <c r="C191" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="D191" s="18" t="s">
+      <c r="D191" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E191" s="21"/>
-      <c r="F191" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="G191" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="H191" s="20" t="s">
+      <c r="E191" s="24"/>
+      <c r="F191" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="G191" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="H191" s="18" t="s">
         <v>26</v>
       </c>
       <c r="I191" s="26" t="s">
         <v>49</v>
       </c>
-      <c r="J191" s="20"/>
+      <c r="J191" s="18"/>
       <c r="L191" s="9" t="s">
         <v>0</v>
       </c>
@@ -7345,14 +7352,14 @@
       <c r="U191" s="10"/>
     </row>
     <row r="192" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C192" s="20"/>
-      <c r="D192" s="18"/>
-      <c r="E192" s="21"/>
-      <c r="F192" s="19"/>
-      <c r="G192" s="20"/>
-      <c r="H192" s="20"/>
+      <c r="C192" s="18"/>
+      <c r="D192" s="19"/>
+      <c r="E192" s="24"/>
+      <c r="F192" s="23"/>
+      <c r="G192" s="18"/>
+      <c r="H192" s="18"/>
       <c r="I192" s="27"/>
-      <c r="J192" s="20"/>
+      <c r="J192" s="18"/>
       <c r="L192" s="11" t="s">
         <v>5</v>
       </c>
@@ -7388,14 +7395,14 @@
       </c>
     </row>
     <row r="193" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C193" s="20"/>
-      <c r="D193" s="18"/>
-      <c r="E193" s="21"/>
-      <c r="F193" s="19"/>
-      <c r="G193" s="20"/>
-      <c r="H193" s="20"/>
+      <c r="C193" s="18"/>
+      <c r="D193" s="19"/>
+      <c r="E193" s="24"/>
+      <c r="F193" s="23"/>
+      <c r="G193" s="18"/>
+      <c r="H193" s="18"/>
       <c r="I193" s="27"/>
-      <c r="J193" s="20"/>
+      <c r="J193" s="18"/>
       <c r="L193" s="12" t="s">
         <v>15</v>
       </c>
@@ -7421,14 +7428,14 @@
       </c>
     </row>
     <row r="194" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C194" s="20"/>
-      <c r="D194" s="18"/>
-      <c r="E194" s="21"/>
-      <c r="F194" s="19"/>
-      <c r="G194" s="20"/>
-      <c r="H194" s="20"/>
+      <c r="C194" s="18"/>
+      <c r="D194" s="19"/>
+      <c r="E194" s="24"/>
+      <c r="F194" s="23"/>
+      <c r="G194" s="18"/>
+      <c r="H194" s="18"/>
       <c r="I194" s="27"/>
-      <c r="J194" s="20"/>
+      <c r="J194" s="18"/>
       <c r="L194" s="14" t="s">
         <v>17</v>
       </c>
@@ -7451,14 +7458,14 @@
       <c r="U194" s="10"/>
     </row>
     <row r="195" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C195" s="20"/>
-      <c r="D195" s="18"/>
-      <c r="E195" s="21"/>
-      <c r="F195" s="19"/>
-      <c r="G195" s="20"/>
-      <c r="H195" s="20"/>
+      <c r="C195" s="18"/>
+      <c r="D195" s="19"/>
+      <c r="E195" s="24"/>
+      <c r="F195" s="23"/>
+      <c r="G195" s="18"/>
+      <c r="H195" s="18"/>
       <c r="I195" s="27"/>
-      <c r="J195" s="20"/>
+      <c r="J195" s="18"/>
       <c r="L195" s="15" t="s">
         <v>23</v>
       </c>
@@ -7475,24 +7482,24 @@
       <c r="U195" s="10"/>
     </row>
     <row r="196" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C196" s="20" t="s">
+      <c r="C196" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="D196" s="20"/>
-      <c r="E196" s="20"/>
-      <c r="F196" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="G196" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="H196" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="I196" s="18" t="s">
+      <c r="D196" s="18"/>
+      <c r="E196" s="18"/>
+      <c r="F196" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="G196" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="H196" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="I196" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="J196" s="19" t="s">
+      <c r="J196" s="23" t="s">
         <v>26</v>
       </c>
       <c r="L196" s="9" t="s">
@@ -7517,14 +7524,14 @@
       <c r="U196" s="10"/>
     </row>
     <row r="197" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C197" s="20"/>
-      <c r="D197" s="20"/>
-      <c r="E197" s="20"/>
-      <c r="F197" s="20"/>
-      <c r="G197" s="20"/>
-      <c r="H197" s="20"/>
-      <c r="I197" s="18"/>
-      <c r="J197" s="19"/>
+      <c r="C197" s="18"/>
+      <c r="D197" s="18"/>
+      <c r="E197" s="18"/>
+      <c r="F197" s="18"/>
+      <c r="G197" s="18"/>
+      <c r="H197" s="18"/>
+      <c r="I197" s="19"/>
+      <c r="J197" s="23"/>
       <c r="L197" s="11" t="s">
         <v>5</v>
       </c>
@@ -7563,14 +7570,14 @@
       <c r="A198">
         <v>35</v>
       </c>
-      <c r="C198" s="20"/>
-      <c r="D198" s="20"/>
-      <c r="E198" s="20"/>
-      <c r="F198" s="20"/>
-      <c r="G198" s="20"/>
-      <c r="H198" s="20"/>
-      <c r="I198" s="18"/>
-      <c r="J198" s="19"/>
+      <c r="C198" s="18"/>
+      <c r="D198" s="18"/>
+      <c r="E198" s="18"/>
+      <c r="F198" s="18"/>
+      <c r="G198" s="18"/>
+      <c r="H198" s="18"/>
+      <c r="I198" s="19"/>
+      <c r="J198" s="23"/>
       <c r="L198" s="12" t="s">
         <v>15</v>
       </c>
@@ -7596,14 +7603,14 @@
       </c>
     </row>
     <row r="199" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C199" s="20"/>
-      <c r="D199" s="20"/>
-      <c r="E199" s="20"/>
-      <c r="F199" s="20"/>
-      <c r="G199" s="20"/>
-      <c r="H199" s="20"/>
-      <c r="I199" s="18"/>
-      <c r="J199" s="19"/>
+      <c r="C199" s="18"/>
+      <c r="D199" s="18"/>
+      <c r="E199" s="18"/>
+      <c r="F199" s="18"/>
+      <c r="G199" s="18"/>
+      <c r="H199" s="18"/>
+      <c r="I199" s="19"/>
+      <c r="J199" s="23"/>
       <c r="L199" s="14" t="s">
         <v>17</v>
       </c>
@@ -7626,14 +7633,14 @@
       <c r="U199" s="10"/>
     </row>
     <row r="200" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C200" s="20"/>
-      <c r="D200" s="20"/>
-      <c r="E200" s="20"/>
-      <c r="F200" s="20"/>
-      <c r="G200" s="20"/>
-      <c r="H200" s="20"/>
-      <c r="I200" s="18"/>
-      <c r="J200" s="19"/>
+      <c r="C200" s="18"/>
+      <c r="D200" s="18"/>
+      <c r="E200" s="18"/>
+      <c r="F200" s="18"/>
+      <c r="G200" s="18"/>
+      <c r="H200" s="18"/>
+      <c r="I200" s="19"/>
+      <c r="J200" s="23"/>
       <c r="L200" s="15" t="s">
         <v>23</v>
       </c>
@@ -7653,26 +7660,26 @@
       <c r="B201" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C201" s="20" t="s">
+      <c r="C201" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="D201" s="20"/>
-      <c r="E201" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="F201" s="18" t="s">
+      <c r="D201" s="18"/>
+      <c r="E201" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="F201" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="G201" s="18" t="s">
+      <c r="G201" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="H201" s="18" t="s">
+      <c r="H201" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="I201" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="J201" s="25" t="s">
+      <c r="I201" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="J201" s="28" t="s">
         <v>32</v>
       </c>
       <c r="L201" s="9" t="s">
@@ -7700,14 +7707,14 @@
       <c r="B202">
         <v>13</v>
       </c>
-      <c r="C202" s="20"/>
-      <c r="D202" s="20"/>
-      <c r="E202" s="21"/>
-      <c r="F202" s="18"/>
-      <c r="G202" s="18"/>
-      <c r="H202" s="18"/>
-      <c r="I202" s="19"/>
-      <c r="J202" s="25"/>
+      <c r="C202" s="18"/>
+      <c r="D202" s="18"/>
+      <c r="E202" s="24"/>
+      <c r="F202" s="19"/>
+      <c r="G202" s="19"/>
+      <c r="H202" s="19"/>
+      <c r="I202" s="23"/>
+      <c r="J202" s="28"/>
       <c r="L202" s="11" t="s">
         <v>5</v>
       </c>
@@ -7746,14 +7753,14 @@
       <c r="B203" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="C203" s="20"/>
-      <c r="D203" s="20"/>
-      <c r="E203" s="21"/>
-      <c r="F203" s="18"/>
-      <c r="G203" s="18"/>
-      <c r="H203" s="18"/>
-      <c r="I203" s="19"/>
-      <c r="J203" s="25"/>
+      <c r="C203" s="18"/>
+      <c r="D203" s="18"/>
+      <c r="E203" s="24"/>
+      <c r="F203" s="19"/>
+      <c r="G203" s="19"/>
+      <c r="H203" s="19"/>
+      <c r="I203" s="23"/>
+      <c r="J203" s="28"/>
       <c r="L203" s="12" t="s">
         <v>15</v>
       </c>
@@ -7782,14 +7789,14 @@
       <c r="B204">
         <v>10</v>
       </c>
-      <c r="C204" s="20"/>
-      <c r="D204" s="20"/>
-      <c r="E204" s="21"/>
-      <c r="F204" s="18"/>
-      <c r="G204" s="18"/>
-      <c r="H204" s="18"/>
-      <c r="I204" s="19"/>
-      <c r="J204" s="25"/>
+      <c r="C204" s="18"/>
+      <c r="D204" s="18"/>
+      <c r="E204" s="24"/>
+      <c r="F204" s="19"/>
+      <c r="G204" s="19"/>
+      <c r="H204" s="19"/>
+      <c r="I204" s="23"/>
+      <c r="J204" s="28"/>
       <c r="L204" s="14" t="s">
         <v>17</v>
       </c>
@@ -7814,14 +7821,14 @@
       <c r="U204" s="10"/>
     </row>
     <row r="205" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C205" s="20"/>
-      <c r="D205" s="20"/>
-      <c r="E205" s="21"/>
-      <c r="F205" s="18"/>
-      <c r="G205" s="18"/>
-      <c r="H205" s="18"/>
-      <c r="I205" s="19"/>
-      <c r="J205" s="25"/>
+      <c r="C205" s="18"/>
+      <c r="D205" s="18"/>
+      <c r="E205" s="24"/>
+      <c r="F205" s="19"/>
+      <c r="G205" s="19"/>
+      <c r="H205" s="19"/>
+      <c r="I205" s="23"/>
+      <c r="J205" s="28"/>
       <c r="L205" s="15" t="s">
         <v>23</v>
       </c>
@@ -7845,26 +7852,26 @@
       <c r="P206" s="10"/>
     </row>
     <row r="207" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C207" s="20" t="s">
+      <c r="C207" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="D207" s="18"/>
-      <c r="E207" s="18" t="s">
+      <c r="D207" s="19"/>
+      <c r="E207" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="F207" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="G207" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="H207" s="20" t="s">
+      <c r="F207" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="G207" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="H207" s="18" t="s">
         <v>26</v>
       </c>
       <c r="I207" s="26" t="s">
         <v>49</v>
       </c>
-      <c r="J207" s="20"/>
+      <c r="J207" s="18"/>
       <c r="L207" s="9" t="s">
         <v>0</v>
       </c>
@@ -7887,14 +7894,14 @@
       <c r="U207" s="10"/>
     </row>
     <row r="208" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C208" s="20"/>
-      <c r="D208" s="18"/>
-      <c r="E208" s="18"/>
-      <c r="F208" s="20"/>
-      <c r="G208" s="19"/>
-      <c r="H208" s="20"/>
+      <c r="C208" s="18"/>
+      <c r="D208" s="19"/>
+      <c r="E208" s="19"/>
+      <c r="F208" s="18"/>
+      <c r="G208" s="23"/>
+      <c r="H208" s="18"/>
       <c r="I208" s="27"/>
-      <c r="J208" s="20"/>
+      <c r="J208" s="18"/>
       <c r="L208" s="11" t="s">
         <v>5</v>
       </c>
@@ -7930,14 +7937,14 @@
       </c>
     </row>
     <row r="209" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C209" s="20"/>
-      <c r="D209" s="18"/>
-      <c r="E209" s="18"/>
-      <c r="F209" s="20"/>
-      <c r="G209" s="19"/>
-      <c r="H209" s="20"/>
+      <c r="C209" s="18"/>
+      <c r="D209" s="19"/>
+      <c r="E209" s="19"/>
+      <c r="F209" s="18"/>
+      <c r="G209" s="23"/>
+      <c r="H209" s="18"/>
       <c r="I209" s="27"/>
-      <c r="J209" s="20"/>
+      <c r="J209" s="18"/>
       <c r="L209" s="12" t="s">
         <v>15</v>
       </c>
@@ -7963,14 +7970,14 @@
       </c>
     </row>
     <row r="210" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C210" s="20"/>
-      <c r="D210" s="18"/>
-      <c r="E210" s="18"/>
-      <c r="F210" s="20"/>
-      <c r="G210" s="19"/>
-      <c r="H210" s="20"/>
+      <c r="C210" s="18"/>
+      <c r="D210" s="19"/>
+      <c r="E210" s="19"/>
+      <c r="F210" s="18"/>
+      <c r="G210" s="23"/>
+      <c r="H210" s="18"/>
       <c r="I210" s="27"/>
-      <c r="J210" s="20"/>
+      <c r="J210" s="18"/>
       <c r="L210" s="14" t="s">
         <v>17</v>
       </c>
@@ -7993,14 +8000,14 @@
       <c r="U210" s="10"/>
     </row>
     <row r="211" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C211" s="20"/>
-      <c r="D211" s="18"/>
-      <c r="E211" s="18"/>
-      <c r="F211" s="20"/>
-      <c r="G211" s="19"/>
-      <c r="H211" s="20"/>
+      <c r="C211" s="18"/>
+      <c r="D211" s="19"/>
+      <c r="E211" s="19"/>
+      <c r="F211" s="18"/>
+      <c r="G211" s="23"/>
+      <c r="H211" s="18"/>
       <c r="I211" s="27"/>
-      <c r="J211" s="20"/>
+      <c r="J211" s="18"/>
       <c r="L211" s="15" t="s">
         <v>23</v>
       </c>
@@ -8017,24 +8024,24 @@
       <c r="U211" s="10"/>
     </row>
     <row r="212" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C212" s="20" t="s">
+      <c r="C212" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="D212" s="20"/>
-      <c r="E212" s="20"/>
-      <c r="F212" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="G212" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="H212" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="I212" s="18" t="s">
+      <c r="D212" s="18"/>
+      <c r="E212" s="18"/>
+      <c r="F212" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="G212" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="H212" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="I212" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="J212" s="19" t="s">
+      <c r="J212" s="23" t="s">
         <v>26</v>
       </c>
       <c r="L212" s="9" t="s">
@@ -8059,14 +8066,14 @@
       <c r="U212" s="10"/>
     </row>
     <row r="213" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C213" s="20"/>
-      <c r="D213" s="20"/>
-      <c r="E213" s="20"/>
-      <c r="F213" s="20"/>
-      <c r="G213" s="20"/>
-      <c r="H213" s="20"/>
-      <c r="I213" s="18"/>
-      <c r="J213" s="19"/>
+      <c r="C213" s="18"/>
+      <c r="D213" s="18"/>
+      <c r="E213" s="18"/>
+      <c r="F213" s="18"/>
+      <c r="G213" s="18"/>
+      <c r="H213" s="18"/>
+      <c r="I213" s="19"/>
+      <c r="J213" s="23"/>
       <c r="L213" s="11" t="s">
         <v>5</v>
       </c>
@@ -8102,14 +8109,14 @@
       </c>
     </row>
     <row r="214" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C214" s="20"/>
-      <c r="D214" s="20"/>
-      <c r="E214" s="20"/>
-      <c r="F214" s="20"/>
-      <c r="G214" s="20"/>
-      <c r="H214" s="20"/>
-      <c r="I214" s="18"/>
-      <c r="J214" s="19"/>
+      <c r="C214" s="18"/>
+      <c r="D214" s="18"/>
+      <c r="E214" s="18"/>
+      <c r="F214" s="18"/>
+      <c r="G214" s="18"/>
+      <c r="H214" s="18"/>
+      <c r="I214" s="19"/>
+      <c r="J214" s="23"/>
       <c r="L214" s="12" t="s">
         <v>15</v>
       </c>
@@ -8135,14 +8142,14 @@
       </c>
     </row>
     <row r="215" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C215" s="20"/>
-      <c r="D215" s="20"/>
-      <c r="E215" s="20"/>
-      <c r="F215" s="20"/>
-      <c r="G215" s="20"/>
-      <c r="H215" s="20"/>
-      <c r="I215" s="18"/>
-      <c r="J215" s="19"/>
+      <c r="C215" s="18"/>
+      <c r="D215" s="18"/>
+      <c r="E215" s="18"/>
+      <c r="F215" s="18"/>
+      <c r="G215" s="18"/>
+      <c r="H215" s="18"/>
+      <c r="I215" s="19"/>
+      <c r="J215" s="23"/>
       <c r="L215" s="14" t="s">
         <v>17</v>
       </c>
@@ -8165,14 +8172,14 @@
       <c r="U215" s="10"/>
     </row>
     <row r="216" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C216" s="20"/>
-      <c r="D216" s="20"/>
-      <c r="E216" s="20"/>
-      <c r="F216" s="20"/>
-      <c r="G216" s="20"/>
-      <c r="H216" s="20"/>
-      <c r="I216" s="18"/>
-      <c r="J216" s="19"/>
+      <c r="C216" s="18"/>
+      <c r="D216" s="18"/>
+      <c r="E216" s="18"/>
+      <c r="F216" s="18"/>
+      <c r="G216" s="18"/>
+      <c r="H216" s="18"/>
+      <c r="I216" s="19"/>
+      <c r="J216" s="23"/>
       <c r="L216" s="15" t="s">
         <v>23</v>
       </c>
@@ -8192,26 +8199,26 @@
       <c r="B217" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C217" s="20" t="s">
+      <c r="C217" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="D217" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="E217" s="21"/>
-      <c r="F217" s="18" t="s">
+      <c r="D217" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="E217" s="24"/>
+      <c r="F217" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="G217" s="18" t="s">
+      <c r="G217" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="H217" s="18" t="s">
+      <c r="H217" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="I217" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="J217" s="25" t="s">
+      <c r="I217" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="J217" s="28" t="s">
         <v>32</v>
       </c>
       <c r="L217" s="9" t="s">
@@ -8239,14 +8246,14 @@
       <c r="B218">
         <v>14</v>
       </c>
-      <c r="C218" s="20"/>
-      <c r="D218" s="21"/>
-      <c r="E218" s="21"/>
-      <c r="F218" s="18"/>
-      <c r="G218" s="18"/>
-      <c r="H218" s="18"/>
-      <c r="I218" s="19"/>
-      <c r="J218" s="25"/>
+      <c r="C218" s="18"/>
+      <c r="D218" s="24"/>
+      <c r="E218" s="24"/>
+      <c r="F218" s="19"/>
+      <c r="G218" s="19"/>
+      <c r="H218" s="19"/>
+      <c r="I218" s="23"/>
+      <c r="J218" s="28"/>
       <c r="L218" s="11" t="s">
         <v>5</v>
       </c>
@@ -8285,14 +8292,14 @@
       <c r="B219" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="C219" s="20"/>
-      <c r="D219" s="21"/>
-      <c r="E219" s="21"/>
-      <c r="F219" s="18"/>
-      <c r="G219" s="18"/>
-      <c r="H219" s="18"/>
-      <c r="I219" s="19"/>
-      <c r="J219" s="25"/>
+      <c r="C219" s="18"/>
+      <c r="D219" s="24"/>
+      <c r="E219" s="24"/>
+      <c r="F219" s="19"/>
+      <c r="G219" s="19"/>
+      <c r="H219" s="19"/>
+      <c r="I219" s="23"/>
+      <c r="J219" s="28"/>
       <c r="L219" s="12" t="s">
         <v>15</v>
       </c>
@@ -8321,14 +8328,14 @@
       <c r="B220">
         <v>11</v>
       </c>
-      <c r="C220" s="20"/>
-      <c r="D220" s="21"/>
-      <c r="E220" s="21"/>
-      <c r="F220" s="18"/>
-      <c r="G220" s="18"/>
-      <c r="H220" s="18"/>
-      <c r="I220" s="19"/>
-      <c r="J220" s="25"/>
+      <c r="C220" s="18"/>
+      <c r="D220" s="24"/>
+      <c r="E220" s="24"/>
+      <c r="F220" s="19"/>
+      <c r="G220" s="19"/>
+      <c r="H220" s="19"/>
+      <c r="I220" s="23"/>
+      <c r="J220" s="28"/>
       <c r="L220" s="14" t="s">
         <v>17</v>
       </c>
@@ -8353,14 +8360,14 @@
       <c r="U220" s="10"/>
     </row>
     <row r="221" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C221" s="20"/>
-      <c r="D221" s="21"/>
-      <c r="E221" s="21"/>
-      <c r="F221" s="18"/>
-      <c r="G221" s="18"/>
-      <c r="H221" s="18"/>
-      <c r="I221" s="19"/>
-      <c r="J221" s="25"/>
+      <c r="C221" s="18"/>
+      <c r="D221" s="24"/>
+      <c r="E221" s="24"/>
+      <c r="F221" s="19"/>
+      <c r="G221" s="19"/>
+      <c r="H221" s="19"/>
+      <c r="I221" s="23"/>
+      <c r="J221" s="28"/>
       <c r="L221" s="15" t="s">
         <v>23</v>
       </c>
@@ -8394,26 +8401,26 @@
     </row>
     <row r="225" spans="1:22" x14ac:dyDescent="0.45">
       <c r="B225" s="17"/>
-      <c r="C225" s="20" t="s">
+      <c r="C225" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="D225" s="18" t="s">
+      <c r="D225" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E225" s="21"/>
-      <c r="F225" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="G225" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="H225" s="19" t="s">
+      <c r="E225" s="24"/>
+      <c r="F225" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="G225" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="H225" s="23" t="s">
         <v>26</v>
       </c>
       <c r="I225" s="26" t="s">
         <v>49</v>
       </c>
-      <c r="J225" s="20"/>
+      <c r="J225" s="18"/>
       <c r="L225" s="9" t="s">
         <v>0</v>
       </c>
@@ -8436,14 +8443,14 @@
       <c r="U225" s="10"/>
     </row>
     <row r="226" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C226" s="20"/>
-      <c r="D226" s="18"/>
-      <c r="E226" s="21"/>
-      <c r="F226" s="20"/>
-      <c r="G226" s="20"/>
-      <c r="H226" s="19"/>
+      <c r="C226" s="18"/>
+      <c r="D226" s="19"/>
+      <c r="E226" s="24"/>
+      <c r="F226" s="18"/>
+      <c r="G226" s="18"/>
+      <c r="H226" s="23"/>
       <c r="I226" s="27"/>
-      <c r="J226" s="20"/>
+      <c r="J226" s="18"/>
       <c r="L226" s="11" t="s">
         <v>5</v>
       </c>
@@ -8482,14 +8489,14 @@
       <c r="A227">
         <v>40</v>
       </c>
-      <c r="C227" s="20"/>
-      <c r="D227" s="18"/>
-      <c r="E227" s="21"/>
-      <c r="F227" s="20"/>
-      <c r="G227" s="20"/>
-      <c r="H227" s="19"/>
+      <c r="C227" s="18"/>
+      <c r="D227" s="19"/>
+      <c r="E227" s="24"/>
+      <c r="F227" s="18"/>
+      <c r="G227" s="18"/>
+      <c r="H227" s="23"/>
       <c r="I227" s="27"/>
-      <c r="J227" s="20"/>
+      <c r="J227" s="18"/>
       <c r="L227" s="12" t="s">
         <v>15</v>
       </c>
@@ -8515,14 +8522,14 @@
       </c>
     </row>
     <row r="228" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C228" s="20"/>
-      <c r="D228" s="18"/>
-      <c r="E228" s="21"/>
-      <c r="F228" s="20"/>
-      <c r="G228" s="20"/>
-      <c r="H228" s="19"/>
+      <c r="C228" s="18"/>
+      <c r="D228" s="19"/>
+      <c r="E228" s="24"/>
+      <c r="F228" s="18"/>
+      <c r="G228" s="18"/>
+      <c r="H228" s="23"/>
       <c r="I228" s="27"/>
-      <c r="J228" s="20"/>
+      <c r="J228" s="18"/>
       <c r="L228" s="14" t="s">
         <v>17</v>
       </c>
@@ -8545,14 +8552,14 @@
       <c r="U228" s="10"/>
     </row>
     <row r="229" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C229" s="20"/>
-      <c r="D229" s="18"/>
-      <c r="E229" s="21"/>
-      <c r="F229" s="20"/>
-      <c r="G229" s="20"/>
-      <c r="H229" s="19"/>
+      <c r="C229" s="18"/>
+      <c r="D229" s="19"/>
+      <c r="E229" s="24"/>
+      <c r="F229" s="18"/>
+      <c r="G229" s="18"/>
+      <c r="H229" s="23"/>
       <c r="I229" s="27"/>
-      <c r="J229" s="20"/>
+      <c r="J229" s="18"/>
       <c r="L229" s="15" t="s">
         <v>23</v>
       </c>
@@ -8569,24 +8576,24 @@
       <c r="U229" s="10"/>
     </row>
     <row r="230" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C230" s="20" t="s">
+      <c r="C230" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="D230" s="20"/>
-      <c r="E230" s="20"/>
-      <c r="F230" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="G230" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="H230" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="I230" s="18" t="s">
+      <c r="D230" s="18"/>
+      <c r="E230" s="18"/>
+      <c r="F230" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="G230" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="H230" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="I230" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="J230" s="19" t="s">
+      <c r="J230" s="23" t="s">
         <v>26</v>
       </c>
       <c r="L230" s="9" t="s">
@@ -8611,14 +8618,14 @@
       <c r="U230" s="10"/>
     </row>
     <row r="231" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C231" s="20"/>
-      <c r="D231" s="20"/>
-      <c r="E231" s="20"/>
-      <c r="F231" s="20"/>
-      <c r="G231" s="20"/>
-      <c r="H231" s="20"/>
-      <c r="I231" s="18"/>
-      <c r="J231" s="19"/>
+      <c r="C231" s="18"/>
+      <c r="D231" s="18"/>
+      <c r="E231" s="18"/>
+      <c r="F231" s="18"/>
+      <c r="G231" s="18"/>
+      <c r="H231" s="18"/>
+      <c r="I231" s="19"/>
+      <c r="J231" s="23"/>
       <c r="L231" s="11" t="s">
         <v>5</v>
       </c>
@@ -8654,14 +8661,14 @@
       </c>
     </row>
     <row r="232" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C232" s="20"/>
-      <c r="D232" s="20"/>
-      <c r="E232" s="20"/>
-      <c r="F232" s="20"/>
-      <c r="G232" s="20"/>
-      <c r="H232" s="20"/>
-      <c r="I232" s="18"/>
-      <c r="J232" s="19"/>
+      <c r="C232" s="18"/>
+      <c r="D232" s="18"/>
+      <c r="E232" s="18"/>
+      <c r="F232" s="18"/>
+      <c r="G232" s="18"/>
+      <c r="H232" s="18"/>
+      <c r="I232" s="19"/>
+      <c r="J232" s="23"/>
       <c r="L232" s="12" t="s">
         <v>15</v>
       </c>
@@ -8687,14 +8694,14 @@
       </c>
     </row>
     <row r="233" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C233" s="20"/>
-      <c r="D233" s="20"/>
-      <c r="E233" s="20"/>
-      <c r="F233" s="20"/>
-      <c r="G233" s="20"/>
-      <c r="H233" s="20"/>
-      <c r="I233" s="18"/>
-      <c r="J233" s="19"/>
+      <c r="C233" s="18"/>
+      <c r="D233" s="18"/>
+      <c r="E233" s="18"/>
+      <c r="F233" s="18"/>
+      <c r="G233" s="18"/>
+      <c r="H233" s="18"/>
+      <c r="I233" s="19"/>
+      <c r="J233" s="23"/>
       <c r="L233" s="14" t="s">
         <v>17</v>
       </c>
@@ -8717,14 +8724,14 @@
       <c r="U233" s="10"/>
     </row>
     <row r="234" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C234" s="20"/>
-      <c r="D234" s="20"/>
-      <c r="E234" s="20"/>
-      <c r="F234" s="20"/>
-      <c r="G234" s="20"/>
-      <c r="H234" s="20"/>
-      <c r="I234" s="18"/>
-      <c r="J234" s="19"/>
+      <c r="C234" s="18"/>
+      <c r="D234" s="18"/>
+      <c r="E234" s="18"/>
+      <c r="F234" s="18"/>
+      <c r="G234" s="18"/>
+      <c r="H234" s="18"/>
+      <c r="I234" s="19"/>
+      <c r="J234" s="23"/>
       <c r="L234" s="15" t="s">
         <v>23</v>
       </c>
@@ -8744,26 +8751,26 @@
       <c r="B235" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C235" s="20" t="s">
+      <c r="C235" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="D235" s="20"/>
-      <c r="E235" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="F235" s="18" t="s">
+      <c r="D235" s="18"/>
+      <c r="E235" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="F235" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="G235" s="18" t="s">
+      <c r="G235" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="H235" s="18" t="s">
+      <c r="H235" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="I235" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="J235" s="25" t="s">
+      <c r="I235" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="J235" s="28" t="s">
         <v>32</v>
       </c>
       <c r="L235" s="9" t="s">
@@ -8791,14 +8798,14 @@
       <c r="B236">
         <v>15</v>
       </c>
-      <c r="C236" s="20"/>
-      <c r="D236" s="20"/>
-      <c r="E236" s="21"/>
-      <c r="F236" s="18"/>
-      <c r="G236" s="18"/>
-      <c r="H236" s="18"/>
-      <c r="I236" s="19"/>
-      <c r="J236" s="25"/>
+      <c r="C236" s="18"/>
+      <c r="D236" s="18"/>
+      <c r="E236" s="24"/>
+      <c r="F236" s="19"/>
+      <c r="G236" s="19"/>
+      <c r="H236" s="19"/>
+      <c r="I236" s="23"/>
+      <c r="J236" s="28"/>
       <c r="L236" s="11" t="s">
         <v>5</v>
       </c>
@@ -8837,14 +8844,14 @@
       <c r="B237" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="C237" s="20"/>
-      <c r="D237" s="20"/>
-      <c r="E237" s="21"/>
-      <c r="F237" s="18"/>
-      <c r="G237" s="18"/>
-      <c r="H237" s="18"/>
-      <c r="I237" s="19"/>
-      <c r="J237" s="25"/>
+      <c r="C237" s="18"/>
+      <c r="D237" s="18"/>
+      <c r="E237" s="24"/>
+      <c r="F237" s="19"/>
+      <c r="G237" s="19"/>
+      <c r="H237" s="19"/>
+      <c r="I237" s="23"/>
+      <c r="J237" s="28"/>
       <c r="L237" s="12" t="s">
         <v>15</v>
       </c>
@@ -8873,14 +8880,14 @@
       <c r="B238">
         <v>12</v>
       </c>
-      <c r="C238" s="20"/>
-      <c r="D238" s="20"/>
-      <c r="E238" s="21"/>
-      <c r="F238" s="18"/>
-      <c r="G238" s="18"/>
-      <c r="H238" s="18"/>
-      <c r="I238" s="19"/>
-      <c r="J238" s="25"/>
+      <c r="C238" s="18"/>
+      <c r="D238" s="18"/>
+      <c r="E238" s="24"/>
+      <c r="F238" s="19"/>
+      <c r="G238" s="19"/>
+      <c r="H238" s="19"/>
+      <c r="I238" s="23"/>
+      <c r="J238" s="28"/>
       <c r="L238" s="14" t="s">
         <v>17</v>
       </c>
@@ -8905,14 +8912,14 @@
       <c r="U238" s="10"/>
     </row>
     <row r="239" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C239" s="20"/>
-      <c r="D239" s="20"/>
-      <c r="E239" s="21"/>
-      <c r="F239" s="18"/>
-      <c r="G239" s="18"/>
-      <c r="H239" s="18"/>
-      <c r="I239" s="19"/>
-      <c r="J239" s="25"/>
+      <c r="C239" s="18"/>
+      <c r="D239" s="18"/>
+      <c r="E239" s="24"/>
+      <c r="F239" s="19"/>
+      <c r="G239" s="19"/>
+      <c r="H239" s="19"/>
+      <c r="I239" s="23"/>
+      <c r="J239" s="28"/>
       <c r="L239" s="15" t="s">
         <v>23</v>
       </c>
@@ -8936,26 +8943,26 @@
       <c r="P240" s="10"/>
     </row>
     <row r="241" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C241" s="20" t="s">
+      <c r="C241" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="D241" s="18"/>
-      <c r="E241" s="18" t="s">
+      <c r="D241" s="19"/>
+      <c r="E241" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="F241" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="G241" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="H241" s="20" t="s">
+      <c r="F241" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="G241" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="H241" s="18" t="s">
         <v>26</v>
       </c>
       <c r="I241" s="26" t="s">
         <v>49</v>
       </c>
-      <c r="J241" s="20"/>
+      <c r="J241" s="18"/>
       <c r="L241" s="9" t="s">
         <v>0</v>
       </c>
@@ -8978,14 +8985,14 @@
       <c r="U241" s="10"/>
     </row>
     <row r="242" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C242" s="20"/>
-      <c r="D242" s="18"/>
-      <c r="E242" s="18"/>
-      <c r="F242" s="19"/>
-      <c r="G242" s="20"/>
-      <c r="H242" s="20"/>
+      <c r="C242" s="18"/>
+      <c r="D242" s="19"/>
+      <c r="E242" s="19"/>
+      <c r="F242" s="23"/>
+      <c r="G242" s="18"/>
+      <c r="H242" s="18"/>
       <c r="I242" s="27"/>
-      <c r="J242" s="20"/>
+      <c r="J242" s="18"/>
       <c r="L242" s="11" t="s">
         <v>5</v>
       </c>
@@ -9021,14 +9028,14 @@
       </c>
     </row>
     <row r="243" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C243" s="20"/>
-      <c r="D243" s="18"/>
-      <c r="E243" s="18"/>
-      <c r="F243" s="19"/>
-      <c r="G243" s="20"/>
-      <c r="H243" s="20"/>
+      <c r="C243" s="18"/>
+      <c r="D243" s="19"/>
+      <c r="E243" s="19"/>
+      <c r="F243" s="23"/>
+      <c r="G243" s="18"/>
+      <c r="H243" s="18"/>
       <c r="I243" s="27"/>
-      <c r="J243" s="20"/>
+      <c r="J243" s="18"/>
       <c r="L243" s="12" t="s">
         <v>15</v>
       </c>
@@ -9054,14 +9061,14 @@
       </c>
     </row>
     <row r="244" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C244" s="20"/>
-      <c r="D244" s="18"/>
-      <c r="E244" s="18"/>
-      <c r="F244" s="19"/>
-      <c r="G244" s="20"/>
-      <c r="H244" s="20"/>
+      <c r="C244" s="18"/>
+      <c r="D244" s="19"/>
+      <c r="E244" s="19"/>
+      <c r="F244" s="23"/>
+      <c r="G244" s="18"/>
+      <c r="H244" s="18"/>
       <c r="I244" s="27"/>
-      <c r="J244" s="20"/>
+      <c r="J244" s="18"/>
       <c r="L244" s="14" t="s">
         <v>17</v>
       </c>
@@ -9084,14 +9091,14 @@
       <c r="U244" s="10"/>
     </row>
     <row r="245" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C245" s="20"/>
-      <c r="D245" s="18"/>
-      <c r="E245" s="18"/>
-      <c r="F245" s="19"/>
-      <c r="G245" s="20"/>
-      <c r="H245" s="20"/>
+      <c r="C245" s="18"/>
+      <c r="D245" s="19"/>
+      <c r="E245" s="19"/>
+      <c r="F245" s="23"/>
+      <c r="G245" s="18"/>
+      <c r="H245" s="18"/>
       <c r="I245" s="27"/>
-      <c r="J245" s="20"/>
+      <c r="J245" s="18"/>
       <c r="L245" s="15" t="s">
         <v>23</v>
       </c>
@@ -9108,24 +9115,24 @@
       <c r="U245" s="10"/>
     </row>
     <row r="246" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C246" s="20" t="s">
+      <c r="C246" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="D246" s="20"/>
-      <c r="E246" s="20"/>
-      <c r="F246" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="G246" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="H246" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="I246" s="18" t="s">
+      <c r="D246" s="18"/>
+      <c r="E246" s="18"/>
+      <c r="F246" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="G246" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="H246" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="I246" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="J246" s="19" t="s">
+      <c r="J246" s="23" t="s">
         <v>26</v>
       </c>
       <c r="L246" s="9" t="s">
@@ -9150,14 +9157,14 @@
       <c r="U246" s="10"/>
     </row>
     <row r="247" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C247" s="20"/>
-      <c r="D247" s="20"/>
-      <c r="E247" s="20"/>
-      <c r="F247" s="20"/>
-      <c r="G247" s="20"/>
-      <c r="H247" s="20"/>
-      <c r="I247" s="18"/>
-      <c r="J247" s="19"/>
+      <c r="C247" s="18"/>
+      <c r="D247" s="18"/>
+      <c r="E247" s="18"/>
+      <c r="F247" s="18"/>
+      <c r="G247" s="18"/>
+      <c r="H247" s="18"/>
+      <c r="I247" s="19"/>
+      <c r="J247" s="23"/>
       <c r="L247" s="11" t="s">
         <v>5</v>
       </c>
@@ -9193,14 +9200,14 @@
       </c>
     </row>
     <row r="248" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C248" s="20"/>
-      <c r="D248" s="20"/>
-      <c r="E248" s="20"/>
-      <c r="F248" s="20"/>
-      <c r="G248" s="20"/>
-      <c r="H248" s="20"/>
-      <c r="I248" s="18"/>
-      <c r="J248" s="19"/>
+      <c r="C248" s="18"/>
+      <c r="D248" s="18"/>
+      <c r="E248" s="18"/>
+      <c r="F248" s="18"/>
+      <c r="G248" s="18"/>
+      <c r="H248" s="18"/>
+      <c r="I248" s="19"/>
+      <c r="J248" s="23"/>
       <c r="L248" s="12" t="s">
         <v>15</v>
       </c>
@@ -9226,14 +9233,14 @@
       </c>
     </row>
     <row r="249" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C249" s="20"/>
-      <c r="D249" s="20"/>
-      <c r="E249" s="20"/>
-      <c r="F249" s="20"/>
-      <c r="G249" s="20"/>
-      <c r="H249" s="20"/>
-      <c r="I249" s="18"/>
-      <c r="J249" s="19"/>
+      <c r="C249" s="18"/>
+      <c r="D249" s="18"/>
+      <c r="E249" s="18"/>
+      <c r="F249" s="18"/>
+      <c r="G249" s="18"/>
+      <c r="H249" s="18"/>
+      <c r="I249" s="19"/>
+      <c r="J249" s="23"/>
       <c r="L249" s="14" t="s">
         <v>17</v>
       </c>
@@ -9256,14 +9263,14 @@
       <c r="U249" s="10"/>
     </row>
     <row r="250" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C250" s="20"/>
-      <c r="D250" s="20"/>
-      <c r="E250" s="20"/>
-      <c r="F250" s="20"/>
-      <c r="G250" s="20"/>
-      <c r="H250" s="20"/>
-      <c r="I250" s="18"/>
-      <c r="J250" s="19"/>
+      <c r="C250" s="18"/>
+      <c r="D250" s="18"/>
+      <c r="E250" s="18"/>
+      <c r="F250" s="18"/>
+      <c r="G250" s="18"/>
+      <c r="H250" s="18"/>
+      <c r="I250" s="19"/>
+      <c r="J250" s="23"/>
       <c r="L250" s="15" t="s">
         <v>23</v>
       </c>
@@ -9280,24 +9287,24 @@
       <c r="U250" s="10"/>
     </row>
     <row r="251" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C251" s="20" t="s">
+      <c r="C251" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="D251" s="20"/>
-      <c r="E251" s="21"/>
-      <c r="F251" s="18" t="s">
+      <c r="D251" s="18"/>
+      <c r="E251" s="24"/>
+      <c r="F251" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="G251" s="18" t="s">
+      <c r="G251" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="H251" s="18" t="s">
+      <c r="H251" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="I251" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="J251" s="25" t="s">
+      <c r="I251" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="J251" s="28" t="s">
         <v>32</v>
       </c>
       <c r="L251" s="9" t="s">
@@ -9322,14 +9329,14 @@
       <c r="U251" s="10"/>
     </row>
     <row r="252" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C252" s="20"/>
-      <c r="D252" s="20"/>
-      <c r="E252" s="21"/>
-      <c r="F252" s="18"/>
-      <c r="G252" s="18"/>
-      <c r="H252" s="18"/>
-      <c r="I252" s="19"/>
-      <c r="J252" s="25"/>
+      <c r="C252" s="18"/>
+      <c r="D252" s="18"/>
+      <c r="E252" s="24"/>
+      <c r="F252" s="19"/>
+      <c r="G252" s="19"/>
+      <c r="H252" s="19"/>
+      <c r="I252" s="23"/>
+      <c r="J252" s="28"/>
       <c r="L252" s="11" t="s">
         <v>5</v>
       </c>
@@ -9371,14 +9378,14 @@
       <c r="B253" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="C253" s="20"/>
-      <c r="D253" s="20"/>
-      <c r="E253" s="21"/>
-      <c r="F253" s="18"/>
-      <c r="G253" s="18"/>
-      <c r="H253" s="18"/>
-      <c r="I253" s="19"/>
-      <c r="J253" s="25"/>
+      <c r="C253" s="18"/>
+      <c r="D253" s="18"/>
+      <c r="E253" s="24"/>
+      <c r="F253" s="19"/>
+      <c r="G253" s="19"/>
+      <c r="H253" s="19"/>
+      <c r="I253" s="23"/>
+      <c r="J253" s="28"/>
       <c r="L253" s="12" t="s">
         <v>15</v>
       </c>
@@ -9407,14 +9414,14 @@
       <c r="B254">
         <v>13</v>
       </c>
-      <c r="C254" s="20"/>
-      <c r="D254" s="20"/>
-      <c r="E254" s="21"/>
-      <c r="F254" s="18"/>
-      <c r="G254" s="18"/>
-      <c r="H254" s="18"/>
-      <c r="I254" s="19"/>
-      <c r="J254" s="25"/>
+      <c r="C254" s="18"/>
+      <c r="D254" s="18"/>
+      <c r="E254" s="24"/>
+      <c r="F254" s="19"/>
+      <c r="G254" s="19"/>
+      <c r="H254" s="19"/>
+      <c r="I254" s="23"/>
+      <c r="J254" s="28"/>
       <c r="L254" s="14" t="s">
         <v>17</v>
       </c>
@@ -9438,14 +9445,14 @@
       <c r="U254" s="10"/>
     </row>
     <row r="255" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C255" s="20"/>
-      <c r="D255" s="20"/>
-      <c r="E255" s="21"/>
-      <c r="F255" s="18"/>
-      <c r="G255" s="18"/>
-      <c r="H255" s="18"/>
-      <c r="I255" s="19"/>
-      <c r="J255" s="25"/>
+      <c r="C255" s="18"/>
+      <c r="D255" s="18"/>
+      <c r="E255" s="24"/>
+      <c r="F255" s="19"/>
+      <c r="G255" s="19"/>
+      <c r="H255" s="19"/>
+      <c r="I255" s="23"/>
+      <c r="J255" s="28"/>
       <c r="L255" s="15" t="s">
         <v>23</v>
       </c>
@@ -9467,22 +9474,22 @@
       <c r="P256" s="10"/>
     </row>
     <row r="257" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C257" s="20" t="s">
+      <c r="C257" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="D257" s="18"/>
-      <c r="E257" s="21"/>
-      <c r="F257" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="G257" s="20"/>
-      <c r="H257" s="20" t="s">
+      <c r="D257" s="19"/>
+      <c r="E257" s="24"/>
+      <c r="F257" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="G257" s="18"/>
+      <c r="H257" s="18" t="s">
         <v>26</v>
       </c>
       <c r="I257" s="26" t="s">
         <v>49</v>
       </c>
-      <c r="J257" s="20"/>
+      <c r="J257" s="18"/>
       <c r="L257" s="9" t="s">
         <v>0</v>
       </c>
@@ -9505,14 +9512,14 @@
       <c r="U257" s="10"/>
     </row>
     <row r="258" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C258" s="20"/>
-      <c r="D258" s="18"/>
-      <c r="E258" s="21"/>
-      <c r="F258" s="20"/>
-      <c r="G258" s="20"/>
-      <c r="H258" s="20"/>
+      <c r="C258" s="18"/>
+      <c r="D258" s="19"/>
+      <c r="E258" s="24"/>
+      <c r="F258" s="18"/>
+      <c r="G258" s="18"/>
+      <c r="H258" s="18"/>
       <c r="I258" s="27"/>
-      <c r="J258" s="20"/>
+      <c r="J258" s="18"/>
       <c r="L258" s="11" t="s">
         <v>5</v>
       </c>
@@ -9548,14 +9555,14 @@
       </c>
     </row>
     <row r="259" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C259" s="20"/>
-      <c r="D259" s="18"/>
-      <c r="E259" s="21"/>
-      <c r="F259" s="20"/>
-      <c r="G259" s="20"/>
-      <c r="H259" s="20"/>
+      <c r="C259" s="18"/>
+      <c r="D259" s="19"/>
+      <c r="E259" s="24"/>
+      <c r="F259" s="18"/>
+      <c r="G259" s="18"/>
+      <c r="H259" s="18"/>
       <c r="I259" s="27"/>
-      <c r="J259" s="20"/>
+      <c r="J259" s="18"/>
       <c r="L259" s="12" t="s">
         <v>15</v>
       </c>
@@ -9573,14 +9580,14 @@
       <c r="V259" s="10"/>
     </row>
     <row r="260" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C260" s="20"/>
-      <c r="D260" s="18"/>
-      <c r="E260" s="21"/>
-      <c r="F260" s="20"/>
-      <c r="G260" s="20"/>
-      <c r="H260" s="20"/>
+      <c r="C260" s="18"/>
+      <c r="D260" s="19"/>
+      <c r="E260" s="24"/>
+      <c r="F260" s="18"/>
+      <c r="G260" s="18"/>
+      <c r="H260" s="18"/>
       <c r="I260" s="27"/>
-      <c r="J260" s="20"/>
+      <c r="J260" s="18"/>
       <c r="L260" s="14" t="s">
         <v>17</v>
       </c>
@@ -9603,14 +9610,14 @@
       <c r="U260" s="10"/>
     </row>
     <row r="261" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C261" s="20"/>
-      <c r="D261" s="18"/>
-      <c r="E261" s="21"/>
-      <c r="F261" s="20"/>
-      <c r="G261" s="20"/>
-      <c r="H261" s="20"/>
+      <c r="C261" s="18"/>
+      <c r="D261" s="19"/>
+      <c r="E261" s="24"/>
+      <c r="F261" s="18"/>
+      <c r="G261" s="18"/>
+      <c r="H261" s="18"/>
       <c r="I261" s="27"/>
-      <c r="J261" s="20"/>
+      <c r="J261" s="18"/>
       <c r="L261" s="15" t="s">
         <v>23</v>
       </c>
@@ -9627,22 +9634,22 @@
       <c r="U261" s="10"/>
     </row>
     <row r="262" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C262" s="20" t="s">
+      <c r="C262" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="D262" s="20"/>
-      <c r="E262" s="20"/>
-      <c r="F262" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="G262" s="20"/>
-      <c r="H262" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="I262" s="18" t="s">
+      <c r="D262" s="18"/>
+      <c r="E262" s="18"/>
+      <c r="F262" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="G262" s="18"/>
+      <c r="H262" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="I262" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="J262" s="19" t="s">
+      <c r="J262" s="23" t="s">
         <v>26</v>
       </c>
       <c r="L262" s="9" t="s">
@@ -9667,14 +9674,14 @@
       <c r="U262" s="10"/>
     </row>
     <row r="263" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C263" s="20"/>
-      <c r="D263" s="20"/>
-      <c r="E263" s="20"/>
-      <c r="F263" s="20"/>
-      <c r="G263" s="20"/>
-      <c r="H263" s="20"/>
-      <c r="I263" s="18"/>
-      <c r="J263" s="19"/>
+      <c r="C263" s="18"/>
+      <c r="D263" s="18"/>
+      <c r="E263" s="18"/>
+      <c r="F263" s="18"/>
+      <c r="G263" s="18"/>
+      <c r="H263" s="18"/>
+      <c r="I263" s="19"/>
+      <c r="J263" s="23"/>
       <c r="L263" s="11" t="s">
         <v>5</v>
       </c>
@@ -9710,14 +9717,14 @@
       </c>
     </row>
     <row r="264" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C264" s="20"/>
-      <c r="D264" s="20"/>
-      <c r="E264" s="20"/>
-      <c r="F264" s="20"/>
-      <c r="G264" s="20"/>
-      <c r="H264" s="20"/>
-      <c r="I264" s="18"/>
-      <c r="J264" s="19"/>
+      <c r="C264" s="18"/>
+      <c r="D264" s="18"/>
+      <c r="E264" s="18"/>
+      <c r="F264" s="18"/>
+      <c r="G264" s="18"/>
+      <c r="H264" s="18"/>
+      <c r="I264" s="19"/>
+      <c r="J264" s="23"/>
       <c r="L264" s="12" t="s">
         <v>15</v>
       </c>
@@ -9743,14 +9750,14 @@
       </c>
     </row>
     <row r="265" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C265" s="20"/>
-      <c r="D265" s="20"/>
-      <c r="E265" s="20"/>
-      <c r="F265" s="20"/>
-      <c r="G265" s="20"/>
-      <c r="H265" s="20"/>
-      <c r="I265" s="18"/>
-      <c r="J265" s="19"/>
+      <c r="C265" s="18"/>
+      <c r="D265" s="18"/>
+      <c r="E265" s="18"/>
+      <c r="F265" s="18"/>
+      <c r="G265" s="18"/>
+      <c r="H265" s="18"/>
+      <c r="I265" s="19"/>
+      <c r="J265" s="23"/>
       <c r="L265" s="14" t="s">
         <v>17</v>
       </c>
@@ -9773,14 +9780,14 @@
       <c r="U265" s="10"/>
     </row>
     <row r="266" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C266" s="20"/>
-      <c r="D266" s="20"/>
-      <c r="E266" s="20"/>
-      <c r="F266" s="20"/>
-      <c r="G266" s="20"/>
-      <c r="H266" s="20"/>
-      <c r="I266" s="18"/>
-      <c r="J266" s="19"/>
+      <c r="C266" s="18"/>
+      <c r="D266" s="18"/>
+      <c r="E266" s="18"/>
+      <c r="F266" s="18"/>
+      <c r="G266" s="18"/>
+      <c r="H266" s="18"/>
+      <c r="I266" s="19"/>
+      <c r="J266" s="23"/>
       <c r="L266" s="15" t="s">
         <v>23</v>
       </c>
@@ -9797,22 +9804,22 @@
       <c r="U266" s="10"/>
     </row>
     <row r="267" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C267" s="20" t="s">
+      <c r="C267" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="D267" s="20"/>
-      <c r="E267" s="21"/>
-      <c r="F267" s="18" t="s">
+      <c r="D267" s="18"/>
+      <c r="E267" s="24"/>
+      <c r="F267" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="G267" s="18"/>
-      <c r="H267" s="18" t="s">
+      <c r="G267" s="19"/>
+      <c r="H267" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="I267" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="J267" s="25" t="s">
+      <c r="I267" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="J267" s="28" t="s">
         <v>32</v>
       </c>
       <c r="L267" s="9" t="s">
@@ -9837,14 +9844,14 @@
       <c r="U267" s="10"/>
     </row>
     <row r="268" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C268" s="20"/>
-      <c r="D268" s="20"/>
-      <c r="E268" s="21"/>
-      <c r="F268" s="18"/>
-      <c r="G268" s="18"/>
-      <c r="H268" s="18"/>
-      <c r="I268" s="19"/>
-      <c r="J268" s="25"/>
+      <c r="C268" s="18"/>
+      <c r="D268" s="18"/>
+      <c r="E268" s="24"/>
+      <c r="F268" s="19"/>
+      <c r="G268" s="19"/>
+      <c r="H268" s="19"/>
+      <c r="I268" s="23"/>
+      <c r="J268" s="28"/>
       <c r="L268" s="11" t="s">
         <v>5</v>
       </c>
@@ -9883,14 +9890,14 @@
       <c r="B269" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="C269" s="20"/>
-      <c r="D269" s="20"/>
-      <c r="E269" s="21"/>
-      <c r="F269" s="18"/>
-      <c r="G269" s="18"/>
-      <c r="H269" s="18"/>
-      <c r="I269" s="19"/>
-      <c r="J269" s="25"/>
+      <c r="C269" s="18"/>
+      <c r="D269" s="18"/>
+      <c r="E269" s="24"/>
+      <c r="F269" s="19"/>
+      <c r="G269" s="19"/>
+      <c r="H269" s="19"/>
+      <c r="I269" s="23"/>
+      <c r="J269" s="28"/>
       <c r="L269" s="12" t="s">
         <v>15</v>
       </c>
@@ -9919,14 +9926,14 @@
       <c r="B270">
         <v>14</v>
       </c>
-      <c r="C270" s="20"/>
-      <c r="D270" s="20"/>
-      <c r="E270" s="21"/>
-      <c r="F270" s="18"/>
-      <c r="G270" s="18"/>
-      <c r="H270" s="18"/>
-      <c r="I270" s="19"/>
-      <c r="J270" s="25"/>
+      <c r="C270" s="18"/>
+      <c r="D270" s="18"/>
+      <c r="E270" s="24"/>
+      <c r="F270" s="19"/>
+      <c r="G270" s="19"/>
+      <c r="H270" s="19"/>
+      <c r="I270" s="23"/>
+      <c r="J270" s="28"/>
       <c r="L270" s="14" t="s">
         <v>17</v>
       </c>
@@ -9950,14 +9957,14 @@
       <c r="U270" s="10"/>
     </row>
     <row r="271" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C271" s="20"/>
-      <c r="D271" s="20"/>
-      <c r="E271" s="21"/>
-      <c r="F271" s="18"/>
-      <c r="G271" s="18"/>
-      <c r="H271" s="18"/>
-      <c r="I271" s="19"/>
-      <c r="J271" s="25"/>
+      <c r="C271" s="18"/>
+      <c r="D271" s="18"/>
+      <c r="E271" s="24"/>
+      <c r="F271" s="19"/>
+      <c r="G271" s="19"/>
+      <c r="H271" s="19"/>
+      <c r="I271" s="23"/>
+      <c r="J271" s="28"/>
       <c r="L271" s="15" t="s">
         <v>23</v>
       </c>
@@ -9979,18 +9986,18 @@
       <c r="P272" s="10"/>
     </row>
     <row r="273" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C273" s="20" t="s">
+      <c r="C273" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="D273" s="20"/>
-      <c r="E273" s="21"/>
-      <c r="F273" s="21"/>
-      <c r="G273" s="20"/>
-      <c r="H273" s="20"/>
+      <c r="D273" s="18"/>
+      <c r="E273" s="24"/>
+      <c r="F273" s="24"/>
+      <c r="G273" s="18"/>
+      <c r="H273" s="18"/>
       <c r="I273" s="26" t="s">
         <v>49</v>
       </c>
-      <c r="J273" s="20"/>
+      <c r="J273" s="18"/>
       <c r="L273" s="9" t="s">
         <v>0</v>
       </c>
@@ -10013,14 +10020,14 @@
       <c r="U273" s="10"/>
     </row>
     <row r="274" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C274" s="20"/>
-      <c r="D274" s="20"/>
-      <c r="E274" s="21"/>
-      <c r="F274" s="21"/>
-      <c r="G274" s="20"/>
-      <c r="H274" s="20"/>
+      <c r="C274" s="18"/>
+      <c r="D274" s="18"/>
+      <c r="E274" s="24"/>
+      <c r="F274" s="24"/>
+      <c r="G274" s="18"/>
+      <c r="H274" s="18"/>
       <c r="I274" s="27"/>
-      <c r="J274" s="20"/>
+      <c r="J274" s="18"/>
       <c r="L274" s="11" t="s">
         <v>5</v>
       </c>
@@ -10056,14 +10063,14 @@
       </c>
     </row>
     <row r="275" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C275" s="20"/>
-      <c r="D275" s="20"/>
-      <c r="E275" s="21"/>
-      <c r="F275" s="21"/>
-      <c r="G275" s="20"/>
-      <c r="H275" s="20"/>
+      <c r="C275" s="18"/>
+      <c r="D275" s="18"/>
+      <c r="E275" s="24"/>
+      <c r="F275" s="24"/>
+      <c r="G275" s="18"/>
+      <c r="H275" s="18"/>
       <c r="I275" s="27"/>
-      <c r="J275" s="20"/>
+      <c r="J275" s="18"/>
       <c r="L275" s="12" t="s">
         <v>15</v>
       </c>
@@ -10081,14 +10088,14 @@
       <c r="V275" s="10"/>
     </row>
     <row r="276" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C276" s="20"/>
-      <c r="D276" s="20"/>
-      <c r="E276" s="21"/>
-      <c r="F276" s="21"/>
-      <c r="G276" s="20"/>
-      <c r="H276" s="20"/>
+      <c r="C276" s="18"/>
+      <c r="D276" s="18"/>
+      <c r="E276" s="24"/>
+      <c r="F276" s="24"/>
+      <c r="G276" s="18"/>
+      <c r="H276" s="18"/>
       <c r="I276" s="27"/>
-      <c r="J276" s="20"/>
+      <c r="J276" s="18"/>
       <c r="L276" s="14" t="s">
         <v>17</v>
       </c>
@@ -10111,14 +10118,14 @@
       <c r="U276" s="10"/>
     </row>
     <row r="277" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C277" s="20"/>
-      <c r="D277" s="20"/>
-      <c r="E277" s="21"/>
-      <c r="F277" s="21"/>
-      <c r="G277" s="20"/>
-      <c r="H277" s="20"/>
+      <c r="C277" s="18"/>
+      <c r="D277" s="18"/>
+      <c r="E277" s="24"/>
+      <c r="F277" s="24"/>
+      <c r="G277" s="18"/>
+      <c r="H277" s="18"/>
       <c r="I277" s="27"/>
-      <c r="J277" s="20"/>
+      <c r="J277" s="18"/>
       <c r="L277" s="15" t="s">
         <v>23</v>
       </c>
@@ -10135,18 +10142,18 @@
       <c r="U277" s="10"/>
     </row>
     <row r="278" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C278" s="20" t="s">
+      <c r="C278" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="D278" s="20"/>
-      <c r="E278" s="21"/>
-      <c r="F278" s="21"/>
-      <c r="G278" s="20"/>
-      <c r="H278" s="20"/>
-      <c r="I278" s="18" t="s">
+      <c r="D278" s="18"/>
+      <c r="E278" s="24"/>
+      <c r="F278" s="24"/>
+      <c r="G278" s="18"/>
+      <c r="H278" s="18"/>
+      <c r="I278" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="J278" s="19" t="s">
+      <c r="J278" s="23" t="s">
         <v>26</v>
       </c>
       <c r="L278" s="9" t="s">
@@ -10171,14 +10178,14 @@
       <c r="U278" s="10"/>
     </row>
     <row r="279" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C279" s="20"/>
-      <c r="D279" s="20"/>
-      <c r="E279" s="21"/>
-      <c r="F279" s="21"/>
-      <c r="G279" s="20"/>
-      <c r="H279" s="20"/>
-      <c r="I279" s="18"/>
-      <c r="J279" s="19"/>
+      <c r="C279" s="18"/>
+      <c r="D279" s="18"/>
+      <c r="E279" s="24"/>
+      <c r="F279" s="24"/>
+      <c r="G279" s="18"/>
+      <c r="H279" s="18"/>
+      <c r="I279" s="19"/>
+      <c r="J279" s="23"/>
       <c r="L279" s="11" t="s">
         <v>5</v>
       </c>
@@ -10217,14 +10224,14 @@
       <c r="A280">
         <v>50</v>
       </c>
-      <c r="C280" s="20"/>
-      <c r="D280" s="20"/>
-      <c r="E280" s="21"/>
-      <c r="F280" s="21"/>
-      <c r="G280" s="20"/>
-      <c r="H280" s="20"/>
-      <c r="I280" s="18"/>
-      <c r="J280" s="19"/>
+      <c r="C280" s="18"/>
+      <c r="D280" s="18"/>
+      <c r="E280" s="24"/>
+      <c r="F280" s="24"/>
+      <c r="G280" s="18"/>
+      <c r="H280" s="18"/>
+      <c r="I280" s="19"/>
+      <c r="J280" s="23"/>
       <c r="L280" s="12" t="s">
         <v>15</v>
       </c>
@@ -10250,14 +10257,14 @@
       </c>
     </row>
     <row r="281" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C281" s="20"/>
-      <c r="D281" s="20"/>
-      <c r="E281" s="21"/>
-      <c r="F281" s="21"/>
-      <c r="G281" s="20"/>
-      <c r="H281" s="20"/>
-      <c r="I281" s="18"/>
-      <c r="J281" s="19"/>
+      <c r="C281" s="18"/>
+      <c r="D281" s="18"/>
+      <c r="E281" s="24"/>
+      <c r="F281" s="24"/>
+      <c r="G281" s="18"/>
+      <c r="H281" s="18"/>
+      <c r="I281" s="19"/>
+      <c r="J281" s="23"/>
       <c r="L281" s="14" t="s">
         <v>17</v>
       </c>
@@ -10280,14 +10287,14 @@
       <c r="U281" s="10"/>
     </row>
     <row r="282" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C282" s="20"/>
-      <c r="D282" s="20"/>
-      <c r="E282" s="21"/>
-      <c r="F282" s="21"/>
-      <c r="G282" s="20"/>
-      <c r="H282" s="20"/>
-      <c r="I282" s="18"/>
-      <c r="J282" s="19"/>
+      <c r="C282" s="18"/>
+      <c r="D282" s="18"/>
+      <c r="E282" s="24"/>
+      <c r="F282" s="24"/>
+      <c r="G282" s="18"/>
+      <c r="H282" s="18"/>
+      <c r="I282" s="19"/>
+      <c r="J282" s="23"/>
       <c r="L282" s="15" t="s">
         <v>23</v>
       </c>
@@ -10304,16 +10311,16 @@
       <c r="U282" s="10"/>
     </row>
     <row r="283" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C283" s="20" t="s">
+      <c r="C283" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="D283" s="20"/>
-      <c r="E283" s="21"/>
-      <c r="F283" s="21"/>
-      <c r="G283" s="20"/>
-      <c r="H283" s="20"/>
-      <c r="I283" s="22"/>
-      <c r="J283" s="25" t="s">
+      <c r="D283" s="18"/>
+      <c r="E283" s="24"/>
+      <c r="F283" s="24"/>
+      <c r="G283" s="18"/>
+      <c r="H283" s="18"/>
+      <c r="I283" s="29"/>
+      <c r="J283" s="28" t="s">
         <v>32</v>
       </c>
       <c r="L283" s="9" t="s">
@@ -10338,14 +10345,14 @@
       <c r="U283" s="10"/>
     </row>
     <row r="284" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C284" s="20"/>
-      <c r="D284" s="20"/>
-      <c r="E284" s="21"/>
-      <c r="F284" s="21"/>
-      <c r="G284" s="20"/>
-      <c r="H284" s="20"/>
-      <c r="I284" s="23"/>
-      <c r="J284" s="25"/>
+      <c r="C284" s="18"/>
+      <c r="D284" s="18"/>
+      <c r="E284" s="24"/>
+      <c r="F284" s="24"/>
+      <c r="G284" s="18"/>
+      <c r="H284" s="18"/>
+      <c r="I284" s="30"/>
+      <c r="J284" s="28"/>
       <c r="L284" s="11" t="s">
         <v>5</v>
       </c>
@@ -10384,14 +10391,14 @@
       <c r="B285" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="C285" s="20"/>
-      <c r="D285" s="20"/>
-      <c r="E285" s="21"/>
-      <c r="F285" s="21"/>
-      <c r="G285" s="20"/>
-      <c r="H285" s="20"/>
-      <c r="I285" s="23"/>
-      <c r="J285" s="25"/>
+      <c r="C285" s="18"/>
+      <c r="D285" s="18"/>
+      <c r="E285" s="24"/>
+      <c r="F285" s="24"/>
+      <c r="G285" s="18"/>
+      <c r="H285" s="18"/>
+      <c r="I285" s="30"/>
+      <c r="J285" s="28"/>
       <c r="L285" s="12" t="s">
         <v>15</v>
       </c>
@@ -10412,14 +10419,14 @@
       <c r="B286">
         <v>15</v>
       </c>
-      <c r="C286" s="20"/>
-      <c r="D286" s="20"/>
-      <c r="E286" s="21"/>
-      <c r="F286" s="21"/>
-      <c r="G286" s="20"/>
-      <c r="H286" s="20"/>
-      <c r="I286" s="23"/>
-      <c r="J286" s="25"/>
+      <c r="C286" s="18"/>
+      <c r="D286" s="18"/>
+      <c r="E286" s="24"/>
+      <c r="F286" s="24"/>
+      <c r="G286" s="18"/>
+      <c r="H286" s="18"/>
+      <c r="I286" s="30"/>
+      <c r="J286" s="28"/>
       <c r="L286" s="14" t="s">
         <v>17</v>
       </c>
@@ -10443,14 +10450,14 @@
       <c r="U286" s="10"/>
     </row>
     <row r="287" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C287" s="20"/>
-      <c r="D287" s="20"/>
-      <c r="E287" s="21"/>
-      <c r="F287" s="21"/>
-      <c r="G287" s="20"/>
-      <c r="H287" s="20"/>
-      <c r="I287" s="24"/>
-      <c r="J287" s="25"/>
+      <c r="C287" s="18"/>
+      <c r="D287" s="18"/>
+      <c r="E287" s="24"/>
+      <c r="F287" s="24"/>
+      <c r="G287" s="18"/>
+      <c r="H287" s="18"/>
+      <c r="I287" s="31"/>
+      <c r="J287" s="28"/>
       <c r="L287" s="15" t="s">
         <v>23</v>
       </c>
@@ -10470,6 +10477,406 @@
     </row>
   </sheetData>
   <mergeCells count="416">
+    <mergeCell ref="I278:I282"/>
+    <mergeCell ref="J278:J282"/>
+    <mergeCell ref="C283:C287"/>
+    <mergeCell ref="D283:D287"/>
+    <mergeCell ref="E283:E287"/>
+    <mergeCell ref="F283:F287"/>
+    <mergeCell ref="G283:G287"/>
+    <mergeCell ref="H283:H287"/>
+    <mergeCell ref="I283:I287"/>
+    <mergeCell ref="J283:J287"/>
+    <mergeCell ref="C278:C282"/>
+    <mergeCell ref="D278:D282"/>
+    <mergeCell ref="E278:E282"/>
+    <mergeCell ref="F278:F282"/>
+    <mergeCell ref="G278:G282"/>
+    <mergeCell ref="H278:H282"/>
+    <mergeCell ref="I267:I271"/>
+    <mergeCell ref="J267:J271"/>
+    <mergeCell ref="C273:C277"/>
+    <mergeCell ref="D273:D277"/>
+    <mergeCell ref="E273:E277"/>
+    <mergeCell ref="F273:F277"/>
+    <mergeCell ref="G273:G277"/>
+    <mergeCell ref="H273:H277"/>
+    <mergeCell ref="I273:I277"/>
+    <mergeCell ref="J273:J277"/>
+    <mergeCell ref="C267:C271"/>
+    <mergeCell ref="D267:D271"/>
+    <mergeCell ref="E267:E271"/>
+    <mergeCell ref="F267:F271"/>
+    <mergeCell ref="G267:G271"/>
+    <mergeCell ref="H267:H271"/>
+    <mergeCell ref="I257:I261"/>
+    <mergeCell ref="J257:J261"/>
+    <mergeCell ref="C262:C266"/>
+    <mergeCell ref="D262:D266"/>
+    <mergeCell ref="E262:E266"/>
+    <mergeCell ref="F262:F266"/>
+    <mergeCell ref="G262:G266"/>
+    <mergeCell ref="H262:H266"/>
+    <mergeCell ref="I262:I266"/>
+    <mergeCell ref="J262:J266"/>
+    <mergeCell ref="C257:C261"/>
+    <mergeCell ref="D257:D261"/>
+    <mergeCell ref="E257:E261"/>
+    <mergeCell ref="F257:F261"/>
+    <mergeCell ref="G257:G261"/>
+    <mergeCell ref="H257:H261"/>
+    <mergeCell ref="I246:I250"/>
+    <mergeCell ref="J246:J250"/>
+    <mergeCell ref="C251:C255"/>
+    <mergeCell ref="D251:D255"/>
+    <mergeCell ref="E251:E255"/>
+    <mergeCell ref="F251:F255"/>
+    <mergeCell ref="G251:G255"/>
+    <mergeCell ref="H251:H255"/>
+    <mergeCell ref="I251:I255"/>
+    <mergeCell ref="J251:J255"/>
+    <mergeCell ref="C246:C250"/>
+    <mergeCell ref="D246:D250"/>
+    <mergeCell ref="E246:E250"/>
+    <mergeCell ref="F246:F250"/>
+    <mergeCell ref="G246:G250"/>
+    <mergeCell ref="H246:H250"/>
+    <mergeCell ref="I235:I239"/>
+    <mergeCell ref="J235:J239"/>
+    <mergeCell ref="C241:C245"/>
+    <mergeCell ref="D241:D245"/>
+    <mergeCell ref="E241:E245"/>
+    <mergeCell ref="F241:F245"/>
+    <mergeCell ref="G241:G245"/>
+    <mergeCell ref="H241:H245"/>
+    <mergeCell ref="I241:I245"/>
+    <mergeCell ref="J241:J245"/>
+    <mergeCell ref="C235:C239"/>
+    <mergeCell ref="D235:D239"/>
+    <mergeCell ref="E235:E239"/>
+    <mergeCell ref="F235:F239"/>
+    <mergeCell ref="G235:G239"/>
+    <mergeCell ref="H235:H239"/>
+    <mergeCell ref="I225:I229"/>
+    <mergeCell ref="J225:J229"/>
+    <mergeCell ref="C230:C234"/>
+    <mergeCell ref="D230:D234"/>
+    <mergeCell ref="E230:E234"/>
+    <mergeCell ref="F230:F234"/>
+    <mergeCell ref="G230:G234"/>
+    <mergeCell ref="H230:H234"/>
+    <mergeCell ref="I230:I234"/>
+    <mergeCell ref="J230:J234"/>
+    <mergeCell ref="C225:C229"/>
+    <mergeCell ref="D225:D229"/>
+    <mergeCell ref="E225:E229"/>
+    <mergeCell ref="F225:F229"/>
+    <mergeCell ref="G225:G229"/>
+    <mergeCell ref="H225:H229"/>
+    <mergeCell ref="I212:I216"/>
+    <mergeCell ref="J212:J216"/>
+    <mergeCell ref="C217:C221"/>
+    <mergeCell ref="D217:D221"/>
+    <mergeCell ref="E217:E221"/>
+    <mergeCell ref="F217:F221"/>
+    <mergeCell ref="G217:G221"/>
+    <mergeCell ref="H217:H221"/>
+    <mergeCell ref="I217:I221"/>
+    <mergeCell ref="J217:J221"/>
+    <mergeCell ref="C212:C216"/>
+    <mergeCell ref="D212:D216"/>
+    <mergeCell ref="E212:E216"/>
+    <mergeCell ref="F212:F216"/>
+    <mergeCell ref="G212:G216"/>
+    <mergeCell ref="H212:H216"/>
+    <mergeCell ref="I201:I205"/>
+    <mergeCell ref="J201:J205"/>
+    <mergeCell ref="C207:C211"/>
+    <mergeCell ref="D207:D211"/>
+    <mergeCell ref="E207:E211"/>
+    <mergeCell ref="F207:F211"/>
+    <mergeCell ref="G207:G211"/>
+    <mergeCell ref="H207:H211"/>
+    <mergeCell ref="I207:I211"/>
+    <mergeCell ref="J207:J211"/>
+    <mergeCell ref="C201:C205"/>
+    <mergeCell ref="D201:D205"/>
+    <mergeCell ref="E201:E205"/>
+    <mergeCell ref="F201:F205"/>
+    <mergeCell ref="G201:G205"/>
+    <mergeCell ref="H201:H205"/>
+    <mergeCell ref="I191:I195"/>
+    <mergeCell ref="J191:J195"/>
+    <mergeCell ref="C196:C200"/>
+    <mergeCell ref="D196:D200"/>
+    <mergeCell ref="E196:E200"/>
+    <mergeCell ref="F196:F200"/>
+    <mergeCell ref="G196:G200"/>
+    <mergeCell ref="H196:H200"/>
+    <mergeCell ref="I196:I200"/>
+    <mergeCell ref="J196:J200"/>
+    <mergeCell ref="C191:C195"/>
+    <mergeCell ref="D191:D195"/>
+    <mergeCell ref="E191:E195"/>
+    <mergeCell ref="F191:F195"/>
+    <mergeCell ref="G191:G195"/>
+    <mergeCell ref="H191:H195"/>
+    <mergeCell ref="I180:I184"/>
+    <mergeCell ref="J180:J184"/>
+    <mergeCell ref="C185:C189"/>
+    <mergeCell ref="D185:D189"/>
+    <mergeCell ref="E185:E189"/>
+    <mergeCell ref="F185:F189"/>
+    <mergeCell ref="G185:G189"/>
+    <mergeCell ref="H185:H189"/>
+    <mergeCell ref="I185:I189"/>
+    <mergeCell ref="J185:J189"/>
+    <mergeCell ref="C180:C184"/>
+    <mergeCell ref="D180:D184"/>
+    <mergeCell ref="E180:E184"/>
+    <mergeCell ref="F180:F184"/>
+    <mergeCell ref="G180:G184"/>
+    <mergeCell ref="H180:H184"/>
+    <mergeCell ref="I169:I173"/>
+    <mergeCell ref="J169:J173"/>
+    <mergeCell ref="C175:C179"/>
+    <mergeCell ref="D175:D179"/>
+    <mergeCell ref="E175:E179"/>
+    <mergeCell ref="F175:F179"/>
+    <mergeCell ref="G175:G179"/>
+    <mergeCell ref="H175:H179"/>
+    <mergeCell ref="I175:I179"/>
+    <mergeCell ref="J175:J179"/>
+    <mergeCell ref="C169:C173"/>
+    <mergeCell ref="D169:D173"/>
+    <mergeCell ref="E169:E173"/>
+    <mergeCell ref="F169:F173"/>
+    <mergeCell ref="G169:G173"/>
+    <mergeCell ref="H169:H173"/>
+    <mergeCell ref="I159:I163"/>
+    <mergeCell ref="J159:J163"/>
+    <mergeCell ref="C164:C168"/>
+    <mergeCell ref="D164:D168"/>
+    <mergeCell ref="E164:E168"/>
+    <mergeCell ref="F164:F168"/>
+    <mergeCell ref="G164:G168"/>
+    <mergeCell ref="H164:H168"/>
+    <mergeCell ref="I164:I168"/>
+    <mergeCell ref="J164:J168"/>
+    <mergeCell ref="C159:C163"/>
+    <mergeCell ref="D159:D163"/>
+    <mergeCell ref="E159:E163"/>
+    <mergeCell ref="F159:F163"/>
+    <mergeCell ref="G159:G163"/>
+    <mergeCell ref="H159:H163"/>
+    <mergeCell ref="I147:I151"/>
+    <mergeCell ref="J147:J151"/>
+    <mergeCell ref="C152:C156"/>
+    <mergeCell ref="D152:D156"/>
+    <mergeCell ref="E152:E156"/>
+    <mergeCell ref="F152:F156"/>
+    <mergeCell ref="G152:G156"/>
+    <mergeCell ref="H152:H156"/>
+    <mergeCell ref="I152:I156"/>
+    <mergeCell ref="J152:J156"/>
+    <mergeCell ref="C147:C151"/>
+    <mergeCell ref="D147:D151"/>
+    <mergeCell ref="E147:E151"/>
+    <mergeCell ref="F147:F151"/>
+    <mergeCell ref="G147:G151"/>
+    <mergeCell ref="H147:H151"/>
+    <mergeCell ref="I136:I140"/>
+    <mergeCell ref="J136:J140"/>
+    <mergeCell ref="C142:C146"/>
+    <mergeCell ref="D142:D146"/>
+    <mergeCell ref="E142:E146"/>
+    <mergeCell ref="F142:F146"/>
+    <mergeCell ref="G142:G146"/>
+    <mergeCell ref="H142:H146"/>
+    <mergeCell ref="I142:I146"/>
+    <mergeCell ref="J142:J146"/>
+    <mergeCell ref="C136:C140"/>
+    <mergeCell ref="D136:D140"/>
+    <mergeCell ref="E136:E140"/>
+    <mergeCell ref="F136:F140"/>
+    <mergeCell ref="G136:G140"/>
+    <mergeCell ref="H136:H140"/>
+    <mergeCell ref="I126:I130"/>
+    <mergeCell ref="J126:J130"/>
+    <mergeCell ref="C131:C135"/>
+    <mergeCell ref="D131:D135"/>
+    <mergeCell ref="E131:E135"/>
+    <mergeCell ref="F131:F135"/>
+    <mergeCell ref="G131:G135"/>
+    <mergeCell ref="H131:H135"/>
+    <mergeCell ref="I131:I135"/>
+    <mergeCell ref="J131:J135"/>
+    <mergeCell ref="C126:C130"/>
+    <mergeCell ref="D126:D130"/>
+    <mergeCell ref="E126:E130"/>
+    <mergeCell ref="F126:F130"/>
+    <mergeCell ref="G126:G130"/>
+    <mergeCell ref="H126:H130"/>
+    <mergeCell ref="I115:I119"/>
+    <mergeCell ref="J115:J119"/>
+    <mergeCell ref="C120:C124"/>
+    <mergeCell ref="D120:D124"/>
+    <mergeCell ref="E120:E124"/>
+    <mergeCell ref="F120:F124"/>
+    <mergeCell ref="G120:G124"/>
+    <mergeCell ref="H120:H124"/>
+    <mergeCell ref="I120:I124"/>
+    <mergeCell ref="J120:J124"/>
+    <mergeCell ref="C115:C119"/>
+    <mergeCell ref="D115:D119"/>
+    <mergeCell ref="E115:E119"/>
+    <mergeCell ref="F115:F119"/>
+    <mergeCell ref="G115:G119"/>
+    <mergeCell ref="H115:H119"/>
+    <mergeCell ref="I104:I108"/>
+    <mergeCell ref="J104:J108"/>
+    <mergeCell ref="C110:C114"/>
+    <mergeCell ref="D110:D114"/>
+    <mergeCell ref="E110:E114"/>
+    <mergeCell ref="F110:F114"/>
+    <mergeCell ref="G110:G114"/>
+    <mergeCell ref="H110:H114"/>
+    <mergeCell ref="I110:I114"/>
+    <mergeCell ref="J110:J114"/>
+    <mergeCell ref="C104:C108"/>
+    <mergeCell ref="D104:D108"/>
+    <mergeCell ref="E104:E108"/>
+    <mergeCell ref="F104:F108"/>
+    <mergeCell ref="G104:G108"/>
+    <mergeCell ref="H104:H108"/>
+    <mergeCell ref="I94:I98"/>
+    <mergeCell ref="J94:J98"/>
+    <mergeCell ref="C99:C103"/>
+    <mergeCell ref="D99:D103"/>
+    <mergeCell ref="E99:E103"/>
+    <mergeCell ref="F99:F103"/>
+    <mergeCell ref="G99:G103"/>
+    <mergeCell ref="H99:H103"/>
+    <mergeCell ref="I99:I103"/>
+    <mergeCell ref="J99:J103"/>
+    <mergeCell ref="C94:C98"/>
+    <mergeCell ref="D94:D98"/>
+    <mergeCell ref="E94:E98"/>
+    <mergeCell ref="F94:F98"/>
+    <mergeCell ref="G94:G98"/>
+    <mergeCell ref="H94:H98"/>
+    <mergeCell ref="I82:I86"/>
+    <mergeCell ref="J82:J86"/>
+    <mergeCell ref="C87:C91"/>
+    <mergeCell ref="D87:D91"/>
+    <mergeCell ref="E87:E91"/>
+    <mergeCell ref="F87:F91"/>
+    <mergeCell ref="G87:G91"/>
+    <mergeCell ref="H87:H91"/>
+    <mergeCell ref="I87:I91"/>
+    <mergeCell ref="J87:J91"/>
+    <mergeCell ref="C82:C86"/>
+    <mergeCell ref="D82:D86"/>
+    <mergeCell ref="E82:E86"/>
+    <mergeCell ref="F82:F86"/>
+    <mergeCell ref="G82:G86"/>
+    <mergeCell ref="H82:H86"/>
+    <mergeCell ref="I71:I75"/>
+    <mergeCell ref="J71:J75"/>
+    <mergeCell ref="C77:C81"/>
+    <mergeCell ref="D77:D81"/>
+    <mergeCell ref="E77:E81"/>
+    <mergeCell ref="F77:F81"/>
+    <mergeCell ref="G77:G81"/>
+    <mergeCell ref="H77:H81"/>
+    <mergeCell ref="I77:I81"/>
+    <mergeCell ref="J77:J81"/>
+    <mergeCell ref="C71:C75"/>
+    <mergeCell ref="D71:D75"/>
+    <mergeCell ref="E71:E75"/>
+    <mergeCell ref="F71:F75"/>
+    <mergeCell ref="G71:G75"/>
+    <mergeCell ref="H71:H75"/>
+    <mergeCell ref="I61:I65"/>
+    <mergeCell ref="J61:J65"/>
+    <mergeCell ref="C66:C70"/>
+    <mergeCell ref="D66:D70"/>
+    <mergeCell ref="E66:E70"/>
+    <mergeCell ref="F66:F70"/>
+    <mergeCell ref="G66:G70"/>
+    <mergeCell ref="H66:H70"/>
+    <mergeCell ref="I66:I70"/>
+    <mergeCell ref="J66:J70"/>
+    <mergeCell ref="C61:C65"/>
+    <mergeCell ref="D61:D65"/>
+    <mergeCell ref="E61:E65"/>
+    <mergeCell ref="F61:F65"/>
+    <mergeCell ref="G61:G65"/>
+    <mergeCell ref="H61:H65"/>
+    <mergeCell ref="I50:I54"/>
+    <mergeCell ref="J50:J54"/>
+    <mergeCell ref="C55:C59"/>
+    <mergeCell ref="D55:D59"/>
+    <mergeCell ref="E55:E59"/>
+    <mergeCell ref="F55:F59"/>
+    <mergeCell ref="G55:G59"/>
+    <mergeCell ref="H55:H59"/>
+    <mergeCell ref="I55:I59"/>
+    <mergeCell ref="J55:J59"/>
+    <mergeCell ref="C50:C54"/>
+    <mergeCell ref="D50:D54"/>
+    <mergeCell ref="E50:E54"/>
+    <mergeCell ref="F50:F54"/>
+    <mergeCell ref="G50:G54"/>
+    <mergeCell ref="H50:H54"/>
+    <mergeCell ref="I39:I43"/>
+    <mergeCell ref="J39:J43"/>
+    <mergeCell ref="C45:C49"/>
+    <mergeCell ref="D45:D49"/>
+    <mergeCell ref="E45:E49"/>
+    <mergeCell ref="F45:F49"/>
+    <mergeCell ref="G45:G49"/>
+    <mergeCell ref="H45:H49"/>
+    <mergeCell ref="I45:I49"/>
+    <mergeCell ref="J45:J49"/>
+    <mergeCell ref="C39:C43"/>
+    <mergeCell ref="D39:D43"/>
+    <mergeCell ref="E39:E43"/>
+    <mergeCell ref="F39:F43"/>
+    <mergeCell ref="G39:G43"/>
+    <mergeCell ref="H39:H43"/>
+    <mergeCell ref="I29:I33"/>
+    <mergeCell ref="J29:J33"/>
+    <mergeCell ref="C34:C38"/>
+    <mergeCell ref="D34:D38"/>
+    <mergeCell ref="E34:E38"/>
+    <mergeCell ref="F34:F38"/>
+    <mergeCell ref="G34:G38"/>
+    <mergeCell ref="H34:H38"/>
+    <mergeCell ref="I34:I38"/>
+    <mergeCell ref="J34:J38"/>
+    <mergeCell ref="C29:C33"/>
+    <mergeCell ref="D29:D33"/>
+    <mergeCell ref="E29:E33"/>
+    <mergeCell ref="F29:F33"/>
+    <mergeCell ref="G29:G33"/>
+    <mergeCell ref="H29:H33"/>
+    <mergeCell ref="I17:I21"/>
+    <mergeCell ref="J17:J21"/>
+    <mergeCell ref="C22:C26"/>
+    <mergeCell ref="D22:D26"/>
+    <mergeCell ref="E22:E26"/>
+    <mergeCell ref="F22:F26"/>
+    <mergeCell ref="G22:G26"/>
+    <mergeCell ref="H22:H26"/>
+    <mergeCell ref="I22:I26"/>
+    <mergeCell ref="J22:J26"/>
+    <mergeCell ref="C17:C21"/>
+    <mergeCell ref="D17:D21"/>
+    <mergeCell ref="E17:E21"/>
+    <mergeCell ref="F17:F21"/>
+    <mergeCell ref="G17:G21"/>
+    <mergeCell ref="H17:H21"/>
     <mergeCell ref="I7:I11"/>
     <mergeCell ref="J7:J11"/>
     <mergeCell ref="C12:C16"/>
@@ -10486,406 +10893,6 @@
     <mergeCell ref="F7:F11"/>
     <mergeCell ref="G7:G11"/>
     <mergeCell ref="H7:H11"/>
-    <mergeCell ref="I17:I21"/>
-    <mergeCell ref="J17:J21"/>
-    <mergeCell ref="C22:C26"/>
-    <mergeCell ref="D22:D26"/>
-    <mergeCell ref="E22:E26"/>
-    <mergeCell ref="F22:F26"/>
-    <mergeCell ref="G22:G26"/>
-    <mergeCell ref="H22:H26"/>
-    <mergeCell ref="I22:I26"/>
-    <mergeCell ref="J22:J26"/>
-    <mergeCell ref="C17:C21"/>
-    <mergeCell ref="D17:D21"/>
-    <mergeCell ref="E17:E21"/>
-    <mergeCell ref="F17:F21"/>
-    <mergeCell ref="G17:G21"/>
-    <mergeCell ref="H17:H21"/>
-    <mergeCell ref="I29:I33"/>
-    <mergeCell ref="J29:J33"/>
-    <mergeCell ref="C34:C38"/>
-    <mergeCell ref="D34:D38"/>
-    <mergeCell ref="E34:E38"/>
-    <mergeCell ref="F34:F38"/>
-    <mergeCell ref="G34:G38"/>
-    <mergeCell ref="H34:H38"/>
-    <mergeCell ref="I34:I38"/>
-    <mergeCell ref="J34:J38"/>
-    <mergeCell ref="C29:C33"/>
-    <mergeCell ref="D29:D33"/>
-    <mergeCell ref="E29:E33"/>
-    <mergeCell ref="F29:F33"/>
-    <mergeCell ref="G29:G33"/>
-    <mergeCell ref="H29:H33"/>
-    <mergeCell ref="I39:I43"/>
-    <mergeCell ref="J39:J43"/>
-    <mergeCell ref="C45:C49"/>
-    <mergeCell ref="D45:D49"/>
-    <mergeCell ref="E45:E49"/>
-    <mergeCell ref="F45:F49"/>
-    <mergeCell ref="G45:G49"/>
-    <mergeCell ref="H45:H49"/>
-    <mergeCell ref="I45:I49"/>
-    <mergeCell ref="J45:J49"/>
-    <mergeCell ref="C39:C43"/>
-    <mergeCell ref="D39:D43"/>
-    <mergeCell ref="E39:E43"/>
-    <mergeCell ref="F39:F43"/>
-    <mergeCell ref="G39:G43"/>
-    <mergeCell ref="H39:H43"/>
-    <mergeCell ref="I50:I54"/>
-    <mergeCell ref="J50:J54"/>
-    <mergeCell ref="C55:C59"/>
-    <mergeCell ref="D55:D59"/>
-    <mergeCell ref="E55:E59"/>
-    <mergeCell ref="F55:F59"/>
-    <mergeCell ref="G55:G59"/>
-    <mergeCell ref="H55:H59"/>
-    <mergeCell ref="I55:I59"/>
-    <mergeCell ref="J55:J59"/>
-    <mergeCell ref="C50:C54"/>
-    <mergeCell ref="D50:D54"/>
-    <mergeCell ref="E50:E54"/>
-    <mergeCell ref="F50:F54"/>
-    <mergeCell ref="G50:G54"/>
-    <mergeCell ref="H50:H54"/>
-    <mergeCell ref="I61:I65"/>
-    <mergeCell ref="J61:J65"/>
-    <mergeCell ref="C66:C70"/>
-    <mergeCell ref="D66:D70"/>
-    <mergeCell ref="E66:E70"/>
-    <mergeCell ref="F66:F70"/>
-    <mergeCell ref="G66:G70"/>
-    <mergeCell ref="H66:H70"/>
-    <mergeCell ref="I66:I70"/>
-    <mergeCell ref="J66:J70"/>
-    <mergeCell ref="C61:C65"/>
-    <mergeCell ref="D61:D65"/>
-    <mergeCell ref="E61:E65"/>
-    <mergeCell ref="F61:F65"/>
-    <mergeCell ref="G61:G65"/>
-    <mergeCell ref="H61:H65"/>
-    <mergeCell ref="I71:I75"/>
-    <mergeCell ref="J71:J75"/>
-    <mergeCell ref="C77:C81"/>
-    <mergeCell ref="D77:D81"/>
-    <mergeCell ref="E77:E81"/>
-    <mergeCell ref="F77:F81"/>
-    <mergeCell ref="G77:G81"/>
-    <mergeCell ref="H77:H81"/>
-    <mergeCell ref="I77:I81"/>
-    <mergeCell ref="J77:J81"/>
-    <mergeCell ref="C71:C75"/>
-    <mergeCell ref="D71:D75"/>
-    <mergeCell ref="E71:E75"/>
-    <mergeCell ref="F71:F75"/>
-    <mergeCell ref="G71:G75"/>
-    <mergeCell ref="H71:H75"/>
-    <mergeCell ref="I82:I86"/>
-    <mergeCell ref="J82:J86"/>
-    <mergeCell ref="C87:C91"/>
-    <mergeCell ref="D87:D91"/>
-    <mergeCell ref="E87:E91"/>
-    <mergeCell ref="F87:F91"/>
-    <mergeCell ref="G87:G91"/>
-    <mergeCell ref="H87:H91"/>
-    <mergeCell ref="I87:I91"/>
-    <mergeCell ref="J87:J91"/>
-    <mergeCell ref="C82:C86"/>
-    <mergeCell ref="D82:D86"/>
-    <mergeCell ref="E82:E86"/>
-    <mergeCell ref="F82:F86"/>
-    <mergeCell ref="G82:G86"/>
-    <mergeCell ref="H82:H86"/>
-    <mergeCell ref="I94:I98"/>
-    <mergeCell ref="J94:J98"/>
-    <mergeCell ref="C99:C103"/>
-    <mergeCell ref="D99:D103"/>
-    <mergeCell ref="E99:E103"/>
-    <mergeCell ref="F99:F103"/>
-    <mergeCell ref="G99:G103"/>
-    <mergeCell ref="H99:H103"/>
-    <mergeCell ref="I99:I103"/>
-    <mergeCell ref="J99:J103"/>
-    <mergeCell ref="C94:C98"/>
-    <mergeCell ref="D94:D98"/>
-    <mergeCell ref="E94:E98"/>
-    <mergeCell ref="F94:F98"/>
-    <mergeCell ref="G94:G98"/>
-    <mergeCell ref="H94:H98"/>
-    <mergeCell ref="I104:I108"/>
-    <mergeCell ref="J104:J108"/>
-    <mergeCell ref="C110:C114"/>
-    <mergeCell ref="D110:D114"/>
-    <mergeCell ref="E110:E114"/>
-    <mergeCell ref="F110:F114"/>
-    <mergeCell ref="G110:G114"/>
-    <mergeCell ref="H110:H114"/>
-    <mergeCell ref="I110:I114"/>
-    <mergeCell ref="J110:J114"/>
-    <mergeCell ref="C104:C108"/>
-    <mergeCell ref="D104:D108"/>
-    <mergeCell ref="E104:E108"/>
-    <mergeCell ref="F104:F108"/>
-    <mergeCell ref="G104:G108"/>
-    <mergeCell ref="H104:H108"/>
-    <mergeCell ref="I115:I119"/>
-    <mergeCell ref="J115:J119"/>
-    <mergeCell ref="C120:C124"/>
-    <mergeCell ref="D120:D124"/>
-    <mergeCell ref="E120:E124"/>
-    <mergeCell ref="F120:F124"/>
-    <mergeCell ref="G120:G124"/>
-    <mergeCell ref="H120:H124"/>
-    <mergeCell ref="I120:I124"/>
-    <mergeCell ref="J120:J124"/>
-    <mergeCell ref="C115:C119"/>
-    <mergeCell ref="D115:D119"/>
-    <mergeCell ref="E115:E119"/>
-    <mergeCell ref="F115:F119"/>
-    <mergeCell ref="G115:G119"/>
-    <mergeCell ref="H115:H119"/>
-    <mergeCell ref="I126:I130"/>
-    <mergeCell ref="J126:J130"/>
-    <mergeCell ref="C131:C135"/>
-    <mergeCell ref="D131:D135"/>
-    <mergeCell ref="E131:E135"/>
-    <mergeCell ref="F131:F135"/>
-    <mergeCell ref="G131:G135"/>
-    <mergeCell ref="H131:H135"/>
-    <mergeCell ref="I131:I135"/>
-    <mergeCell ref="J131:J135"/>
-    <mergeCell ref="C126:C130"/>
-    <mergeCell ref="D126:D130"/>
-    <mergeCell ref="E126:E130"/>
-    <mergeCell ref="F126:F130"/>
-    <mergeCell ref="G126:G130"/>
-    <mergeCell ref="H126:H130"/>
-    <mergeCell ref="I136:I140"/>
-    <mergeCell ref="J136:J140"/>
-    <mergeCell ref="C142:C146"/>
-    <mergeCell ref="D142:D146"/>
-    <mergeCell ref="E142:E146"/>
-    <mergeCell ref="F142:F146"/>
-    <mergeCell ref="G142:G146"/>
-    <mergeCell ref="H142:H146"/>
-    <mergeCell ref="I142:I146"/>
-    <mergeCell ref="J142:J146"/>
-    <mergeCell ref="C136:C140"/>
-    <mergeCell ref="D136:D140"/>
-    <mergeCell ref="E136:E140"/>
-    <mergeCell ref="F136:F140"/>
-    <mergeCell ref="G136:G140"/>
-    <mergeCell ref="H136:H140"/>
-    <mergeCell ref="I147:I151"/>
-    <mergeCell ref="J147:J151"/>
-    <mergeCell ref="C152:C156"/>
-    <mergeCell ref="D152:D156"/>
-    <mergeCell ref="E152:E156"/>
-    <mergeCell ref="F152:F156"/>
-    <mergeCell ref="G152:G156"/>
-    <mergeCell ref="H152:H156"/>
-    <mergeCell ref="I152:I156"/>
-    <mergeCell ref="J152:J156"/>
-    <mergeCell ref="C147:C151"/>
-    <mergeCell ref="D147:D151"/>
-    <mergeCell ref="E147:E151"/>
-    <mergeCell ref="F147:F151"/>
-    <mergeCell ref="G147:G151"/>
-    <mergeCell ref="H147:H151"/>
-    <mergeCell ref="I159:I163"/>
-    <mergeCell ref="J159:J163"/>
-    <mergeCell ref="C164:C168"/>
-    <mergeCell ref="D164:D168"/>
-    <mergeCell ref="E164:E168"/>
-    <mergeCell ref="F164:F168"/>
-    <mergeCell ref="G164:G168"/>
-    <mergeCell ref="H164:H168"/>
-    <mergeCell ref="I164:I168"/>
-    <mergeCell ref="J164:J168"/>
-    <mergeCell ref="C159:C163"/>
-    <mergeCell ref="D159:D163"/>
-    <mergeCell ref="E159:E163"/>
-    <mergeCell ref="F159:F163"/>
-    <mergeCell ref="G159:G163"/>
-    <mergeCell ref="H159:H163"/>
-    <mergeCell ref="I169:I173"/>
-    <mergeCell ref="J169:J173"/>
-    <mergeCell ref="C175:C179"/>
-    <mergeCell ref="D175:D179"/>
-    <mergeCell ref="E175:E179"/>
-    <mergeCell ref="F175:F179"/>
-    <mergeCell ref="G175:G179"/>
-    <mergeCell ref="H175:H179"/>
-    <mergeCell ref="I175:I179"/>
-    <mergeCell ref="J175:J179"/>
-    <mergeCell ref="C169:C173"/>
-    <mergeCell ref="D169:D173"/>
-    <mergeCell ref="E169:E173"/>
-    <mergeCell ref="F169:F173"/>
-    <mergeCell ref="G169:G173"/>
-    <mergeCell ref="H169:H173"/>
-    <mergeCell ref="I180:I184"/>
-    <mergeCell ref="J180:J184"/>
-    <mergeCell ref="C185:C189"/>
-    <mergeCell ref="D185:D189"/>
-    <mergeCell ref="E185:E189"/>
-    <mergeCell ref="F185:F189"/>
-    <mergeCell ref="G185:G189"/>
-    <mergeCell ref="H185:H189"/>
-    <mergeCell ref="I185:I189"/>
-    <mergeCell ref="J185:J189"/>
-    <mergeCell ref="C180:C184"/>
-    <mergeCell ref="D180:D184"/>
-    <mergeCell ref="E180:E184"/>
-    <mergeCell ref="F180:F184"/>
-    <mergeCell ref="G180:G184"/>
-    <mergeCell ref="H180:H184"/>
-    <mergeCell ref="I191:I195"/>
-    <mergeCell ref="J191:J195"/>
-    <mergeCell ref="C196:C200"/>
-    <mergeCell ref="D196:D200"/>
-    <mergeCell ref="E196:E200"/>
-    <mergeCell ref="F196:F200"/>
-    <mergeCell ref="G196:G200"/>
-    <mergeCell ref="H196:H200"/>
-    <mergeCell ref="I196:I200"/>
-    <mergeCell ref="J196:J200"/>
-    <mergeCell ref="C191:C195"/>
-    <mergeCell ref="D191:D195"/>
-    <mergeCell ref="E191:E195"/>
-    <mergeCell ref="F191:F195"/>
-    <mergeCell ref="G191:G195"/>
-    <mergeCell ref="H191:H195"/>
-    <mergeCell ref="I201:I205"/>
-    <mergeCell ref="J201:J205"/>
-    <mergeCell ref="C207:C211"/>
-    <mergeCell ref="D207:D211"/>
-    <mergeCell ref="E207:E211"/>
-    <mergeCell ref="F207:F211"/>
-    <mergeCell ref="G207:G211"/>
-    <mergeCell ref="H207:H211"/>
-    <mergeCell ref="I207:I211"/>
-    <mergeCell ref="J207:J211"/>
-    <mergeCell ref="C201:C205"/>
-    <mergeCell ref="D201:D205"/>
-    <mergeCell ref="E201:E205"/>
-    <mergeCell ref="F201:F205"/>
-    <mergeCell ref="G201:G205"/>
-    <mergeCell ref="H201:H205"/>
-    <mergeCell ref="I212:I216"/>
-    <mergeCell ref="J212:J216"/>
-    <mergeCell ref="C217:C221"/>
-    <mergeCell ref="D217:D221"/>
-    <mergeCell ref="E217:E221"/>
-    <mergeCell ref="F217:F221"/>
-    <mergeCell ref="G217:G221"/>
-    <mergeCell ref="H217:H221"/>
-    <mergeCell ref="I217:I221"/>
-    <mergeCell ref="J217:J221"/>
-    <mergeCell ref="C212:C216"/>
-    <mergeCell ref="D212:D216"/>
-    <mergeCell ref="E212:E216"/>
-    <mergeCell ref="F212:F216"/>
-    <mergeCell ref="G212:G216"/>
-    <mergeCell ref="H212:H216"/>
-    <mergeCell ref="I225:I229"/>
-    <mergeCell ref="J225:J229"/>
-    <mergeCell ref="C230:C234"/>
-    <mergeCell ref="D230:D234"/>
-    <mergeCell ref="E230:E234"/>
-    <mergeCell ref="F230:F234"/>
-    <mergeCell ref="G230:G234"/>
-    <mergeCell ref="H230:H234"/>
-    <mergeCell ref="I230:I234"/>
-    <mergeCell ref="J230:J234"/>
-    <mergeCell ref="C225:C229"/>
-    <mergeCell ref="D225:D229"/>
-    <mergeCell ref="E225:E229"/>
-    <mergeCell ref="F225:F229"/>
-    <mergeCell ref="G225:G229"/>
-    <mergeCell ref="H225:H229"/>
-    <mergeCell ref="I235:I239"/>
-    <mergeCell ref="J235:J239"/>
-    <mergeCell ref="C241:C245"/>
-    <mergeCell ref="D241:D245"/>
-    <mergeCell ref="E241:E245"/>
-    <mergeCell ref="F241:F245"/>
-    <mergeCell ref="G241:G245"/>
-    <mergeCell ref="H241:H245"/>
-    <mergeCell ref="I241:I245"/>
-    <mergeCell ref="J241:J245"/>
-    <mergeCell ref="C235:C239"/>
-    <mergeCell ref="D235:D239"/>
-    <mergeCell ref="E235:E239"/>
-    <mergeCell ref="F235:F239"/>
-    <mergeCell ref="G235:G239"/>
-    <mergeCell ref="H235:H239"/>
-    <mergeCell ref="I246:I250"/>
-    <mergeCell ref="J246:J250"/>
-    <mergeCell ref="C251:C255"/>
-    <mergeCell ref="D251:D255"/>
-    <mergeCell ref="E251:E255"/>
-    <mergeCell ref="F251:F255"/>
-    <mergeCell ref="G251:G255"/>
-    <mergeCell ref="H251:H255"/>
-    <mergeCell ref="I251:I255"/>
-    <mergeCell ref="J251:J255"/>
-    <mergeCell ref="C246:C250"/>
-    <mergeCell ref="D246:D250"/>
-    <mergeCell ref="E246:E250"/>
-    <mergeCell ref="F246:F250"/>
-    <mergeCell ref="G246:G250"/>
-    <mergeCell ref="H246:H250"/>
-    <mergeCell ref="I257:I261"/>
-    <mergeCell ref="J257:J261"/>
-    <mergeCell ref="C262:C266"/>
-    <mergeCell ref="D262:D266"/>
-    <mergeCell ref="E262:E266"/>
-    <mergeCell ref="F262:F266"/>
-    <mergeCell ref="G262:G266"/>
-    <mergeCell ref="H262:H266"/>
-    <mergeCell ref="I262:I266"/>
-    <mergeCell ref="J262:J266"/>
-    <mergeCell ref="C257:C261"/>
-    <mergeCell ref="D257:D261"/>
-    <mergeCell ref="E257:E261"/>
-    <mergeCell ref="F257:F261"/>
-    <mergeCell ref="G257:G261"/>
-    <mergeCell ref="H257:H261"/>
-    <mergeCell ref="I267:I271"/>
-    <mergeCell ref="J267:J271"/>
-    <mergeCell ref="C273:C277"/>
-    <mergeCell ref="D273:D277"/>
-    <mergeCell ref="E273:E277"/>
-    <mergeCell ref="F273:F277"/>
-    <mergeCell ref="G273:G277"/>
-    <mergeCell ref="H273:H277"/>
-    <mergeCell ref="I273:I277"/>
-    <mergeCell ref="J273:J277"/>
-    <mergeCell ref="C267:C271"/>
-    <mergeCell ref="D267:D271"/>
-    <mergeCell ref="E267:E271"/>
-    <mergeCell ref="F267:F271"/>
-    <mergeCell ref="G267:G271"/>
-    <mergeCell ref="H267:H271"/>
-    <mergeCell ref="I278:I282"/>
-    <mergeCell ref="J278:J282"/>
-    <mergeCell ref="C283:C287"/>
-    <mergeCell ref="D283:D287"/>
-    <mergeCell ref="E283:E287"/>
-    <mergeCell ref="F283:F287"/>
-    <mergeCell ref="G283:G287"/>
-    <mergeCell ref="H283:H287"/>
-    <mergeCell ref="I283:I287"/>
-    <mergeCell ref="J283:J287"/>
-    <mergeCell ref="C278:C282"/>
-    <mergeCell ref="D278:D282"/>
-    <mergeCell ref="E278:E282"/>
-    <mergeCell ref="F278:F282"/>
-    <mergeCell ref="G278:G282"/>
-    <mergeCell ref="H278:H282"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
